--- a/input_examples/distanceDependency_square_amp.xlsx
+++ b/input_examples/distanceDependency_square_amp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\SelfImaging\input_examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B71E6C8-08F7-4FEF-A2FB-27B55F868BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7DF7E1-1FD5-412D-8A5E-CC52D28976C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grating" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Dependencies" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="24">
   <si>
     <t>Duty factor</t>
   </si>
@@ -185,9 +186,6 @@
   </si>
   <si>
     <t>1D,square,phase</t>
-  </si>
-  <si>
-    <t>2.6*x*x*x</t>
   </si>
 </sst>
 </file>
@@ -7358,9 +7356,6 @@
         <f>-1/200</f>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -7379,10 +7374,6 @@
         <f>+D2</f>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E3" s="8" t="str">
-        <f>E2</f>
-        <v>2.6*x*x*x</v>
-      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
@@ -7401,10 +7392,6 @@
         <f t="shared" si="0"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E4" s="8" t="str">
-        <f t="shared" ref="E4:E67" si="1">E3</f>
-        <v>2.6*x*x*x</v>
-      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
@@ -7420,12 +7407,8 @@
         <v>0</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" ref="D5:D68" si="2">+D4</f>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E5" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" ref="D5:D68" si="1">+D4</f>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7442,12 +7425,8 @@
         <v>0</v>
       </c>
       <c r="D6" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E6" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7464,12 +7443,8 @@
         <v>0</v>
       </c>
       <c r="D7" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E7" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -7486,12 +7461,8 @@
         <v>0</v>
       </c>
       <c r="D8" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E8" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7508,12 +7479,8 @@
         <v>0</v>
       </c>
       <c r="D9" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E9" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7530,12 +7497,8 @@
         <v>0</v>
       </c>
       <c r="D10" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E10" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7552,12 +7515,8 @@
         <v>0</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E11" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -7574,12 +7533,8 @@
         <v>0</v>
       </c>
       <c r="D12" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E12" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -7596,12 +7551,8 @@
         <v>0</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E13" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -7618,12 +7569,8 @@
         <v>0</v>
       </c>
       <c r="D14" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E14" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -7640,12 +7587,8 @@
         <v>0</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E15" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -7662,15 +7605,11 @@
         <v>0</v>
       </c>
       <c r="D16" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E16" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7684,15 +7623,11 @@
         <v>0</v>
       </c>
       <c r="D17" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E17" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7706,15 +7641,11 @@
         <v>0</v>
       </c>
       <c r="D18" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E18" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7728,15 +7659,11 @@
         <v>0</v>
       </c>
       <c r="D19" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E19" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7750,15 +7677,11 @@
         <v>0</v>
       </c>
       <c r="D20" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E20" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7772,15 +7695,11 @@
         <v>0</v>
       </c>
       <c r="D21" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E21" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7794,15 +7713,11 @@
         <v>0</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E22" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7816,15 +7731,11 @@
         <v>0</v>
       </c>
       <c r="D23" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E23" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7838,15 +7749,11 @@
         <v>0</v>
       </c>
       <c r="D24" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E24" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7860,15 +7767,11 @@
         <v>0</v>
       </c>
       <c r="D25" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E25" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7882,15 +7785,11 @@
         <v>0</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E26" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7904,15 +7803,11 @@
         <v>0</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E27" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7926,15 +7821,11 @@
         <v>0</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E28" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7948,15 +7839,11 @@
         <v>0</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E29" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7970,15 +7857,11 @@
         <v>0</v>
       </c>
       <c r="D30" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E30" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -7992,15 +7875,11 @@
         <v>0</v>
       </c>
       <c r="D31" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E31" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8014,15 +7893,11 @@
         <v>0</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E32" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8036,15 +7911,11 @@
         <v>0</v>
       </c>
       <c r="D33" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E33" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8058,15 +7929,11 @@
         <v>0</v>
       </c>
       <c r="D34" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E34" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8080,15 +7947,11 @@
         <v>0</v>
       </c>
       <c r="D35" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E35" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8102,15 +7965,11 @@
         <v>0</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E36" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8124,15 +7983,11 @@
         <v>0</v>
       </c>
       <c r="D37" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E37" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8146,15 +8001,11 @@
         <v>0</v>
       </c>
       <c r="D38" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E38" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8168,15 +8019,11 @@
         <v>0</v>
       </c>
       <c r="D39" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E39" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8190,15 +8037,11 @@
         <v>0</v>
       </c>
       <c r="D40" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E40" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8212,15 +8055,11 @@
         <v>0</v>
       </c>
       <c r="D41" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E41" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8234,15 +8073,11 @@
         <v>0</v>
       </c>
       <c r="D42" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E42" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8256,15 +8091,11 @@
         <v>0</v>
       </c>
       <c r="D43" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E43" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8278,15 +8109,11 @@
         <v>0</v>
       </c>
       <c r="D44" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E44" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8300,15 +8127,11 @@
         <v>0</v>
       </c>
       <c r="D45" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E45" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8322,15 +8145,11 @@
         <v>0</v>
       </c>
       <c r="D46" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E46" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8344,15 +8163,11 @@
         <v>0</v>
       </c>
       <c r="D47" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E47" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8366,15 +8181,11 @@
         <v>0</v>
       </c>
       <c r="D48" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E48" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8388,15 +8199,11 @@
         <v>0</v>
       </c>
       <c r="D49" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E49" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8410,15 +8217,11 @@
         <v>0</v>
       </c>
       <c r="D50" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E50" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8432,15 +8235,11 @@
         <v>0</v>
       </c>
       <c r="D51" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E51" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8454,15 +8253,11 @@
         <v>0</v>
       </c>
       <c r="D52" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E52" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8476,15 +8271,11 @@
         <v>0</v>
       </c>
       <c r="D53" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E53" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8498,15 +8289,11 @@
         <v>0</v>
       </c>
       <c r="D54" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E54" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8520,15 +8307,11 @@
         <v>0</v>
       </c>
       <c r="D55" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E55" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8542,15 +8325,11 @@
         <v>0</v>
       </c>
       <c r="D56" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E56" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8564,15 +8343,11 @@
         <v>0</v>
       </c>
       <c r="D57" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E57" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8586,15 +8361,11 @@
         <v>0</v>
       </c>
       <c r="D58" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E58" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8608,15 +8379,11 @@
         <v>0</v>
       </c>
       <c r="D59" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E59" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8630,15 +8397,11 @@
         <v>0</v>
       </c>
       <c r="D60" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E60" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8652,15 +8415,11 @@
         <v>0</v>
       </c>
       <c r="D61" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E61" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8674,15 +8433,11 @@
         <v>0</v>
       </c>
       <c r="D62" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E62" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8696,15 +8451,11 @@
         <v>0</v>
       </c>
       <c r="D63" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E63" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8718,15 +8469,11 @@
         <v>0</v>
       </c>
       <c r="D64" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E64" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8740,15 +8487,11 @@
         <v>0</v>
       </c>
       <c r="D65" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E65" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <f t="shared" si="0"/>
         <v>0.5</v>
@@ -8762,2960 +8505,2420 @@
         <v>0</v>
       </c>
       <c r="D66" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E66" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
-        <f t="shared" ref="A67:D100" si="3">+A66</f>
+        <f t="shared" ref="A67:D100" si="2">+A66</f>
         <v>0.5</v>
       </c>
       <c r="B67" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C67" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D67" s="8">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B68" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C68" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D68" s="8">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B69" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C69" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D69" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B70" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C70" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D70" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B71" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C71" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D71" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B72" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C72" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D72" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B73" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C73" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D73" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B74" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C74" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D74" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B75" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C75" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D75" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B76" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C76" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D76" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B77" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C77" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D77" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B78" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C78" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D78" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B79" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C79" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D79" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B80" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C80" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D80" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B81" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C81" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D81" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B82" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C82" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D82" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B83" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C83" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D83" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B84" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C84" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D84" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B85" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C85" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D85" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B86" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C86" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D86" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B87" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C87" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D87" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B88" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C88" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D88" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B89" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C89" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D89" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B90" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C90" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D90" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B91" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C91" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D91" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B92" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C92" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D92" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B93" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C93" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D93" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B94" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C94" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D94" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B95" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C95" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D95" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B96" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C96" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D96" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B97" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C97" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D97" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B98" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C98" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D98" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B99" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C99" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D99" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="B100" s="8">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="C100" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D100" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="8">
+        <f t="shared" ref="A101:D101" si="3">+A100</f>
+        <v>0.5</v>
+      </c>
+      <c r="B101" s="8">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="C67" s="8">
+      <c r="C101" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="D67" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E67" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="8">
+      <c r="D101" s="8">
         <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B68" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C68" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D68" s="8">
-        <f t="shared" si="2"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E68" s="8" t="str">
-        <f t="shared" ref="E68:E131" si="4">E67</f>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B69" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C69" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D69" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E69" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B70" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C70" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D70" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E70" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B71" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C71" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D71" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E71" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B72" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C72" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D72" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E72" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B73" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C73" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D73" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E73" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B74" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C74" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D74" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E74" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B75" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C75" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D75" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E75" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B76" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C76" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D76" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E76" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B77" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C77" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D77" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E77" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B78" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C78" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D78" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E78" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B79" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C79" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D79" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E79" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B80" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C80" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D80" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E80" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B81" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C81" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D81" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E81" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B82" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C82" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D82" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E82" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B83" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C83" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D83" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E83" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B84" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C84" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D84" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E84" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B85" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C85" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D85" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E85" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B86" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C86" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D86" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E86" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B87" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C87" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D87" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E87" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B88" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C88" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D88" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E88" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B89" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C89" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D89" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E89" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B90" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C90" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D90" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E90" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B91" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C91" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D91" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E91" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B92" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C92" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D92" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E92" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B93" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C93" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D93" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E93" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B94" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C94" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D94" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E94" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B95" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C95" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D95" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E95" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B96" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C96" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D96" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E96" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B97" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C97" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D97" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E97" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B98" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C98" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D98" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E98" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B99" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C99" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D99" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E99" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="B100" s="8">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="C100" s="8">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="D100" s="8">
-        <f t="shared" si="3"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E100" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="8">
-        <f t="shared" ref="A101:D101" si="5">+A100</f>
-        <v>0.5</v>
-      </c>
-      <c r="B101" s="8">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="C101" s="8">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="D101" s="8">
-        <f t="shared" si="5"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E101" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
-        <f t="shared" ref="A102:D102" si="6">+A101</f>
+        <f t="shared" ref="A102:D102" si="4">+A101</f>
         <v>0.5</v>
       </c>
       <c r="B102" s="8">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="C102" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="D102" s="8">
+        <f t="shared" si="4"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="8">
+        <f t="shared" ref="A103:D103" si="5">+A102</f>
+        <v>0.5</v>
+      </c>
+      <c r="B103" s="8">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="C103" s="8">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D103" s="8">
+        <f t="shared" si="5"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="8">
+        <f t="shared" ref="A104:D104" si="6">+A103</f>
+        <v>0.5</v>
+      </c>
+      <c r="B104" s="8">
         <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
-      <c r="C102" s="8">
+      <c r="C104" s="8">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="D102" s="8">
+      <c r="D104" s="8">
         <f t="shared" si="6"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E102" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="8">
-        <f t="shared" ref="A103:D103" si="7">+A102</f>
-        <v>0.5</v>
-      </c>
-      <c r="B103" s="8">
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="8">
+        <f t="shared" ref="A105:D105" si="7">+A104</f>
+        <v>0.5</v>
+      </c>
+      <c r="B105" s="8">
         <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
-      <c r="C103" s="8">
+      <c r="C105" s="8">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="D103" s="8">
+      <c r="D105" s="8">
         <f t="shared" si="7"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E103" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="8">
-        <f t="shared" ref="A104:D104" si="8">+A103</f>
-        <v>0.5</v>
-      </c>
-      <c r="B104" s="8">
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="8">
+        <f t="shared" ref="A106:D106" si="8">+A105</f>
+        <v>0.5</v>
+      </c>
+      <c r="B106" s="8">
         <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
-      <c r="C104" s="8">
+      <c r="C106" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="D104" s="8">
+      <c r="D106" s="8">
         <f t="shared" si="8"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E104" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="8">
-        <f t="shared" ref="A105:D105" si="9">+A104</f>
-        <v>0.5</v>
-      </c>
-      <c r="B105" s="8">
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="8">
+        <f t="shared" ref="A107:D107" si="9">+A106</f>
+        <v>0.5</v>
+      </c>
+      <c r="B107" s="8">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="C105" s="8">
+      <c r="C107" s="8">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="D105" s="8">
+      <c r="D107" s="8">
         <f t="shared" si="9"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E105" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="8">
-        <f t="shared" ref="A106:D106" si="10">+A105</f>
-        <v>0.5</v>
-      </c>
-      <c r="B106" s="8">
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="8">
+        <f t="shared" ref="A108:D108" si="10">+A107</f>
+        <v>0.5</v>
+      </c>
+      <c r="B108" s="8">
         <f t="shared" si="10"/>
         <v>0.5</v>
       </c>
-      <c r="C106" s="8">
+      <c r="C108" s="8">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D108" s="8">
         <f t="shared" si="10"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E106" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="8">
-        <f t="shared" ref="A107:D107" si="11">+A106</f>
-        <v>0.5</v>
-      </c>
-      <c r="B107" s="8">
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="8">
+        <f t="shared" ref="A109:D109" si="11">+A108</f>
+        <v>0.5</v>
+      </c>
+      <c r="B109" s="8">
         <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
-      <c r="C107" s="8">
+      <c r="C109" s="8">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D109" s="8">
         <f t="shared" si="11"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E107" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="8">
-        <f t="shared" ref="A108:D108" si="12">+A107</f>
-        <v>0.5</v>
-      </c>
-      <c r="B108" s="8">
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="8">
+        <f t="shared" ref="A110:D110" si="12">+A109</f>
+        <v>0.5</v>
+      </c>
+      <c r="B110" s="8">
         <f t="shared" si="12"/>
         <v>0.5</v>
       </c>
-      <c r="C108" s="8">
+      <c r="C110" s="8">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="D108" s="8">
+      <c r="D110" s="8">
         <f t="shared" si="12"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E108" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="8">
-        <f t="shared" ref="A109:D109" si="13">+A108</f>
-        <v>0.5</v>
-      </c>
-      <c r="B109" s="8">
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="8">
+        <f t="shared" ref="A111:D111" si="13">+A110</f>
+        <v>0.5</v>
+      </c>
+      <c r="B111" s="8">
         <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
-      <c r="C109" s="8">
+      <c r="C111" s="8">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="D109" s="8">
+      <c r="D111" s="8">
         <f t="shared" si="13"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E109" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="8">
-        <f t="shared" ref="A110:D110" si="14">+A109</f>
-        <v>0.5</v>
-      </c>
-      <c r="B110" s="8">
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="8">
+        <f t="shared" ref="A112:D112" si="14">+A111</f>
+        <v>0.5</v>
+      </c>
+      <c r="B112" s="8">
         <f t="shared" si="14"/>
         <v>0.5</v>
       </c>
-      <c r="C110" s="8">
+      <c r="C112" s="8">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="D110" s="8">
+      <c r="D112" s="8">
         <f t="shared" si="14"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E110" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="8">
-        <f t="shared" ref="A111:D111" si="15">+A110</f>
-        <v>0.5</v>
-      </c>
-      <c r="B111" s="8">
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="8">
+        <f t="shared" ref="A113:D113" si="15">+A112</f>
+        <v>0.5</v>
+      </c>
+      <c r="B113" s="8">
         <f t="shared" si="15"/>
         <v>0.5</v>
       </c>
-      <c r="C111" s="8">
+      <c r="C113" s="8">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="D111" s="8">
+      <c r="D113" s="8">
         <f t="shared" si="15"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E111" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="8">
-        <f t="shared" ref="A112:D112" si="16">+A111</f>
-        <v>0.5</v>
-      </c>
-      <c r="B112" s="8">
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="8">
+        <f t="shared" ref="A114:D114" si="16">+A113</f>
+        <v>0.5</v>
+      </c>
+      <c r="B114" s="8">
         <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
-      <c r="C112" s="8">
+      <c r="C114" s="8">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="D112" s="8">
+      <c r="D114" s="8">
         <f t="shared" si="16"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E112" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="8">
-        <f t="shared" ref="A113:D113" si="17">+A112</f>
-        <v>0.5</v>
-      </c>
-      <c r="B113" s="8">
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="8">
+        <f t="shared" ref="A115:D115" si="17">+A114</f>
+        <v>0.5</v>
+      </c>
+      <c r="B115" s="8">
         <f t="shared" si="17"/>
         <v>0.5</v>
       </c>
-      <c r="C113" s="8">
+      <c r="C115" s="8">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="D113" s="8">
+      <c r="D115" s="8">
         <f t="shared" si="17"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E113" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="8">
-        <f t="shared" ref="A114:D114" si="18">+A113</f>
-        <v>0.5</v>
-      </c>
-      <c r="B114" s="8">
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="8">
+        <f t="shared" ref="A116:D116" si="18">+A115</f>
+        <v>0.5</v>
+      </c>
+      <c r="B116" s="8">
         <f t="shared" si="18"/>
         <v>0.5</v>
       </c>
-      <c r="C114" s="8">
+      <c r="C116" s="8">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="D114" s="8">
+      <c r="D116" s="8">
         <f t="shared" si="18"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E114" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="8">
-        <f t="shared" ref="A115:D115" si="19">+A114</f>
-        <v>0.5</v>
-      </c>
-      <c r="B115" s="8">
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="8">
+        <f t="shared" ref="A117:D117" si="19">+A116</f>
+        <v>0.5</v>
+      </c>
+      <c r="B117" s="8">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="C115" s="8">
+      <c r="C117" s="8">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="D115" s="8">
+      <c r="D117" s="8">
         <f t="shared" si="19"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E115" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="8">
-        <f t="shared" ref="A116:D116" si="20">+A115</f>
-        <v>0.5</v>
-      </c>
-      <c r="B116" s="8">
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="8">
+        <f t="shared" ref="A118:D118" si="20">+A117</f>
+        <v>0.5</v>
+      </c>
+      <c r="B118" s="8">
         <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
-      <c r="C116" s="8">
+      <c r="C118" s="8">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="D116" s="8">
+      <c r="D118" s="8">
         <f t="shared" si="20"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E116" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="8">
-        <f t="shared" ref="A117:D117" si="21">+A116</f>
-        <v>0.5</v>
-      </c>
-      <c r="B117" s="8">
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="8">
+        <f t="shared" ref="A119:D119" si="21">+A118</f>
+        <v>0.5</v>
+      </c>
+      <c r="B119" s="8">
         <f t="shared" si="21"/>
         <v>0.5</v>
       </c>
-      <c r="C117" s="8">
+      <c r="C119" s="8">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="D117" s="8">
+      <c r="D119" s="8">
         <f t="shared" si="21"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E117" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="8">
-        <f t="shared" ref="A118:D118" si="22">+A117</f>
-        <v>0.5</v>
-      </c>
-      <c r="B118" s="8">
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="8">
+        <f t="shared" ref="A120:D120" si="22">+A119</f>
+        <v>0.5</v>
+      </c>
+      <c r="B120" s="8">
         <f t="shared" si="22"/>
         <v>0.5</v>
       </c>
-      <c r="C118" s="8">
+      <c r="C120" s="8">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="D118" s="8">
+      <c r="D120" s="8">
         <f t="shared" si="22"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E118" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="8">
-        <f t="shared" ref="A119:D119" si="23">+A118</f>
-        <v>0.5</v>
-      </c>
-      <c r="B119" s="8">
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="8">
+        <f t="shared" ref="A121:D121" si="23">+A120</f>
+        <v>0.5</v>
+      </c>
+      <c r="B121" s="8">
         <f t="shared" si="23"/>
         <v>0.5</v>
       </c>
-      <c r="C119" s="8">
+      <c r="C121" s="8">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="D119" s="8">
+      <c r="D121" s="8">
         <f t="shared" si="23"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E119" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="8">
-        <f t="shared" ref="A120:D120" si="24">+A119</f>
-        <v>0.5</v>
-      </c>
-      <c r="B120" s="8">
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="8">
+        <f t="shared" ref="A122:D122" si="24">+A121</f>
+        <v>0.5</v>
+      </c>
+      <c r="B122" s="8">
         <f t="shared" si="24"/>
         <v>0.5</v>
       </c>
-      <c r="C120" s="8">
+      <c r="C122" s="8">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="D120" s="8">
+      <c r="D122" s="8">
         <f t="shared" si="24"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E120" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="8">
-        <f t="shared" ref="A121:D121" si="25">+A120</f>
-        <v>0.5</v>
-      </c>
-      <c r="B121" s="8">
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="8">
+        <f t="shared" ref="A123:D123" si="25">+A122</f>
+        <v>0.5</v>
+      </c>
+      <c r="B123" s="8">
         <f t="shared" si="25"/>
         <v>0.5</v>
       </c>
-      <c r="C121" s="8">
+      <c r="C123" s="8">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="D121" s="8">
+      <c r="D123" s="8">
         <f t="shared" si="25"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E121" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="8">
-        <f t="shared" ref="A122:D122" si="26">+A121</f>
-        <v>0.5</v>
-      </c>
-      <c r="B122" s="8">
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="8">
+        <f t="shared" ref="A124:D124" si="26">+A123</f>
+        <v>0.5</v>
+      </c>
+      <c r="B124" s="8">
         <f t="shared" si="26"/>
         <v>0.5</v>
       </c>
-      <c r="C122" s="8">
+      <c r="C124" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="D122" s="8">
+      <c r="D124" s="8">
         <f t="shared" si="26"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E122" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="8">
-        <f t="shared" ref="A123:D123" si="27">+A122</f>
-        <v>0.5</v>
-      </c>
-      <c r="B123" s="8">
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="8">
+        <f t="shared" ref="A125:D125" si="27">+A124</f>
+        <v>0.5</v>
+      </c>
+      <c r="B125" s="8">
         <f t="shared" si="27"/>
         <v>0.5</v>
       </c>
-      <c r="C123" s="8">
+      <c r="C125" s="8">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="D123" s="8">
+      <c r="D125" s="8">
         <f t="shared" si="27"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E123" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="8">
-        <f t="shared" ref="A124:D124" si="28">+A123</f>
-        <v>0.5</v>
-      </c>
-      <c r="B124" s="8">
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="8">
+        <f t="shared" ref="A126:D126" si="28">+A125</f>
+        <v>0.5</v>
+      </c>
+      <c r="B126" s="8">
         <f t="shared" si="28"/>
         <v>0.5</v>
       </c>
-      <c r="C124" s="8">
+      <c r="C126" s="8">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="D124" s="8">
+      <c r="D126" s="8">
         <f t="shared" si="28"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E124" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="8">
-        <f t="shared" ref="A125:D125" si="29">+A124</f>
-        <v>0.5</v>
-      </c>
-      <c r="B125" s="8">
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="8">
+        <f t="shared" ref="A127:D127" si="29">+A126</f>
+        <v>0.5</v>
+      </c>
+      <c r="B127" s="8">
         <f t="shared" si="29"/>
         <v>0.5</v>
       </c>
-      <c r="C125" s="8">
+      <c r="C127" s="8">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="D125" s="8">
+      <c r="D127" s="8">
         <f t="shared" si="29"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E125" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="8">
-        <f t="shared" ref="A126:D126" si="30">+A125</f>
-        <v>0.5</v>
-      </c>
-      <c r="B126" s="8">
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="8">
+        <f t="shared" ref="A128:D128" si="30">+A127</f>
+        <v>0.5</v>
+      </c>
+      <c r="B128" s="8">
         <f t="shared" si="30"/>
         <v>0.5</v>
       </c>
-      <c r="C126" s="8">
+      <c r="C128" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="D126" s="8">
+      <c r="D128" s="8">
         <f t="shared" si="30"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E126" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="8">
-        <f t="shared" ref="A127:D127" si="31">+A126</f>
-        <v>0.5</v>
-      </c>
-      <c r="B127" s="8">
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="8">
+        <f t="shared" ref="A129:D129" si="31">+A128</f>
+        <v>0.5</v>
+      </c>
+      <c r="B129" s="8">
         <f t="shared" si="31"/>
         <v>0.5</v>
       </c>
-      <c r="C127" s="8">
+      <c r="C129" s="8">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="D127" s="8">
+      <c r="D129" s="8">
         <f t="shared" si="31"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E127" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="8">
-        <f t="shared" ref="A128:D128" si="32">+A127</f>
-        <v>0.5</v>
-      </c>
-      <c r="B128" s="8">
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="8">
+        <f t="shared" ref="A130:D130" si="32">+A129</f>
+        <v>0.5</v>
+      </c>
+      <c r="B130" s="8">
         <f t="shared" si="32"/>
         <v>0.5</v>
       </c>
-      <c r="C128" s="8">
+      <c r="C130" s="8">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="D128" s="8">
+      <c r="D130" s="8">
         <f t="shared" si="32"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E128" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="8">
-        <f t="shared" ref="A129:D129" si="33">+A128</f>
-        <v>0.5</v>
-      </c>
-      <c r="B129" s="8">
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="8">
+        <f t="shared" ref="A131:D131" si="33">+A130</f>
+        <v>0.5</v>
+      </c>
+      <c r="B131" s="8">
         <f t="shared" si="33"/>
         <v>0.5</v>
       </c>
-      <c r="C129" s="8">
+      <c r="C131" s="8">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="D129" s="8">
+      <c r="D131" s="8">
         <f t="shared" si="33"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E129" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="8">
-        <f t="shared" ref="A130:D130" si="34">+A129</f>
-        <v>0.5</v>
-      </c>
-      <c r="B130" s="8">
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="8">
+        <f t="shared" ref="A132:D132" si="34">+A131</f>
+        <v>0.5</v>
+      </c>
+      <c r="B132" s="8">
         <f t="shared" si="34"/>
         <v>0.5</v>
       </c>
-      <c r="C130" s="8">
+      <c r="C132" s="8">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="D130" s="8">
+      <c r="D132" s="8">
         <f t="shared" si="34"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E130" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="8">
-        <f t="shared" ref="A131:D131" si="35">+A130</f>
-        <v>0.5</v>
-      </c>
-      <c r="B131" s="8">
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="8">
+        <f t="shared" ref="A133:D133" si="35">+A132</f>
+        <v>0.5</v>
+      </c>
+      <c r="B133" s="8">
         <f t="shared" si="35"/>
         <v>0.5</v>
       </c>
-      <c r="C131" s="8">
+      <c r="C133" s="8">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="D131" s="8">
+      <c r="D133" s="8">
         <f t="shared" si="35"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E131" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="8">
-        <f t="shared" ref="A132:D132" si="36">+A131</f>
-        <v>0.5</v>
-      </c>
-      <c r="B132" s="8">
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="8">
+        <f t="shared" ref="A134:D134" si="36">+A133</f>
+        <v>0.5</v>
+      </c>
+      <c r="B134" s="8">
         <f t="shared" si="36"/>
         <v>0.5</v>
       </c>
-      <c r="C132" s="8">
+      <c r="C134" s="8">
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="D132" s="8">
+      <c r="D134" s="8">
         <f t="shared" si="36"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E132" s="8" t="str">
-        <f t="shared" ref="E132:E195" si="37">E131</f>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="8">
-        <f t="shared" ref="A133:D133" si="38">+A132</f>
-        <v>0.5</v>
-      </c>
-      <c r="B133" s="8">
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="8">
+        <f t="shared" ref="A135:D135" si="37">+A134</f>
+        <v>0.5</v>
+      </c>
+      <c r="B135" s="8">
+        <f t="shared" si="37"/>
+        <v>0.5</v>
+      </c>
+      <c r="C135" s="8">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="D135" s="8">
+        <f t="shared" si="37"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="8">
+        <f t="shared" ref="A136:D136" si="38">+A135</f>
+        <v>0.5</v>
+      </c>
+      <c r="B136" s="8">
         <f t="shared" si="38"/>
         <v>0.5</v>
       </c>
-      <c r="C133" s="8">
+      <c r="C136" s="8">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="D133" s="8">
+      <c r="D136" s="8">
         <f t="shared" si="38"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E133" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="8">
-        <f t="shared" ref="A134:D134" si="39">+A133</f>
-        <v>0.5</v>
-      </c>
-      <c r="B134" s="8">
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="8">
+        <f t="shared" ref="A137:D137" si="39">+A136</f>
+        <v>0.5</v>
+      </c>
+      <c r="B137" s="8">
         <f t="shared" si="39"/>
         <v>0.5</v>
       </c>
-      <c r="C134" s="8">
+      <c r="C137" s="8">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="D134" s="8">
+      <c r="D137" s="8">
         <f t="shared" si="39"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E134" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="8">
-        <f t="shared" ref="A135:D135" si="40">+A134</f>
-        <v>0.5</v>
-      </c>
-      <c r="B135" s="8">
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="8">
+        <f t="shared" ref="A138:D138" si="40">+A137</f>
+        <v>0.5</v>
+      </c>
+      <c r="B138" s="8">
         <f t="shared" si="40"/>
         <v>0.5</v>
       </c>
-      <c r="C135" s="8">
+      <c r="C138" s="8">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="D135" s="8">
+      <c r="D138" s="8">
         <f t="shared" si="40"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E135" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="8">
-        <f t="shared" ref="A136:D136" si="41">+A135</f>
-        <v>0.5</v>
-      </c>
-      <c r="B136" s="8">
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="8">
+        <f t="shared" ref="A139:D139" si="41">+A138</f>
+        <v>0.5</v>
+      </c>
+      <c r="B139" s="8">
         <f t="shared" si="41"/>
         <v>0.5</v>
       </c>
-      <c r="C136" s="8">
+      <c r="C139" s="8">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="D136" s="8">
+      <c r="D139" s="8">
         <f t="shared" si="41"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E136" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="8">
-        <f t="shared" ref="A137:D137" si="42">+A136</f>
-        <v>0.5</v>
-      </c>
-      <c r="B137" s="8">
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="8">
+        <f t="shared" ref="A140:D140" si="42">+A139</f>
+        <v>0.5</v>
+      </c>
+      <c r="B140" s="8">
         <f t="shared" si="42"/>
         <v>0.5</v>
       </c>
-      <c r="C137" s="8">
+      <c r="C140" s="8">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="D137" s="8">
+      <c r="D140" s="8">
         <f t="shared" si="42"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E137" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="8">
-        <f t="shared" ref="A138:D138" si="43">+A137</f>
-        <v>0.5</v>
-      </c>
-      <c r="B138" s="8">
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="8">
+        <f t="shared" ref="A141:D141" si="43">+A140</f>
+        <v>0.5</v>
+      </c>
+      <c r="B141" s="8">
         <f t="shared" si="43"/>
         <v>0.5</v>
       </c>
-      <c r="C138" s="8">
+      <c r="C141" s="8">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="D138" s="8">
+      <c r="D141" s="8">
         <f t="shared" si="43"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E138" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="8">
-        <f t="shared" ref="A139:D139" si="44">+A138</f>
-        <v>0.5</v>
-      </c>
-      <c r="B139" s="8">
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="8">
+        <f t="shared" ref="A142:D142" si="44">+A141</f>
+        <v>0.5</v>
+      </c>
+      <c r="B142" s="8">
         <f t="shared" si="44"/>
         <v>0.5</v>
       </c>
-      <c r="C139" s="8">
+      <c r="C142" s="8">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="D139" s="8">
+      <c r="D142" s="8">
         <f t="shared" si="44"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E139" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="8">
-        <f t="shared" ref="A140:D140" si="45">+A139</f>
-        <v>0.5</v>
-      </c>
-      <c r="B140" s="8">
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="8">
+        <f t="shared" ref="A143:D143" si="45">+A142</f>
+        <v>0.5</v>
+      </c>
+      <c r="B143" s="8">
         <f t="shared" si="45"/>
         <v>0.5</v>
       </c>
-      <c r="C140" s="8">
+      <c r="C143" s="8">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="D140" s="8">
+      <c r="D143" s="8">
         <f t="shared" si="45"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E140" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="8">
-        <f t="shared" ref="A141:D141" si="46">+A140</f>
-        <v>0.5</v>
-      </c>
-      <c r="B141" s="8">
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="8">
+        <f t="shared" ref="A144:D144" si="46">+A143</f>
+        <v>0.5</v>
+      </c>
+      <c r="B144" s="8">
         <f t="shared" si="46"/>
         <v>0.5</v>
       </c>
-      <c r="C141" s="8">
+      <c r="C144" s="8">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="D141" s="8">
+      <c r="D144" s="8">
         <f t="shared" si="46"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E141" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="8">
-        <f t="shared" ref="A142:D142" si="47">+A141</f>
-        <v>0.5</v>
-      </c>
-      <c r="B142" s="8">
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="8">
+        <f t="shared" ref="A145:D145" si="47">+A144</f>
+        <v>0.5</v>
+      </c>
+      <c r="B145" s="8">
         <f t="shared" si="47"/>
         <v>0.5</v>
       </c>
-      <c r="C142" s="8">
+      <c r="C145" s="8">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
-      <c r="D142" s="8">
+      <c r="D145" s="8">
         <f t="shared" si="47"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E142" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="8">
-        <f t="shared" ref="A143:D143" si="48">+A142</f>
-        <v>0.5</v>
-      </c>
-      <c r="B143" s="8">
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="8">
+        <f t="shared" ref="A146:D146" si="48">+A145</f>
+        <v>0.5</v>
+      </c>
+      <c r="B146" s="8">
         <f t="shared" si="48"/>
         <v>0.5</v>
       </c>
-      <c r="C143" s="8">
+      <c r="C146" s="8">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="D143" s="8">
+      <c r="D146" s="8">
         <f t="shared" si="48"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E143" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="8">
-        <f t="shared" ref="A144:D144" si="49">+A143</f>
-        <v>0.5</v>
-      </c>
-      <c r="B144" s="8">
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="8">
+        <f t="shared" ref="A147:D147" si="49">+A146</f>
+        <v>0.5</v>
+      </c>
+      <c r="B147" s="8">
         <f t="shared" si="49"/>
         <v>0.5</v>
       </c>
-      <c r="C144" s="8">
+      <c r="C147" s="8">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="D144" s="8">
+      <c r="D147" s="8">
         <f t="shared" si="49"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E144" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="8">
-        <f t="shared" ref="A145:D145" si="50">+A144</f>
-        <v>0.5</v>
-      </c>
-      <c r="B145" s="8">
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="8">
+        <f t="shared" ref="A148:D148" si="50">+A147</f>
+        <v>0.5</v>
+      </c>
+      <c r="B148" s="8">
         <f t="shared" si="50"/>
         <v>0.5</v>
       </c>
-      <c r="C145" s="8">
+      <c r="C148" s="8">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="D145" s="8">
+      <c r="D148" s="8">
         <f t="shared" si="50"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E145" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="8">
-        <f t="shared" ref="A146:D146" si="51">+A145</f>
-        <v>0.5</v>
-      </c>
-      <c r="B146" s="8">
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="8">
+        <f t="shared" ref="A149:D149" si="51">+A148</f>
+        <v>0.5</v>
+      </c>
+      <c r="B149" s="8">
         <f t="shared" si="51"/>
         <v>0.5</v>
       </c>
-      <c r="C146" s="8">
+      <c r="C149" s="8">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="D146" s="8">
+      <c r="D149" s="8">
         <f t="shared" si="51"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E146" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="8">
-        <f t="shared" ref="A147:D147" si="52">+A146</f>
-        <v>0.5</v>
-      </c>
-      <c r="B147" s="8">
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="8">
+        <f t="shared" ref="A150:D150" si="52">+A149</f>
+        <v>0.5</v>
+      </c>
+      <c r="B150" s="8">
         <f t="shared" si="52"/>
         <v>0.5</v>
       </c>
-      <c r="C147" s="8">
+      <c r="C150" s="8">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="D147" s="8">
+      <c r="D150" s="8">
         <f t="shared" si="52"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E147" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="8">
-        <f t="shared" ref="A148:D148" si="53">+A147</f>
-        <v>0.5</v>
-      </c>
-      <c r="B148" s="8">
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="8">
+        <f t="shared" ref="A151:D151" si="53">+A150</f>
+        <v>0.5</v>
+      </c>
+      <c r="B151" s="8">
         <f t="shared" si="53"/>
         <v>0.5</v>
       </c>
-      <c r="C148" s="8">
+      <c r="C151" s="8">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="D148" s="8">
+      <c r="D151" s="8">
         <f t="shared" si="53"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E148" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="8">
-        <f t="shared" ref="A149:D149" si="54">+A148</f>
-        <v>0.5</v>
-      </c>
-      <c r="B149" s="8">
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="8">
+        <f t="shared" ref="A152:D152" si="54">+A151</f>
+        <v>0.5</v>
+      </c>
+      <c r="B152" s="8">
         <f t="shared" si="54"/>
         <v>0.5</v>
       </c>
-      <c r="C149" s="8">
+      <c r="C152" s="8">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="D149" s="8">
+      <c r="D152" s="8">
         <f t="shared" si="54"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E149" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="8">
-        <f t="shared" ref="A150:D150" si="55">+A149</f>
-        <v>0.5</v>
-      </c>
-      <c r="B150" s="8">
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="8">
+        <f t="shared" ref="A153:D153" si="55">+A152</f>
+        <v>0.5</v>
+      </c>
+      <c r="B153" s="8">
         <f t="shared" si="55"/>
         <v>0.5</v>
       </c>
-      <c r="C150" s="8">
+      <c r="C153" s="8">
         <f t="shared" si="55"/>
         <v>0</v>
       </c>
-      <c r="D150" s="8">
+      <c r="D153" s="8">
         <f t="shared" si="55"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E150" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="8">
-        <f t="shared" ref="A151:D151" si="56">+A150</f>
-        <v>0.5</v>
-      </c>
-      <c r="B151" s="8">
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="8">
+        <f t="shared" ref="A154:D154" si="56">+A153</f>
+        <v>0.5</v>
+      </c>
+      <c r="B154" s="8">
         <f t="shared" si="56"/>
         <v>0.5</v>
       </c>
-      <c r="C151" s="8">
+      <c r="C154" s="8">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="D151" s="8">
+      <c r="D154" s="8">
         <f t="shared" si="56"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E151" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="8">
-        <f t="shared" ref="A152:D152" si="57">+A151</f>
-        <v>0.5</v>
-      </c>
-      <c r="B152" s="8">
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="8">
+        <f t="shared" ref="A155:D155" si="57">+A154</f>
+        <v>0.5</v>
+      </c>
+      <c r="B155" s="8">
         <f t="shared" si="57"/>
         <v>0.5</v>
       </c>
-      <c r="C152" s="8">
+      <c r="C155" s="8">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="D152" s="8">
+      <c r="D155" s="8">
         <f t="shared" si="57"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E152" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="8">
-        <f t="shared" ref="A153:D153" si="58">+A152</f>
-        <v>0.5</v>
-      </c>
-      <c r="B153" s="8">
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="8">
+        <f t="shared" ref="A156:D156" si="58">+A155</f>
+        <v>0.5</v>
+      </c>
+      <c r="B156" s="8">
         <f t="shared" si="58"/>
         <v>0.5</v>
       </c>
-      <c r="C153" s="8">
+      <c r="C156" s="8">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="D153" s="8">
+      <c r="D156" s="8">
         <f t="shared" si="58"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E153" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="8">
-        <f t="shared" ref="A154:D154" si="59">+A153</f>
-        <v>0.5</v>
-      </c>
-      <c r="B154" s="8">
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="8">
+        <f t="shared" ref="A157:D157" si="59">+A156</f>
+        <v>0.5</v>
+      </c>
+      <c r="B157" s="8">
         <f t="shared" si="59"/>
         <v>0.5</v>
       </c>
-      <c r="C154" s="8">
+      <c r="C157" s="8">
         <f t="shared" si="59"/>
         <v>0</v>
       </c>
-      <c r="D154" s="8">
+      <c r="D157" s="8">
         <f t="shared" si="59"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E154" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="8">
-        <f t="shared" ref="A155:D155" si="60">+A154</f>
-        <v>0.5</v>
-      </c>
-      <c r="B155" s="8">
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="8">
+        <f t="shared" ref="A158:D158" si="60">+A157</f>
+        <v>0.5</v>
+      </c>
+      <c r="B158" s="8">
         <f t="shared" si="60"/>
         <v>0.5</v>
       </c>
-      <c r="C155" s="8">
+      <c r="C158" s="8">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
-      <c r="D155" s="8">
+      <c r="D158" s="8">
         <f t="shared" si="60"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E155" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="8">
-        <f t="shared" ref="A156:D156" si="61">+A155</f>
-        <v>0.5</v>
-      </c>
-      <c r="B156" s="8">
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" s="8">
+        <f t="shared" ref="A159:D159" si="61">+A158</f>
+        <v>0.5</v>
+      </c>
+      <c r="B159" s="8">
         <f t="shared" si="61"/>
         <v>0.5</v>
       </c>
-      <c r="C156" s="8">
+      <c r="C159" s="8">
         <f t="shared" si="61"/>
         <v>0</v>
       </c>
-      <c r="D156" s="8">
+      <c r="D159" s="8">
         <f t="shared" si="61"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E156" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="8">
-        <f t="shared" ref="A157:D157" si="62">+A156</f>
-        <v>0.5</v>
-      </c>
-      <c r="B157" s="8">
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="8">
+        <f t="shared" ref="A160:D160" si="62">+A159</f>
+        <v>0.5</v>
+      </c>
+      <c r="B160" s="8">
         <f t="shared" si="62"/>
         <v>0.5</v>
       </c>
-      <c r="C157" s="8">
+      <c r="C160" s="8">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
-      <c r="D157" s="8">
+      <c r="D160" s="8">
         <f t="shared" si="62"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E157" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="8">
-        <f t="shared" ref="A158:D158" si="63">+A157</f>
-        <v>0.5</v>
-      </c>
-      <c r="B158" s="8">
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" s="8">
+        <f t="shared" ref="A161:D161" si="63">+A160</f>
+        <v>0.5</v>
+      </c>
+      <c r="B161" s="8">
         <f t="shared" si="63"/>
         <v>0.5</v>
       </c>
-      <c r="C158" s="8">
+      <c r="C161" s="8">
         <f t="shared" si="63"/>
         <v>0</v>
       </c>
-      <c r="D158" s="8">
+      <c r="D161" s="8">
         <f t="shared" si="63"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E158" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="8">
-        <f t="shared" ref="A159:D159" si="64">+A158</f>
-        <v>0.5</v>
-      </c>
-      <c r="B159" s="8">
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" s="8">
+        <f t="shared" ref="A162:D162" si="64">+A161</f>
+        <v>0.5</v>
+      </c>
+      <c r="B162" s="8">
         <f t="shared" si="64"/>
         <v>0.5</v>
       </c>
-      <c r="C159" s="8">
+      <c r="C162" s="8">
         <f t="shared" si="64"/>
         <v>0</v>
       </c>
-      <c r="D159" s="8">
+      <c r="D162" s="8">
         <f t="shared" si="64"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E159" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="8">
-        <f t="shared" ref="A160:D160" si="65">+A159</f>
-        <v>0.5</v>
-      </c>
-      <c r="B160" s="8">
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" s="8">
+        <f t="shared" ref="A163:D163" si="65">+A162</f>
+        <v>0.5</v>
+      </c>
+      <c r="B163" s="8">
         <f t="shared" si="65"/>
         <v>0.5</v>
       </c>
-      <c r="C160" s="8">
+      <c r="C163" s="8">
         <f t="shared" si="65"/>
         <v>0</v>
       </c>
-      <c r="D160" s="8">
+      <c r="D163" s="8">
         <f t="shared" si="65"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E160" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="8">
-        <f t="shared" ref="A161:D161" si="66">+A160</f>
-        <v>0.5</v>
-      </c>
-      <c r="B161" s="8">
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" s="8">
+        <f t="shared" ref="A164:D164" si="66">+A163</f>
+        <v>0.5</v>
+      </c>
+      <c r="B164" s="8">
         <f t="shared" si="66"/>
         <v>0.5</v>
       </c>
-      <c r="C161" s="8">
+      <c r="C164" s="8">
         <f t="shared" si="66"/>
         <v>0</v>
       </c>
-      <c r="D161" s="8">
+      <c r="D164" s="8">
         <f t="shared" si="66"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E161" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="8">
-        <f t="shared" ref="A162:D162" si="67">+A161</f>
-        <v>0.5</v>
-      </c>
-      <c r="B162" s="8">
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" s="8">
+        <f t="shared" ref="A165:D165" si="67">+A164</f>
+        <v>0.5</v>
+      </c>
+      <c r="B165" s="8">
         <f t="shared" si="67"/>
         <v>0.5</v>
       </c>
-      <c r="C162" s="8">
+      <c r="C165" s="8">
         <f t="shared" si="67"/>
         <v>0</v>
       </c>
-      <c r="D162" s="8">
+      <c r="D165" s="8">
         <f t="shared" si="67"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E162" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="8">
-        <f t="shared" ref="A163:D163" si="68">+A162</f>
-        <v>0.5</v>
-      </c>
-      <c r="B163" s="8">
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" s="8">
+        <f t="shared" ref="A166:D166" si="68">+A165</f>
+        <v>0.5</v>
+      </c>
+      <c r="B166" s="8">
         <f t="shared" si="68"/>
         <v>0.5</v>
       </c>
-      <c r="C163" s="8">
+      <c r="C166" s="8">
         <f t="shared" si="68"/>
         <v>0</v>
       </c>
-      <c r="D163" s="8">
+      <c r="D166" s="8">
         <f t="shared" si="68"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E163" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="8">
-        <f t="shared" ref="A164:D164" si="69">+A163</f>
-        <v>0.5</v>
-      </c>
-      <c r="B164" s="8">
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" s="8">
+        <f t="shared" ref="A167:D167" si="69">+A166</f>
+        <v>0.5</v>
+      </c>
+      <c r="B167" s="8">
         <f t="shared" si="69"/>
         <v>0.5</v>
       </c>
-      <c r="C164" s="8">
+      <c r="C167" s="8">
         <f t="shared" si="69"/>
         <v>0</v>
       </c>
-      <c r="D164" s="8">
+      <c r="D167" s="8">
         <f t="shared" si="69"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E164" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="8">
-        <f t="shared" ref="A165:D165" si="70">+A164</f>
-        <v>0.5</v>
-      </c>
-      <c r="B165" s="8">
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" s="8">
+        <f t="shared" ref="A168:D168" si="70">+A167</f>
+        <v>0.5</v>
+      </c>
+      <c r="B168" s="8">
         <f t="shared" si="70"/>
         <v>0.5</v>
       </c>
-      <c r="C165" s="8">
+      <c r="C168" s="8">
         <f t="shared" si="70"/>
         <v>0</v>
       </c>
-      <c r="D165" s="8">
+      <c r="D168" s="8">
         <f t="shared" si="70"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E165" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="8">
-        <f t="shared" ref="A166:D166" si="71">+A165</f>
-        <v>0.5</v>
-      </c>
-      <c r="B166" s="8">
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" s="8">
+        <f t="shared" ref="A169:D169" si="71">+A168</f>
+        <v>0.5</v>
+      </c>
+      <c r="B169" s="8">
         <f t="shared" si="71"/>
         <v>0.5</v>
       </c>
-      <c r="C166" s="8">
+      <c r="C169" s="8">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="D166" s="8">
+      <c r="D169" s="8">
         <f t="shared" si="71"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E166" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="8">
-        <f t="shared" ref="A167:D167" si="72">+A166</f>
-        <v>0.5</v>
-      </c>
-      <c r="B167" s="8">
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" s="8">
+        <f t="shared" ref="A170:D170" si="72">+A169</f>
+        <v>0.5</v>
+      </c>
+      <c r="B170" s="8">
         <f t="shared" si="72"/>
         <v>0.5</v>
       </c>
-      <c r="C167" s="8">
+      <c r="C170" s="8">
         <f t="shared" si="72"/>
         <v>0</v>
       </c>
-      <c r="D167" s="8">
+      <c r="D170" s="8">
         <f t="shared" si="72"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E167" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="8">
-        <f t="shared" ref="A168:D168" si="73">+A167</f>
-        <v>0.5</v>
-      </c>
-      <c r="B168" s="8">
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" s="8">
+        <f t="shared" ref="A171:D171" si="73">+A170</f>
+        <v>0.5</v>
+      </c>
+      <c r="B171" s="8">
         <f t="shared" si="73"/>
         <v>0.5</v>
       </c>
-      <c r="C168" s="8">
+      <c r="C171" s="8">
         <f t="shared" si="73"/>
         <v>0</v>
       </c>
-      <c r="D168" s="8">
+      <c r="D171" s="8">
         <f t="shared" si="73"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E168" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="8">
-        <f t="shared" ref="A169:D169" si="74">+A168</f>
-        <v>0.5</v>
-      </c>
-      <c r="B169" s="8">
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" s="8">
+        <f t="shared" ref="A172:D172" si="74">+A171</f>
+        <v>0.5</v>
+      </c>
+      <c r="B172" s="8">
         <f t="shared" si="74"/>
         <v>0.5</v>
       </c>
-      <c r="C169" s="8">
+      <c r="C172" s="8">
         <f t="shared" si="74"/>
         <v>0</v>
       </c>
-      <c r="D169" s="8">
+      <c r="D172" s="8">
         <f t="shared" si="74"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E169" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="8">
-        <f t="shared" ref="A170:D170" si="75">+A169</f>
-        <v>0.5</v>
-      </c>
-      <c r="B170" s="8">
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" s="8">
+        <f t="shared" ref="A173:D173" si="75">+A172</f>
+        <v>0.5</v>
+      </c>
+      <c r="B173" s="8">
         <f t="shared" si="75"/>
         <v>0.5</v>
       </c>
-      <c r="C170" s="8">
+      <c r="C173" s="8">
         <f t="shared" si="75"/>
         <v>0</v>
       </c>
-      <c r="D170" s="8">
+      <c r="D173" s="8">
         <f t="shared" si="75"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E170" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="8">
-        <f t="shared" ref="A171:D171" si="76">+A170</f>
-        <v>0.5</v>
-      </c>
-      <c r="B171" s="8">
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" s="8">
+        <f t="shared" ref="A174:D174" si="76">+A173</f>
+        <v>0.5</v>
+      </c>
+      <c r="B174" s="8">
         <f t="shared" si="76"/>
         <v>0.5</v>
       </c>
-      <c r="C171" s="8">
+      <c r="C174" s="8">
         <f t="shared" si="76"/>
         <v>0</v>
       </c>
-      <c r="D171" s="8">
+      <c r="D174" s="8">
         <f t="shared" si="76"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E171" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="8">
-        <f t="shared" ref="A172:D172" si="77">+A171</f>
-        <v>0.5</v>
-      </c>
-      <c r="B172" s="8">
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" s="8">
+        <f t="shared" ref="A175:D175" si="77">+A174</f>
+        <v>0.5</v>
+      </c>
+      <c r="B175" s="8">
         <f t="shared" si="77"/>
         <v>0.5</v>
       </c>
-      <c r="C172" s="8">
+      <c r="C175" s="8">
         <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="D172" s="8">
+      <c r="D175" s="8">
         <f t="shared" si="77"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E172" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="8">
-        <f t="shared" ref="A173:D173" si="78">+A172</f>
-        <v>0.5</v>
-      </c>
-      <c r="B173" s="8">
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="8">
+        <f t="shared" ref="A176:D176" si="78">+A175</f>
+        <v>0.5</v>
+      </c>
+      <c r="B176" s="8">
         <f t="shared" si="78"/>
         <v>0.5</v>
       </c>
-      <c r="C173" s="8">
+      <c r="C176" s="8">
         <f t="shared" si="78"/>
         <v>0</v>
       </c>
-      <c r="D173" s="8">
+      <c r="D176" s="8">
         <f t="shared" si="78"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E173" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="8">
-        <f t="shared" ref="A174:D174" si="79">+A173</f>
-        <v>0.5</v>
-      </c>
-      <c r="B174" s="8">
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="8">
+        <f t="shared" ref="A177:D177" si="79">+A176</f>
+        <v>0.5</v>
+      </c>
+      <c r="B177" s="8">
         <f t="shared" si="79"/>
         <v>0.5</v>
       </c>
-      <c r="C174" s="8">
+      <c r="C177" s="8">
         <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="D174" s="8">
+      <c r="D177" s="8">
         <f t="shared" si="79"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E174" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="8">
-        <f t="shared" ref="A175:D175" si="80">+A174</f>
-        <v>0.5</v>
-      </c>
-      <c r="B175" s="8">
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" s="8">
+        <f t="shared" ref="A178:D178" si="80">+A177</f>
+        <v>0.5</v>
+      </c>
+      <c r="B178" s="8">
         <f t="shared" si="80"/>
         <v>0.5</v>
       </c>
-      <c r="C175" s="8">
+      <c r="C178" s="8">
         <f t="shared" si="80"/>
         <v>0</v>
       </c>
-      <c r="D175" s="8">
+      <c r="D178" s="8">
         <f t="shared" si="80"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E175" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="8">
-        <f t="shared" ref="A176:D176" si="81">+A175</f>
-        <v>0.5</v>
-      </c>
-      <c r="B176" s="8">
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" s="8">
+        <f t="shared" ref="A179:D179" si="81">+A178</f>
+        <v>0.5</v>
+      </c>
+      <c r="B179" s="8">
         <f t="shared" si="81"/>
         <v>0.5</v>
       </c>
-      <c r="C176" s="8">
+      <c r="C179" s="8">
         <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="D176" s="8">
+      <c r="D179" s="8">
         <f t="shared" si="81"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E176" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" s="8">
-        <f t="shared" ref="A177:D177" si="82">+A176</f>
-        <v>0.5</v>
-      </c>
-      <c r="B177" s="8">
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" s="8">
+        <f t="shared" ref="A180:D180" si="82">+A179</f>
+        <v>0.5</v>
+      </c>
+      <c r="B180" s="8">
         <f t="shared" si="82"/>
         <v>0.5</v>
       </c>
-      <c r="C177" s="8">
+      <c r="C180" s="8">
         <f t="shared" si="82"/>
         <v>0</v>
       </c>
-      <c r="D177" s="8">
+      <c r="D180" s="8">
         <f t="shared" si="82"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E177" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" s="8">
-        <f t="shared" ref="A178:D178" si="83">+A177</f>
-        <v>0.5</v>
-      </c>
-      <c r="B178" s="8">
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" s="8">
+        <f t="shared" ref="A181:D181" si="83">+A180</f>
+        <v>0.5</v>
+      </c>
+      <c r="B181" s="8">
         <f t="shared" si="83"/>
         <v>0.5</v>
       </c>
-      <c r="C178" s="8">
+      <c r="C181" s="8">
         <f t="shared" si="83"/>
         <v>0</v>
       </c>
-      <c r="D178" s="8">
+      <c r="D181" s="8">
         <f t="shared" si="83"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E178" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" s="8">
-        <f t="shared" ref="A179:D179" si="84">+A178</f>
-        <v>0.5</v>
-      </c>
-      <c r="B179" s="8">
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="8">
+        <f t="shared" ref="A182:D182" si="84">+A181</f>
+        <v>0.5</v>
+      </c>
+      <c r="B182" s="8">
         <f t="shared" si="84"/>
         <v>0.5</v>
       </c>
-      <c r="C179" s="8">
+      <c r="C182" s="8">
         <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="D179" s="8">
+      <c r="D182" s="8">
         <f t="shared" si="84"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E179" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="8">
-        <f t="shared" ref="A180:D180" si="85">+A179</f>
-        <v>0.5</v>
-      </c>
-      <c r="B180" s="8">
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="8">
+        <f t="shared" ref="A183:D183" si="85">+A182</f>
+        <v>0.5</v>
+      </c>
+      <c r="B183" s="8">
         <f t="shared" si="85"/>
         <v>0.5</v>
       </c>
-      <c r="C180" s="8">
+      <c r="C183" s="8">
         <f t="shared" si="85"/>
         <v>0</v>
       </c>
-      <c r="D180" s="8">
+      <c r="D183" s="8">
         <f t="shared" si="85"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E180" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" s="8">
-        <f t="shared" ref="A181:D181" si="86">+A180</f>
-        <v>0.5</v>
-      </c>
-      <c r="B181" s="8">
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="8">
+        <f t="shared" ref="A184:D184" si="86">+A183</f>
+        <v>0.5</v>
+      </c>
+      <c r="B184" s="8">
         <f t="shared" si="86"/>
         <v>0.5</v>
       </c>
-      <c r="C181" s="8">
+      <c r="C184" s="8">
         <f t="shared" si="86"/>
         <v>0</v>
       </c>
-      <c r="D181" s="8">
+      <c r="D184" s="8">
         <f t="shared" si="86"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E181" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" s="8">
-        <f t="shared" ref="A182:D182" si="87">+A181</f>
-        <v>0.5</v>
-      </c>
-      <c r="B182" s="8">
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="8">
+        <f t="shared" ref="A185:D185" si="87">+A184</f>
+        <v>0.5</v>
+      </c>
+      <c r="B185" s="8">
         <f t="shared" si="87"/>
         <v>0.5</v>
       </c>
-      <c r="C182" s="8">
+      <c r="C185" s="8">
         <f t="shared" si="87"/>
         <v>0</v>
       </c>
-      <c r="D182" s="8">
+      <c r="D185" s="8">
         <f t="shared" si="87"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E182" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183" s="8">
-        <f t="shared" ref="A183:D183" si="88">+A182</f>
-        <v>0.5</v>
-      </c>
-      <c r="B183" s="8">
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="8">
+        <f t="shared" ref="A186:D186" si="88">+A185</f>
+        <v>0.5</v>
+      </c>
+      <c r="B186" s="8">
         <f t="shared" si="88"/>
         <v>0.5</v>
       </c>
-      <c r="C183" s="8">
+      <c r="C186" s="8">
         <f t="shared" si="88"/>
         <v>0</v>
       </c>
-      <c r="D183" s="8">
+      <c r="D186" s="8">
         <f t="shared" si="88"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E183" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" s="8">
-        <f t="shared" ref="A184:D184" si="89">+A183</f>
-        <v>0.5</v>
-      </c>
-      <c r="B184" s="8">
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="8">
+        <f t="shared" ref="A187:D187" si="89">+A186</f>
+        <v>0.5</v>
+      </c>
+      <c r="B187" s="8">
         <f t="shared" si="89"/>
         <v>0.5</v>
       </c>
-      <c r="C184" s="8">
+      <c r="C187" s="8">
         <f t="shared" si="89"/>
         <v>0</v>
       </c>
-      <c r="D184" s="8">
+      <c r="D187" s="8">
         <f t="shared" si="89"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E184" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" s="8">
-        <f t="shared" ref="A185:D185" si="90">+A184</f>
-        <v>0.5</v>
-      </c>
-      <c r="B185" s="8">
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="8">
+        <f t="shared" ref="A188:D188" si="90">+A187</f>
+        <v>0.5</v>
+      </c>
+      <c r="B188" s="8">
         <f t="shared" si="90"/>
         <v>0.5</v>
       </c>
-      <c r="C185" s="8">
+      <c r="C188" s="8">
         <f t="shared" si="90"/>
         <v>0</v>
       </c>
-      <c r="D185" s="8">
+      <c r="D188" s="8">
         <f t="shared" si="90"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E185" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="8">
-        <f t="shared" ref="A186:D186" si="91">+A185</f>
-        <v>0.5</v>
-      </c>
-      <c r="B186" s="8">
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="8">
+        <f t="shared" ref="A189:D189" si="91">+A188</f>
+        <v>0.5</v>
+      </c>
+      <c r="B189" s="8">
         <f t="shared" si="91"/>
         <v>0.5</v>
       </c>
-      <c r="C186" s="8">
+      <c r="C189" s="8">
         <f t="shared" si="91"/>
         <v>0</v>
       </c>
-      <c r="D186" s="8">
+      <c r="D189" s="8">
         <f t="shared" si="91"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E186" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="8">
-        <f t="shared" ref="A187:D187" si="92">+A186</f>
-        <v>0.5</v>
-      </c>
-      <c r="B187" s="8">
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="8">
+        <f t="shared" ref="A190:D190" si="92">+A189</f>
+        <v>0.5</v>
+      </c>
+      <c r="B190" s="8">
         <f t="shared" si="92"/>
         <v>0.5</v>
       </c>
-      <c r="C187" s="8">
+      <c r="C190" s="8">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="D187" s="8">
+      <c r="D190" s="8">
         <f t="shared" si="92"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E187" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="8">
-        <f t="shared" ref="A188:D188" si="93">+A187</f>
-        <v>0.5</v>
-      </c>
-      <c r="B188" s="8">
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="8">
+        <f t="shared" ref="A191:D191" si="93">+A190</f>
+        <v>0.5</v>
+      </c>
+      <c r="B191" s="8">
         <f t="shared" si="93"/>
         <v>0.5</v>
       </c>
-      <c r="C188" s="8">
+      <c r="C191" s="8">
         <f t="shared" si="93"/>
         <v>0</v>
       </c>
-      <c r="D188" s="8">
+      <c r="D191" s="8">
         <f t="shared" si="93"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E188" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="8">
-        <f t="shared" ref="A189:D189" si="94">+A188</f>
-        <v>0.5</v>
-      </c>
-      <c r="B189" s="8">
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="8">
+        <f t="shared" ref="A192:D192" si="94">+A191</f>
+        <v>0.5</v>
+      </c>
+      <c r="B192" s="8">
         <f t="shared" si="94"/>
         <v>0.5</v>
       </c>
-      <c r="C189" s="8">
+      <c r="C192" s="8">
         <f t="shared" si="94"/>
         <v>0</v>
       </c>
-      <c r="D189" s="8">
+      <c r="D192" s="8">
         <f t="shared" si="94"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E189" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="8">
-        <f t="shared" ref="A190:D190" si="95">+A189</f>
-        <v>0.5</v>
-      </c>
-      <c r="B190" s="8">
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="8">
+        <f t="shared" ref="A193:D193" si="95">+A192</f>
+        <v>0.5</v>
+      </c>
+      <c r="B193" s="8">
         <f t="shared" si="95"/>
         <v>0.5</v>
       </c>
-      <c r="C190" s="8">
+      <c r="C193" s="8">
         <f t="shared" si="95"/>
         <v>0</v>
       </c>
-      <c r="D190" s="8">
+      <c r="D193" s="8">
         <f t="shared" si="95"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E190" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="8">
-        <f t="shared" ref="A191:D191" si="96">+A190</f>
-        <v>0.5</v>
-      </c>
-      <c r="B191" s="8">
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="8">
+        <f t="shared" ref="A194:D194" si="96">+A193</f>
+        <v>0.5</v>
+      </c>
+      <c r="B194" s="8">
         <f t="shared" si="96"/>
         <v>0.5</v>
       </c>
-      <c r="C191" s="8">
+      <c r="C194" s="8">
         <f t="shared" si="96"/>
         <v>0</v>
       </c>
-      <c r="D191" s="8">
+      <c r="D194" s="8">
         <f t="shared" si="96"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E191" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" s="8">
-        <f t="shared" ref="A192:D192" si="97">+A191</f>
-        <v>0.5</v>
-      </c>
-      <c r="B192" s="8">
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="8">
+        <f t="shared" ref="A195:D195" si="97">+A194</f>
+        <v>0.5</v>
+      </c>
+      <c r="B195" s="8">
         <f t="shared" si="97"/>
         <v>0.5</v>
       </c>
-      <c r="C192" s="8">
+      <c r="C195" s="8">
         <f t="shared" si="97"/>
         <v>0</v>
       </c>
-      <c r="D192" s="8">
+      <c r="D195" s="8">
         <f t="shared" si="97"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E192" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A193" s="8">
-        <f t="shared" ref="A193:D193" si="98">+A192</f>
-        <v>0.5</v>
-      </c>
-      <c r="B193" s="8">
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="8">
+        <f t="shared" ref="A196:D196" si="98">+A195</f>
+        <v>0.5</v>
+      </c>
+      <c r="B196" s="8">
         <f t="shared" si="98"/>
         <v>0.5</v>
       </c>
-      <c r="C193" s="8">
+      <c r="C196" s="8">
         <f t="shared" si="98"/>
         <v>0</v>
       </c>
-      <c r="D193" s="8">
+      <c r="D196" s="8">
         <f t="shared" si="98"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E193" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A194" s="8">
-        <f t="shared" ref="A194:D194" si="99">+A193</f>
-        <v>0.5</v>
-      </c>
-      <c r="B194" s="8">
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="8">
+        <f t="shared" ref="A197:D197" si="99">+A196</f>
+        <v>0.5</v>
+      </c>
+      <c r="B197" s="8">
         <f t="shared" si="99"/>
         <v>0.5</v>
       </c>
-      <c r="C194" s="8">
+      <c r="C197" s="8">
         <f t="shared" si="99"/>
         <v>0</v>
       </c>
-      <c r="D194" s="8">
+      <c r="D197" s="8">
         <f t="shared" si="99"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E194" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A195" s="8">
-        <f t="shared" ref="A195:D195" si="100">+A194</f>
-        <v>0.5</v>
-      </c>
-      <c r="B195" s="8">
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="8">
+        <f t="shared" ref="A198:D198" si="100">+A197</f>
+        <v>0.5</v>
+      </c>
+      <c r="B198" s="8">
         <f t="shared" si="100"/>
         <v>0.5</v>
       </c>
-      <c r="C195" s="8">
+      <c r="C198" s="8">
         <f t="shared" si="100"/>
         <v>0</v>
       </c>
-      <c r="D195" s="8">
+      <c r="D198" s="8">
         <f t="shared" si="100"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E195" s="8" t="str">
-        <f t="shared" si="37"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A196" s="8">
-        <f t="shared" ref="A196:D196" si="101">+A195</f>
-        <v>0.5</v>
-      </c>
-      <c r="B196" s="8">
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="8">
+        <f t="shared" ref="A199:D199" si="101">+A198</f>
+        <v>0.5</v>
+      </c>
+      <c r="B199" s="8">
         <f t="shared" si="101"/>
         <v>0.5</v>
       </c>
-      <c r="C196" s="8">
+      <c r="C199" s="8">
         <f t="shared" si="101"/>
         <v>0</v>
       </c>
-      <c r="D196" s="8">
+      <c r="D199" s="8">
         <f t="shared" si="101"/>
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="E196" s="8" t="str">
-        <f t="shared" ref="E196:E200" si="102">E195</f>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A197" s="8">
-        <f t="shared" ref="A197:D197" si="103">+A196</f>
-        <v>0.5</v>
-      </c>
-      <c r="B197" s="8">
-        <f t="shared" si="103"/>
-        <v>0.5</v>
-      </c>
-      <c r="C197" s="8">
-        <f t="shared" si="103"/>
-        <v>0</v>
-      </c>
-      <c r="D197" s="8">
-        <f t="shared" si="103"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E197" s="8" t="str">
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="8">
+        <f t="shared" ref="A200:D200" si="102">+A199</f>
+        <v>0.5</v>
+      </c>
+      <c r="B200" s="8">
         <f t="shared" si="102"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A198" s="8">
-        <f t="shared" ref="A198:D198" si="104">+A197</f>
-        <v>0.5</v>
-      </c>
-      <c r="B198" s="8">
-        <f t="shared" si="104"/>
-        <v>0.5</v>
-      </c>
-      <c r="C198" s="8">
-        <f t="shared" si="104"/>
-        <v>0</v>
-      </c>
-      <c r="D198" s="8">
-        <f t="shared" si="104"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E198" s="8" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="C200" s="8">
         <f t="shared" si="102"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A199" s="8">
-        <f t="shared" ref="A199:D199" si="105">+A198</f>
-        <v>0.5</v>
-      </c>
-      <c r="B199" s="8">
-        <f t="shared" si="105"/>
-        <v>0.5</v>
-      </c>
-      <c r="C199" s="8">
-        <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="D199" s="8">
-        <f t="shared" si="105"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E199" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="D200" s="8">
         <f t="shared" si="102"/>
-        <v>2.6*x*x*x</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A200" s="8">
-        <f t="shared" ref="A200:D200" si="106">+A199</f>
-        <v>0.5</v>
-      </c>
-      <c r="B200" s="8">
-        <f t="shared" si="106"/>
-        <v>0.5</v>
-      </c>
-      <c r="C200" s="8">
-        <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="D200" s="8">
-        <f t="shared" si="106"/>
-        <v>-5.0000000000000001E-3</v>
-      </c>
-      <c r="E200" s="8" t="str">
-        <f t="shared" si="102"/>
-        <v>2.6*x*x*x</v>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>

--- a/input_examples/distanceDependency_square_amp.xlsx
+++ b/input_examples/distanceDependency_square_amp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\SelfImaging\input_examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7DF7E1-1FD5-412D-8A5E-CC52D28976C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6474C75-A6A1-4811-A5B8-77350028CB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grating" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,6 @@
     <sheet name="Dependencies" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -7344,7 +7343,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B2" s="8">
         <v>0.5</v>
@@ -7360,7 +7359,7 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <f t="shared" ref="A3:D66" si="0">+A2</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B3" s="8">
         <f t="shared" si="0"/>
@@ -7378,7 +7377,7 @@
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B4" s="8">
         <f t="shared" si="0"/>
@@ -7396,7 +7395,7 @@
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B5" s="8">
         <f t="shared" si="0"/>
@@ -7414,7 +7413,7 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B6" s="8">
         <f t="shared" si="0"/>
@@ -7432,7 +7431,7 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B7" s="8">
         <f t="shared" si="0"/>
@@ -7450,7 +7449,7 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B8" s="8">
         <f t="shared" si="0"/>
@@ -7468,7 +7467,7 @@
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B9" s="8">
         <f t="shared" si="0"/>
@@ -7486,7 +7485,7 @@
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B10" s="8">
         <f t="shared" si="0"/>
@@ -7504,7 +7503,7 @@
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B11" s="8">
         <f t="shared" si="0"/>
@@ -7522,7 +7521,7 @@
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B12" s="8">
         <f t="shared" si="0"/>
@@ -7540,7 +7539,7 @@
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B13" s="8">
         <f t="shared" si="0"/>
@@ -7558,7 +7557,7 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B14" s="8">
         <f t="shared" si="0"/>
@@ -7576,7 +7575,7 @@
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B15" s="8">
         <f t="shared" si="0"/>
@@ -7594,7 +7593,7 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B16" s="8">
         <f t="shared" si="0"/>
@@ -7612,7 +7611,7 @@
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B17" s="8">
         <f t="shared" si="0"/>
@@ -7630,7 +7629,7 @@
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B18" s="8">
         <f t="shared" si="0"/>
@@ -7648,7 +7647,7 @@
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B19" s="8">
         <f t="shared" si="0"/>
@@ -7666,7 +7665,7 @@
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B20" s="8">
         <f t="shared" si="0"/>
@@ -7684,7 +7683,7 @@
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B21" s="8">
         <f t="shared" si="0"/>
@@ -7702,7 +7701,7 @@
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B22" s="8">
         <f t="shared" si="0"/>
@@ -7720,7 +7719,7 @@
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B23" s="8">
         <f t="shared" si="0"/>
@@ -7738,7 +7737,7 @@
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B24" s="8">
         <f t="shared" si="0"/>
@@ -7756,7 +7755,7 @@
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B25" s="8">
         <f t="shared" si="0"/>
@@ -7774,7 +7773,7 @@
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B26" s="8">
         <f t="shared" si="0"/>
@@ -7792,7 +7791,7 @@
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B27" s="8">
         <f t="shared" si="0"/>
@@ -7810,7 +7809,7 @@
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B28" s="8">
         <f t="shared" si="0"/>
@@ -7828,7 +7827,7 @@
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B29" s="8">
         <f t="shared" si="0"/>
@@ -7846,7 +7845,7 @@
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B30" s="8">
         <f t="shared" si="0"/>
@@ -7864,7 +7863,7 @@
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B31" s="8">
         <f t="shared" si="0"/>
@@ -7882,7 +7881,7 @@
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B32" s="8">
         <f t="shared" si="0"/>
@@ -7900,7 +7899,7 @@
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B33" s="8">
         <f t="shared" si="0"/>
@@ -7918,7 +7917,7 @@
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B34" s="8">
         <f t="shared" si="0"/>
@@ -7936,7 +7935,7 @@
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B35" s="8">
         <f t="shared" si="0"/>
@@ -7954,7 +7953,7 @@
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B36" s="8">
         <f t="shared" si="0"/>
@@ -7972,7 +7971,7 @@
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B37" s="8">
         <f t="shared" si="0"/>
@@ -7990,7 +7989,7 @@
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B38" s="8">
         <f t="shared" si="0"/>
@@ -8008,7 +8007,7 @@
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B39" s="8">
         <f t="shared" si="0"/>
@@ -8026,7 +8025,7 @@
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B40" s="8">
         <f t="shared" si="0"/>
@@ -8044,7 +8043,7 @@
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B41" s="8">
         <f t="shared" si="0"/>
@@ -8062,7 +8061,7 @@
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B42" s="8">
         <f t="shared" si="0"/>
@@ -8080,7 +8079,7 @@
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B43" s="8">
         <f t="shared" si="0"/>
@@ -8098,7 +8097,7 @@
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B44" s="8">
         <f t="shared" si="0"/>
@@ -8116,7 +8115,7 @@
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B45" s="8">
         <f t="shared" si="0"/>
@@ -8134,7 +8133,7 @@
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B46" s="8">
         <f t="shared" si="0"/>
@@ -8152,7 +8151,7 @@
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B47" s="8">
         <f t="shared" si="0"/>
@@ -8170,7 +8169,7 @@
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B48" s="8">
         <f t="shared" si="0"/>
@@ -8188,7 +8187,7 @@
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B49" s="8">
         <f t="shared" si="0"/>
@@ -8206,7 +8205,7 @@
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B50" s="8">
         <f t="shared" si="0"/>
@@ -8224,7 +8223,7 @@
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B51" s="8">
         <f t="shared" si="0"/>
@@ -8242,7 +8241,7 @@
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B52" s="8">
         <f t="shared" si="0"/>
@@ -8260,7 +8259,7 @@
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B53" s="8">
         <f t="shared" si="0"/>
@@ -8278,7 +8277,7 @@
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B54" s="8">
         <f t="shared" si="0"/>
@@ -8296,7 +8295,7 @@
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B55" s="8">
         <f t="shared" si="0"/>
@@ -8314,7 +8313,7 @@
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B56" s="8">
         <f t="shared" si="0"/>
@@ -8332,7 +8331,7 @@
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B57" s="8">
         <f t="shared" si="0"/>
@@ -8350,7 +8349,7 @@
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B58" s="8">
         <f t="shared" si="0"/>
@@ -8368,7 +8367,7 @@
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B59" s="8">
         <f t="shared" si="0"/>
@@ -8386,7 +8385,7 @@
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B60" s="8">
         <f t="shared" si="0"/>
@@ -8404,7 +8403,7 @@
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B61" s="8">
         <f t="shared" si="0"/>
@@ -8422,7 +8421,7 @@
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B62" s="8">
         <f t="shared" si="0"/>
@@ -8440,7 +8439,7 @@
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B63" s="8">
         <f t="shared" si="0"/>
@@ -8458,7 +8457,7 @@
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B64" s="8">
         <f t="shared" si="0"/>
@@ -8476,7 +8475,7 @@
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B65" s="8">
         <f t="shared" si="0"/>
@@ -8494,7 +8493,7 @@
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B66" s="8">
         <f t="shared" si="0"/>
@@ -8512,7 +8511,7 @@
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <f t="shared" ref="A67:D100" si="2">+A66</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B67" s="8">
         <f t="shared" si="2"/>
@@ -8530,7 +8529,7 @@
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B68" s="8">
         <f t="shared" si="2"/>
@@ -8548,7 +8547,7 @@
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B69" s="8">
         <f t="shared" si="2"/>
@@ -8566,7 +8565,7 @@
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B70" s="8">
         <f t="shared" si="2"/>
@@ -8584,7 +8583,7 @@
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B71" s="8">
         <f t="shared" si="2"/>
@@ -8602,7 +8601,7 @@
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B72" s="8">
         <f t="shared" si="2"/>
@@ -8620,7 +8619,7 @@
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B73" s="8">
         <f t="shared" si="2"/>
@@ -8638,7 +8637,7 @@
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B74" s="8">
         <f t="shared" si="2"/>
@@ -8656,7 +8655,7 @@
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B75" s="8">
         <f t="shared" si="2"/>
@@ -8674,7 +8673,7 @@
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B76" s="8">
         <f t="shared" si="2"/>
@@ -8692,7 +8691,7 @@
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B77" s="8">
         <f t="shared" si="2"/>
@@ -8710,7 +8709,7 @@
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B78" s="8">
         <f t="shared" si="2"/>
@@ -8728,7 +8727,7 @@
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B79" s="8">
         <f t="shared" si="2"/>
@@ -8746,7 +8745,7 @@
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B80" s="8">
         <f t="shared" si="2"/>
@@ -8764,7 +8763,7 @@
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B81" s="8">
         <f t="shared" si="2"/>
@@ -8782,7 +8781,7 @@
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B82" s="8">
         <f t="shared" si="2"/>
@@ -8800,7 +8799,7 @@
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B83" s="8">
         <f t="shared" si="2"/>
@@ -8818,7 +8817,7 @@
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B84" s="8">
         <f t="shared" si="2"/>
@@ -8836,7 +8835,7 @@
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B85" s="8">
         <f t="shared" si="2"/>
@@ -8854,7 +8853,7 @@
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B86" s="8">
         <f t="shared" si="2"/>
@@ -8872,7 +8871,7 @@
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B87" s="8">
         <f t="shared" si="2"/>
@@ -8890,7 +8889,7 @@
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B88" s="8">
         <f t="shared" si="2"/>
@@ -8908,7 +8907,7 @@
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B89" s="8">
         <f t="shared" si="2"/>
@@ -8926,7 +8925,7 @@
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B90" s="8">
         <f t="shared" si="2"/>
@@ -8944,7 +8943,7 @@
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B91" s="8">
         <f t="shared" si="2"/>
@@ -8962,7 +8961,7 @@
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B92" s="8">
         <f t="shared" si="2"/>
@@ -8980,7 +8979,7 @@
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B93" s="8">
         <f t="shared" si="2"/>
@@ -8998,7 +8997,7 @@
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B94" s="8">
         <f t="shared" si="2"/>
@@ -9016,7 +9015,7 @@
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B95" s="8">
         <f t="shared" si="2"/>
@@ -9034,7 +9033,7 @@
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B96" s="8">
         <f t="shared" si="2"/>
@@ -9052,7 +9051,7 @@
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B97" s="8">
         <f t="shared" si="2"/>
@@ -9070,7 +9069,7 @@
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B98" s="8">
         <f t="shared" si="2"/>
@@ -9088,7 +9087,7 @@
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B99" s="8">
         <f t="shared" si="2"/>
@@ -9106,7 +9105,7 @@
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B100" s="8">
         <f t="shared" si="2"/>
@@ -9124,7 +9123,7 @@
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
         <f t="shared" ref="A101:D101" si="3">+A100</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B101" s="8">
         <f t="shared" si="3"/>
@@ -9142,7 +9141,7 @@
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
         <f t="shared" ref="A102:D102" si="4">+A101</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B102" s="8">
         <f t="shared" si="4"/>
@@ -9160,7 +9159,7 @@
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
         <f t="shared" ref="A103:D103" si="5">+A102</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B103" s="8">
         <f t="shared" si="5"/>
@@ -9178,7 +9177,7 @@
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="8">
         <f t="shared" ref="A104:D104" si="6">+A103</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B104" s="8">
         <f t="shared" si="6"/>
@@ -9196,7 +9195,7 @@
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
         <f t="shared" ref="A105:D105" si="7">+A104</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B105" s="8">
         <f t="shared" si="7"/>
@@ -9214,7 +9213,7 @@
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="8">
         <f t="shared" ref="A106:D106" si="8">+A105</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B106" s="8">
         <f t="shared" si="8"/>
@@ -9232,7 +9231,7 @@
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
         <f t="shared" ref="A107:D107" si="9">+A106</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B107" s="8">
         <f t="shared" si="9"/>
@@ -9250,7 +9249,7 @@
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="8">
         <f t="shared" ref="A108:D108" si="10">+A107</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B108" s="8">
         <f t="shared" si="10"/>
@@ -9268,7 +9267,7 @@
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
         <f t="shared" ref="A109:D109" si="11">+A108</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B109" s="8">
         <f t="shared" si="11"/>
@@ -9286,7 +9285,7 @@
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="8">
         <f t="shared" ref="A110:D110" si="12">+A109</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B110" s="8">
         <f t="shared" si="12"/>
@@ -9304,7 +9303,7 @@
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
         <f t="shared" ref="A111:D111" si="13">+A110</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B111" s="8">
         <f t="shared" si="13"/>
@@ -9322,7 +9321,7 @@
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="8">
         <f t="shared" ref="A112:D112" si="14">+A111</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B112" s="8">
         <f t="shared" si="14"/>
@@ -9340,7 +9339,7 @@
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
         <f t="shared" ref="A113:D113" si="15">+A112</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B113" s="8">
         <f t="shared" si="15"/>
@@ -9358,7 +9357,7 @@
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="8">
         <f t="shared" ref="A114:D114" si="16">+A113</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B114" s="8">
         <f t="shared" si="16"/>
@@ -9376,7 +9375,7 @@
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
         <f t="shared" ref="A115:D115" si="17">+A114</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B115" s="8">
         <f t="shared" si="17"/>
@@ -9394,7 +9393,7 @@
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="8">
         <f t="shared" ref="A116:D116" si="18">+A115</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B116" s="8">
         <f t="shared" si="18"/>
@@ -9412,7 +9411,7 @@
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="8">
         <f t="shared" ref="A117:D117" si="19">+A116</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B117" s="8">
         <f t="shared" si="19"/>
@@ -9430,7 +9429,7 @@
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
         <f t="shared" ref="A118:D118" si="20">+A117</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B118" s="8">
         <f t="shared" si="20"/>
@@ -9448,7 +9447,7 @@
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="8">
         <f t="shared" ref="A119:D119" si="21">+A118</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B119" s="8">
         <f t="shared" si="21"/>
@@ -9466,7 +9465,7 @@
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
         <f t="shared" ref="A120:D120" si="22">+A119</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B120" s="8">
         <f t="shared" si="22"/>
@@ -9484,7 +9483,7 @@
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="8">
         <f t="shared" ref="A121:D121" si="23">+A120</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B121" s="8">
         <f t="shared" si="23"/>
@@ -9502,7 +9501,7 @@
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
         <f t="shared" ref="A122:D122" si="24">+A121</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B122" s="8">
         <f t="shared" si="24"/>
@@ -9520,7 +9519,7 @@
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="8">
         <f t="shared" ref="A123:D123" si="25">+A122</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B123" s="8">
         <f t="shared" si="25"/>
@@ -9538,7 +9537,7 @@
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
         <f t="shared" ref="A124:D124" si="26">+A123</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B124" s="8">
         <f t="shared" si="26"/>
@@ -9556,7 +9555,7 @@
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="8">
         <f t="shared" ref="A125:D125" si="27">+A124</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B125" s="8">
         <f t="shared" si="27"/>
@@ -9574,7 +9573,7 @@
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="8">
         <f t="shared" ref="A126:D126" si="28">+A125</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B126" s="8">
         <f t="shared" si="28"/>
@@ -9592,7 +9591,7 @@
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <f t="shared" ref="A127:D127" si="29">+A126</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B127" s="8">
         <f t="shared" si="29"/>
@@ -9610,7 +9609,7 @@
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
         <f t="shared" ref="A128:D128" si="30">+A127</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B128" s="8">
         <f t="shared" si="30"/>
@@ -9628,7 +9627,7 @@
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
         <f t="shared" ref="A129:D129" si="31">+A128</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B129" s="8">
         <f t="shared" si="31"/>
@@ -9646,7 +9645,7 @@
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="8">
         <f t="shared" ref="A130:D130" si="32">+A129</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B130" s="8">
         <f t="shared" si="32"/>
@@ -9664,7 +9663,7 @@
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
         <f t="shared" ref="A131:D131" si="33">+A130</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B131" s="8">
         <f t="shared" si="33"/>
@@ -9682,7 +9681,7 @@
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
         <f t="shared" ref="A132:D132" si="34">+A131</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B132" s="8">
         <f t="shared" si="34"/>
@@ -9700,7 +9699,7 @@
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
         <f t="shared" ref="A133:D133" si="35">+A132</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B133" s="8">
         <f t="shared" si="35"/>
@@ -9718,7 +9717,7 @@
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
         <f t="shared" ref="A134:D134" si="36">+A133</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B134" s="8">
         <f t="shared" si="36"/>
@@ -9736,7 +9735,7 @@
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
         <f t="shared" ref="A135:D135" si="37">+A134</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B135" s="8">
         <f t="shared" si="37"/>
@@ -9754,7 +9753,7 @@
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
         <f t="shared" ref="A136:D136" si="38">+A135</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B136" s="8">
         <f t="shared" si="38"/>
@@ -9772,7 +9771,7 @@
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
         <f t="shared" ref="A137:D137" si="39">+A136</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B137" s="8">
         <f t="shared" si="39"/>
@@ -9790,7 +9789,7 @@
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
         <f t="shared" ref="A138:D138" si="40">+A137</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B138" s="8">
         <f t="shared" si="40"/>
@@ -9808,7 +9807,7 @@
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
         <f t="shared" ref="A139:D139" si="41">+A138</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B139" s="8">
         <f t="shared" si="41"/>
@@ -9826,7 +9825,7 @@
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
         <f t="shared" ref="A140:D140" si="42">+A139</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B140" s="8">
         <f t="shared" si="42"/>
@@ -9844,7 +9843,7 @@
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <f t="shared" ref="A141:D141" si="43">+A140</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B141" s="8">
         <f t="shared" si="43"/>
@@ -9862,7 +9861,7 @@
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
         <f t="shared" ref="A142:D142" si="44">+A141</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B142" s="8">
         <f t="shared" si="44"/>
@@ -9880,7 +9879,7 @@
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <f t="shared" ref="A143:D143" si="45">+A142</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B143" s="8">
         <f t="shared" si="45"/>
@@ -9898,7 +9897,7 @@
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
         <f t="shared" ref="A144:D144" si="46">+A143</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B144" s="8">
         <f t="shared" si="46"/>
@@ -9916,7 +9915,7 @@
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
         <f t="shared" ref="A145:D145" si="47">+A144</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B145" s="8">
         <f t="shared" si="47"/>
@@ -9934,7 +9933,7 @@
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
         <f t="shared" ref="A146:D146" si="48">+A145</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B146" s="8">
         <f t="shared" si="48"/>
@@ -9952,7 +9951,7 @@
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
         <f t="shared" ref="A147:D147" si="49">+A146</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B147" s="8">
         <f t="shared" si="49"/>
@@ -9970,7 +9969,7 @@
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
         <f t="shared" ref="A148:D148" si="50">+A147</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B148" s="8">
         <f t="shared" si="50"/>
@@ -9988,7 +9987,7 @@
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
         <f t="shared" ref="A149:D149" si="51">+A148</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B149" s="8">
         <f t="shared" si="51"/>
@@ -10006,7 +10005,7 @@
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
         <f t="shared" ref="A150:D150" si="52">+A149</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B150" s="8">
         <f t="shared" si="52"/>
@@ -10024,7 +10023,7 @@
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
         <f t="shared" ref="A151:D151" si="53">+A150</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B151" s="8">
         <f t="shared" si="53"/>
@@ -10042,7 +10041,7 @@
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
         <f t="shared" ref="A152:D152" si="54">+A151</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B152" s="8">
         <f t="shared" si="54"/>
@@ -10060,7 +10059,7 @@
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
         <f t="shared" ref="A153:D153" si="55">+A152</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B153" s="8">
         <f t="shared" si="55"/>
@@ -10078,7 +10077,7 @@
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
         <f t="shared" ref="A154:D154" si="56">+A153</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B154" s="8">
         <f t="shared" si="56"/>
@@ -10096,7 +10095,7 @@
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
         <f t="shared" ref="A155:D155" si="57">+A154</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B155" s="8">
         <f t="shared" si="57"/>
@@ -10114,7 +10113,7 @@
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
         <f t="shared" ref="A156:D156" si="58">+A155</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B156" s="8">
         <f t="shared" si="58"/>
@@ -10132,7 +10131,7 @@
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
         <f t="shared" ref="A157:D157" si="59">+A156</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B157" s="8">
         <f t="shared" si="59"/>
@@ -10150,7 +10149,7 @@
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
         <f t="shared" ref="A158:D158" si="60">+A157</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B158" s="8">
         <f t="shared" si="60"/>
@@ -10168,7 +10167,7 @@
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
         <f t="shared" ref="A159:D159" si="61">+A158</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B159" s="8">
         <f t="shared" si="61"/>
@@ -10186,7 +10185,7 @@
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
         <f t="shared" ref="A160:D160" si="62">+A159</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B160" s="8">
         <f t="shared" si="62"/>
@@ -10204,7 +10203,7 @@
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
         <f t="shared" ref="A161:D161" si="63">+A160</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B161" s="8">
         <f t="shared" si="63"/>
@@ -10222,7 +10221,7 @@
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
         <f t="shared" ref="A162:D162" si="64">+A161</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B162" s="8">
         <f t="shared" si="64"/>
@@ -10240,7 +10239,7 @@
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
         <f t="shared" ref="A163:D163" si="65">+A162</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B163" s="8">
         <f t="shared" si="65"/>
@@ -10258,7 +10257,7 @@
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
         <f t="shared" ref="A164:D164" si="66">+A163</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B164" s="8">
         <f t="shared" si="66"/>
@@ -10276,7 +10275,7 @@
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
         <f t="shared" ref="A165:D165" si="67">+A164</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B165" s="8">
         <f t="shared" si="67"/>
@@ -10294,7 +10293,7 @@
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
         <f t="shared" ref="A166:D166" si="68">+A165</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B166" s="8">
         <f t="shared" si="68"/>
@@ -10312,7 +10311,7 @@
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
         <f t="shared" ref="A167:D167" si="69">+A166</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B167" s="8">
         <f t="shared" si="69"/>
@@ -10330,7 +10329,7 @@
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
         <f t="shared" ref="A168:D168" si="70">+A167</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B168" s="8">
         <f t="shared" si="70"/>
@@ -10348,7 +10347,7 @@
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
         <f t="shared" ref="A169:D169" si="71">+A168</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B169" s="8">
         <f t="shared" si="71"/>
@@ -10366,7 +10365,7 @@
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="8">
         <f t="shared" ref="A170:D170" si="72">+A169</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B170" s="8">
         <f t="shared" si="72"/>
@@ -10384,7 +10383,7 @@
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="8">
         <f t="shared" ref="A171:D171" si="73">+A170</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B171" s="8">
         <f t="shared" si="73"/>
@@ -10402,7 +10401,7 @@
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="8">
         <f t="shared" ref="A172:D172" si="74">+A171</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B172" s="8">
         <f t="shared" si="74"/>
@@ -10420,7 +10419,7 @@
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="8">
         <f t="shared" ref="A173:D173" si="75">+A172</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B173" s="8">
         <f t="shared" si="75"/>
@@ -10438,7 +10437,7 @@
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="8">
         <f t="shared" ref="A174:D174" si="76">+A173</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B174" s="8">
         <f t="shared" si="76"/>
@@ -10456,7 +10455,7 @@
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="8">
         <f t="shared" ref="A175:D175" si="77">+A174</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B175" s="8">
         <f t="shared" si="77"/>
@@ -10474,7 +10473,7 @@
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="8">
         <f t="shared" ref="A176:D176" si="78">+A175</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B176" s="8">
         <f t="shared" si="78"/>
@@ -10492,7 +10491,7 @@
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="8">
         <f t="shared" ref="A177:D177" si="79">+A176</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B177" s="8">
         <f t="shared" si="79"/>
@@ -10510,7 +10509,7 @@
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="8">
         <f t="shared" ref="A178:D178" si="80">+A177</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B178" s="8">
         <f t="shared" si="80"/>
@@ -10528,7 +10527,7 @@
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="8">
         <f t="shared" ref="A179:D179" si="81">+A178</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B179" s="8">
         <f t="shared" si="81"/>
@@ -10546,7 +10545,7 @@
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="8">
         <f t="shared" ref="A180:D180" si="82">+A179</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B180" s="8">
         <f t="shared" si="82"/>
@@ -10564,7 +10563,7 @@
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="8">
         <f t="shared" ref="A181:D181" si="83">+A180</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B181" s="8">
         <f t="shared" si="83"/>
@@ -10582,7 +10581,7 @@
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="8">
         <f t="shared" ref="A182:D182" si="84">+A181</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B182" s="8">
         <f t="shared" si="84"/>
@@ -10600,7 +10599,7 @@
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="8">
         <f t="shared" ref="A183:D183" si="85">+A182</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B183" s="8">
         <f t="shared" si="85"/>
@@ -10618,7 +10617,7 @@
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="8">
         <f t="shared" ref="A184:D184" si="86">+A183</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B184" s="8">
         <f t="shared" si="86"/>
@@ -10636,7 +10635,7 @@
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="8">
         <f t="shared" ref="A185:D185" si="87">+A184</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B185" s="8">
         <f t="shared" si="87"/>
@@ -10654,7 +10653,7 @@
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="8">
         <f t="shared" ref="A186:D186" si="88">+A185</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B186" s="8">
         <f t="shared" si="88"/>
@@ -10672,7 +10671,7 @@
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="8">
         <f t="shared" ref="A187:D187" si="89">+A186</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B187" s="8">
         <f t="shared" si="89"/>
@@ -10690,7 +10689,7 @@
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="8">
         <f t="shared" ref="A188:D188" si="90">+A187</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B188" s="8">
         <f t="shared" si="90"/>
@@ -10708,7 +10707,7 @@
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="8">
         <f t="shared" ref="A189:D189" si="91">+A188</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B189" s="8">
         <f t="shared" si="91"/>
@@ -10726,7 +10725,7 @@
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="8">
         <f t="shared" ref="A190:D190" si="92">+A189</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B190" s="8">
         <f t="shared" si="92"/>
@@ -10744,7 +10743,7 @@
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="8">
         <f t="shared" ref="A191:D191" si="93">+A190</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B191" s="8">
         <f t="shared" si="93"/>
@@ -10762,7 +10761,7 @@
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="8">
         <f t="shared" ref="A192:D192" si="94">+A191</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B192" s="8">
         <f t="shared" si="94"/>
@@ -10780,7 +10779,7 @@
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="8">
         <f t="shared" ref="A193:D193" si="95">+A192</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B193" s="8">
         <f t="shared" si="95"/>
@@ -10798,7 +10797,7 @@
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="8">
         <f t="shared" ref="A194:D194" si="96">+A193</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B194" s="8">
         <f t="shared" si="96"/>
@@ -10816,7 +10815,7 @@
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="8">
         <f t="shared" ref="A195:D195" si="97">+A194</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B195" s="8">
         <f t="shared" si="97"/>
@@ -10834,7 +10833,7 @@
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="8">
         <f t="shared" ref="A196:D196" si="98">+A195</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B196" s="8">
         <f t="shared" si="98"/>
@@ -10852,7 +10851,7 @@
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="8">
         <f t="shared" ref="A197:D197" si="99">+A196</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B197" s="8">
         <f t="shared" si="99"/>
@@ -10870,7 +10869,7 @@
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="8">
         <f t="shared" ref="A198:D198" si="100">+A197</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B198" s="8">
         <f t="shared" si="100"/>
@@ -10888,7 +10887,7 @@
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="8">
         <f t="shared" ref="A199:D199" si="101">+A198</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B199" s="8">
         <f t="shared" si="101"/>
@@ -10906,7 +10905,7 @@
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="8">
         <f t="shared" ref="A200:D200" si="102">+A199</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B200" s="8">
         <f t="shared" si="102"/>
@@ -12974,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C2" s="12">
         <v>5</v>
@@ -12990,7 +12989,7 @@
       </c>
       <c r="B3" s="8">
         <f>+B2</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C3" s="12">
         <f>+C2</f>
@@ -13008,7 +13007,7 @@
       </c>
       <c r="B4" s="8">
         <f t="shared" ref="B4:C67" si="1">+B3</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4" s="12">
         <f t="shared" si="1"/>
@@ -13026,7 +13025,7 @@
       </c>
       <c r="B5" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C5" s="12">
         <f t="shared" si="1"/>
@@ -13044,7 +13043,7 @@
       </c>
       <c r="B6" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" s="12">
         <f t="shared" si="1"/>
@@ -13062,7 +13061,7 @@
       </c>
       <c r="B7" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C7" s="12">
         <f t="shared" si="1"/>
@@ -13080,7 +13079,7 @@
       </c>
       <c r="B8" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C8" s="12">
         <f t="shared" si="1"/>
@@ -13098,7 +13097,7 @@
       </c>
       <c r="B9" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C9" s="12">
         <f t="shared" si="1"/>
@@ -13116,7 +13115,7 @@
       </c>
       <c r="B10" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C10" s="12">
         <f t="shared" si="1"/>
@@ -13134,7 +13133,7 @@
       </c>
       <c r="B11" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" s="12">
         <f t="shared" si="1"/>
@@ -13152,7 +13151,7 @@
       </c>
       <c r="B12" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" s="12">
         <f t="shared" si="1"/>
@@ -13170,7 +13169,7 @@
       </c>
       <c r="B13" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C13" s="12">
         <f t="shared" si="1"/>
@@ -13188,7 +13187,7 @@
       </c>
       <c r="B14" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C14" s="12">
         <f t="shared" si="1"/>
@@ -13206,7 +13205,7 @@
       </c>
       <c r="B15" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C15" s="12">
         <f t="shared" si="1"/>
@@ -13224,7 +13223,7 @@
       </c>
       <c r="B16" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C16" s="12">
         <f t="shared" si="1"/>
@@ -13242,7 +13241,7 @@
       </c>
       <c r="B17" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C17" s="12">
         <f t="shared" si="1"/>
@@ -13260,7 +13259,7 @@
       </c>
       <c r="B18" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C18" s="12">
         <f t="shared" si="1"/>
@@ -13278,7 +13277,7 @@
       </c>
       <c r="B19" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C19" s="12">
         <f t="shared" si="1"/>
@@ -13296,7 +13295,7 @@
       </c>
       <c r="B20" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C20" s="12">
         <f t="shared" si="1"/>
@@ -13314,7 +13313,7 @@
       </c>
       <c r="B21" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C21" s="12">
         <f t="shared" si="1"/>
@@ -13332,7 +13331,7 @@
       </c>
       <c r="B22" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C22" s="12">
         <f t="shared" si="1"/>
@@ -13350,7 +13349,7 @@
       </c>
       <c r="B23" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C23" s="12">
         <f t="shared" si="1"/>
@@ -13368,7 +13367,7 @@
       </c>
       <c r="B24" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C24" s="12">
         <f t="shared" si="1"/>
@@ -13386,7 +13385,7 @@
       </c>
       <c r="B25" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C25" s="12">
         <f t="shared" si="1"/>
@@ -13404,7 +13403,7 @@
       </c>
       <c r="B26" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C26" s="12">
         <f t="shared" si="1"/>
@@ -13422,7 +13421,7 @@
       </c>
       <c r="B27" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C27" s="12">
         <f t="shared" si="1"/>
@@ -13440,7 +13439,7 @@
       </c>
       <c r="B28" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C28" s="12">
         <f t="shared" si="1"/>
@@ -13458,7 +13457,7 @@
       </c>
       <c r="B29" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C29" s="12">
         <f t="shared" si="1"/>
@@ -13476,7 +13475,7 @@
       </c>
       <c r="B30" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C30" s="12">
         <f t="shared" si="1"/>
@@ -13494,7 +13493,7 @@
       </c>
       <c r="B31" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C31" s="12">
         <f t="shared" si="1"/>
@@ -13512,7 +13511,7 @@
       </c>
       <c r="B32" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C32" s="12">
         <f t="shared" si="1"/>
@@ -13530,7 +13529,7 @@
       </c>
       <c r="B33" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C33" s="12">
         <f t="shared" si="1"/>
@@ -13548,7 +13547,7 @@
       </c>
       <c r="B34" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C34" s="12">
         <f t="shared" si="1"/>
@@ -13566,7 +13565,7 @@
       </c>
       <c r="B35" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C35" s="12">
         <f t="shared" si="1"/>
@@ -13584,7 +13583,7 @@
       </c>
       <c r="B36" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C36" s="12">
         <f t="shared" si="1"/>
@@ -13602,7 +13601,7 @@
       </c>
       <c r="B37" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C37" s="12">
         <f t="shared" si="1"/>
@@ -13620,7 +13619,7 @@
       </c>
       <c r="B38" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C38" s="12">
         <f t="shared" si="1"/>
@@ -13638,7 +13637,7 @@
       </c>
       <c r="B39" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C39" s="12">
         <f t="shared" si="1"/>
@@ -13656,7 +13655,7 @@
       </c>
       <c r="B40" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C40" s="12">
         <f t="shared" si="1"/>
@@ -13674,7 +13673,7 @@
       </c>
       <c r="B41" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C41" s="12">
         <f t="shared" si="1"/>
@@ -13692,7 +13691,7 @@
       </c>
       <c r="B42" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C42" s="12">
         <f t="shared" si="1"/>
@@ -13710,7 +13709,7 @@
       </c>
       <c r="B43" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C43" s="12">
         <f t="shared" si="1"/>
@@ -13728,7 +13727,7 @@
       </c>
       <c r="B44" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C44" s="12">
         <f t="shared" si="1"/>
@@ -13746,7 +13745,7 @@
       </c>
       <c r="B45" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C45" s="12">
         <f t="shared" si="1"/>
@@ -13764,7 +13763,7 @@
       </c>
       <c r="B46" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C46" s="12">
         <f t="shared" si="1"/>
@@ -13782,7 +13781,7 @@
       </c>
       <c r="B47" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C47" s="12">
         <f t="shared" si="1"/>
@@ -13800,7 +13799,7 @@
       </c>
       <c r="B48" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C48" s="12">
         <f t="shared" si="1"/>
@@ -13818,7 +13817,7 @@
       </c>
       <c r="B49" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C49" s="12">
         <f t="shared" si="1"/>
@@ -13836,7 +13835,7 @@
       </c>
       <c r="B50" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C50" s="12">
         <f t="shared" si="1"/>
@@ -13854,7 +13853,7 @@
       </c>
       <c r="B51" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C51" s="12">
         <f t="shared" si="1"/>
@@ -13872,7 +13871,7 @@
       </c>
       <c r="B52" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C52" s="12">
         <f t="shared" si="1"/>
@@ -13890,7 +13889,7 @@
       </c>
       <c r="B53" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C53" s="12">
         <f t="shared" si="1"/>
@@ -13908,7 +13907,7 @@
       </c>
       <c r="B54" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C54" s="12">
         <f t="shared" si="1"/>
@@ -13926,7 +13925,7 @@
       </c>
       <c r="B55" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C55" s="12">
         <f t="shared" si="1"/>
@@ -13944,7 +13943,7 @@
       </c>
       <c r="B56" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C56" s="12">
         <f t="shared" si="1"/>
@@ -13962,7 +13961,7 @@
       </c>
       <c r="B57" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C57" s="12">
         <f t="shared" si="1"/>
@@ -13980,7 +13979,7 @@
       </c>
       <c r="B58" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C58" s="12">
         <f t="shared" si="1"/>
@@ -13998,7 +13997,7 @@
       </c>
       <c r="B59" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C59" s="12">
         <f t="shared" si="1"/>
@@ -14016,7 +14015,7 @@
       </c>
       <c r="B60" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C60" s="12">
         <f t="shared" si="1"/>
@@ -14034,7 +14033,7 @@
       </c>
       <c r="B61" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C61" s="12">
         <f t="shared" si="1"/>
@@ -14052,7 +14051,7 @@
       </c>
       <c r="B62" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C62" s="12">
         <f t="shared" si="1"/>
@@ -14070,7 +14069,7 @@
       </c>
       <c r="B63" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C63" s="12">
         <f t="shared" si="1"/>
@@ -14088,7 +14087,7 @@
       </c>
       <c r="B64" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C64" s="12">
         <f t="shared" si="1"/>
@@ -14106,7 +14105,7 @@
       </c>
       <c r="B65" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C65" s="12">
         <f t="shared" si="1"/>
@@ -14124,7 +14123,7 @@
       </c>
       <c r="B66" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C66" s="12">
         <f t="shared" si="1"/>
@@ -14142,7 +14141,7 @@
       </c>
       <c r="B67" s="8">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C67" s="12">
         <f t="shared" si="1"/>
@@ -14160,7 +14159,7 @@
       </c>
       <c r="B68" s="8">
         <f t="shared" ref="B68:C100" si="4">+B67</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C68" s="12">
         <f t="shared" si="4"/>
@@ -14178,7 +14177,7 @@
       </c>
       <c r="B69" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C69" s="12">
         <f t="shared" si="4"/>
@@ -14196,7 +14195,7 @@
       </c>
       <c r="B70" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C70" s="12">
         <f t="shared" si="4"/>
@@ -14214,7 +14213,7 @@
       </c>
       <c r="B71" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C71" s="12">
         <f t="shared" si="4"/>
@@ -14232,7 +14231,7 @@
       </c>
       <c r="B72" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C72" s="12">
         <f t="shared" si="4"/>
@@ -14250,7 +14249,7 @@
       </c>
       <c r="B73" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C73" s="12">
         <f t="shared" si="4"/>
@@ -14268,7 +14267,7 @@
       </c>
       <c r="B74" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C74" s="12">
         <f t="shared" si="4"/>
@@ -14286,7 +14285,7 @@
       </c>
       <c r="B75" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C75" s="12">
         <f t="shared" si="4"/>
@@ -14304,7 +14303,7 @@
       </c>
       <c r="B76" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C76" s="12">
         <f t="shared" si="4"/>
@@ -14322,7 +14321,7 @@
       </c>
       <c r="B77" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C77" s="12">
         <f t="shared" si="4"/>
@@ -14340,7 +14339,7 @@
       </c>
       <c r="B78" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C78" s="12">
         <f t="shared" si="4"/>
@@ -14358,7 +14357,7 @@
       </c>
       <c r="B79" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C79" s="12">
         <f t="shared" si="4"/>
@@ -14376,7 +14375,7 @@
       </c>
       <c r="B80" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C80" s="12">
         <f t="shared" si="4"/>
@@ -14394,7 +14393,7 @@
       </c>
       <c r="B81" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C81" s="12">
         <f t="shared" si="4"/>
@@ -14412,7 +14411,7 @@
       </c>
       <c r="B82" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C82" s="12">
         <f t="shared" si="4"/>
@@ -14430,7 +14429,7 @@
       </c>
       <c r="B83" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C83" s="12">
         <f t="shared" si="4"/>
@@ -14448,7 +14447,7 @@
       </c>
       <c r="B84" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C84" s="12">
         <f t="shared" si="4"/>
@@ -14466,7 +14465,7 @@
       </c>
       <c r="B85" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C85" s="12">
         <f t="shared" si="4"/>
@@ -14484,7 +14483,7 @@
       </c>
       <c r="B86" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C86" s="12">
         <f t="shared" si="4"/>
@@ -14502,7 +14501,7 @@
       </c>
       <c r="B87" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C87" s="12">
         <f t="shared" si="4"/>
@@ -14520,7 +14519,7 @@
       </c>
       <c r="B88" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C88" s="12">
         <f t="shared" si="4"/>
@@ -14538,7 +14537,7 @@
       </c>
       <c r="B89" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C89" s="12">
         <f t="shared" si="4"/>
@@ -14556,7 +14555,7 @@
       </c>
       <c r="B90" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C90" s="12">
         <f t="shared" si="4"/>
@@ -14574,7 +14573,7 @@
       </c>
       <c r="B91" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C91" s="12">
         <f t="shared" si="4"/>
@@ -14592,7 +14591,7 @@
       </c>
       <c r="B92" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C92" s="12">
         <f t="shared" si="4"/>
@@ -14610,7 +14609,7 @@
       </c>
       <c r="B93" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C93" s="12">
         <f t="shared" si="4"/>
@@ -14628,7 +14627,7 @@
       </c>
       <c r="B94" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C94" s="12">
         <f t="shared" si="4"/>
@@ -14646,7 +14645,7 @@
       </c>
       <c r="B95" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C95" s="12">
         <f t="shared" si="4"/>
@@ -14664,7 +14663,7 @@
       </c>
       <c r="B96" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C96" s="12">
         <f t="shared" si="4"/>
@@ -14682,7 +14681,7 @@
       </c>
       <c r="B97" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C97" s="12">
         <f t="shared" si="4"/>
@@ -14700,7 +14699,7 @@
       </c>
       <c r="B98" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C98" s="12">
         <f t="shared" si="4"/>
@@ -14718,7 +14717,7 @@
       </c>
       <c r="B99" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C99" s="12">
         <f t="shared" si="4"/>
@@ -14736,7 +14735,7 @@
       </c>
       <c r="B100" s="8">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C100" s="12">
         <f t="shared" si="4"/>
@@ -14754,7 +14753,7 @@
       </c>
       <c r="B101" s="8">
         <f t="shared" ref="B101:C101" si="7">+B100</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C101" s="12">
         <f t="shared" si="7"/>
@@ -14772,7 +14771,7 @@
       </c>
       <c r="B102" s="8">
         <f t="shared" ref="B102:C102" si="8">+B101</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C102" s="12">
         <f t="shared" si="8"/>
@@ -14790,7 +14789,7 @@
       </c>
       <c r="B103" s="8">
         <f t="shared" ref="B103:C103" si="9">+B102</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C103" s="12">
         <f t="shared" si="9"/>
@@ -14808,7 +14807,7 @@
       </c>
       <c r="B104" s="8">
         <f t="shared" ref="B104:C104" si="10">+B103</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C104" s="12">
         <f t="shared" si="10"/>
@@ -14826,7 +14825,7 @@
       </c>
       <c r="B105" s="8">
         <f t="shared" ref="B105:C105" si="11">+B104</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C105" s="12">
         <f t="shared" si="11"/>
@@ -14844,7 +14843,7 @@
       </c>
       <c r="B106" s="8">
         <f t="shared" ref="B106:C106" si="12">+B105</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C106" s="12">
         <f t="shared" si="12"/>
@@ -14862,7 +14861,7 @@
       </c>
       <c r="B107" s="8">
         <f t="shared" ref="B107:C107" si="13">+B106</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C107" s="12">
         <f t="shared" si="13"/>
@@ -14880,7 +14879,7 @@
       </c>
       <c r="B108" s="8">
         <f t="shared" ref="B108:C108" si="14">+B107</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C108" s="12">
         <f t="shared" si="14"/>
@@ -14898,7 +14897,7 @@
       </c>
       <c r="B109" s="8">
         <f t="shared" ref="B109:C109" si="15">+B108</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C109" s="12">
         <f t="shared" si="15"/>
@@ -14916,7 +14915,7 @@
       </c>
       <c r="B110" s="8">
         <f t="shared" ref="B110:C110" si="16">+B109</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C110" s="12">
         <f t="shared" si="16"/>
@@ -14934,7 +14933,7 @@
       </c>
       <c r="B111" s="8">
         <f t="shared" ref="B111:C111" si="17">+B110</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C111" s="12">
         <f t="shared" si="17"/>
@@ -14952,7 +14951,7 @@
       </c>
       <c r="B112" s="8">
         <f t="shared" ref="B112:C112" si="18">+B111</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C112" s="12">
         <f t="shared" si="18"/>
@@ -14970,7 +14969,7 @@
       </c>
       <c r="B113" s="8">
         <f t="shared" ref="B113:C113" si="19">+B112</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C113" s="12">
         <f t="shared" si="19"/>
@@ -14988,7 +14987,7 @@
       </c>
       <c r="B114" s="8">
         <f t="shared" ref="B114:C114" si="20">+B113</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C114" s="12">
         <f t="shared" si="20"/>
@@ -15006,7 +15005,7 @@
       </c>
       <c r="B115" s="8">
         <f t="shared" ref="B115:C115" si="21">+B114</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C115" s="12">
         <f t="shared" si="21"/>
@@ -15024,7 +15023,7 @@
       </c>
       <c r="B116" s="8">
         <f t="shared" ref="B116:C116" si="22">+B115</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C116" s="12">
         <f t="shared" si="22"/>
@@ -15042,7 +15041,7 @@
       </c>
       <c r="B117" s="8">
         <f t="shared" ref="B117:C117" si="23">+B116</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C117" s="12">
         <f t="shared" si="23"/>
@@ -15060,7 +15059,7 @@
       </c>
       <c r="B118" s="8">
         <f t="shared" ref="B118:C118" si="24">+B117</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C118" s="12">
         <f t="shared" si="24"/>
@@ -15078,7 +15077,7 @@
       </c>
       <c r="B119" s="8">
         <f t="shared" ref="B119:C119" si="25">+B118</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C119" s="12">
         <f t="shared" si="25"/>
@@ -15096,7 +15095,7 @@
       </c>
       <c r="B120" s="8">
         <f t="shared" ref="B120:C120" si="26">+B119</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C120" s="12">
         <f t="shared" si="26"/>
@@ -15114,7 +15113,7 @@
       </c>
       <c r="B121" s="8">
         <f t="shared" ref="B121:C121" si="27">+B120</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C121" s="12">
         <f t="shared" si="27"/>
@@ -15132,7 +15131,7 @@
       </c>
       <c r="B122" s="8">
         <f t="shared" ref="B122:C122" si="28">+B121</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C122" s="12">
         <f t="shared" si="28"/>
@@ -15150,7 +15149,7 @@
       </c>
       <c r="B123" s="8">
         <f t="shared" ref="B123:C123" si="29">+B122</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C123" s="12">
         <f t="shared" si="29"/>
@@ -15168,7 +15167,7 @@
       </c>
       <c r="B124" s="8">
         <f t="shared" ref="B124:C124" si="30">+B123</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C124" s="12">
         <f t="shared" si="30"/>
@@ -15186,7 +15185,7 @@
       </c>
       <c r="B125" s="8">
         <f t="shared" ref="B125:C125" si="31">+B124</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C125" s="12">
         <f t="shared" si="31"/>
@@ -15204,7 +15203,7 @@
       </c>
       <c r="B126" s="8">
         <f t="shared" ref="B126:C126" si="32">+B125</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C126" s="12">
         <f t="shared" si="32"/>
@@ -15222,7 +15221,7 @@
       </c>
       <c r="B127" s="8">
         <f t="shared" ref="B127:C127" si="33">+B126</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C127" s="12">
         <f t="shared" si="33"/>
@@ -15240,7 +15239,7 @@
       </c>
       <c r="B128" s="8">
         <f t="shared" ref="B128:C128" si="34">+B127</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C128" s="12">
         <f t="shared" si="34"/>
@@ -15258,7 +15257,7 @@
       </c>
       <c r="B129" s="8">
         <f t="shared" ref="B129:C129" si="35">+B128</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C129" s="12">
         <f t="shared" si="35"/>
@@ -15276,7 +15275,7 @@
       </c>
       <c r="B130" s="8">
         <f t="shared" ref="B130:C130" si="36">+B129</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C130" s="12">
         <f t="shared" si="36"/>
@@ -15294,7 +15293,7 @@
       </c>
       <c r="B131" s="8">
         <f t="shared" ref="B131:C131" si="37">+B130</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C131" s="12">
         <f t="shared" si="37"/>
@@ -15312,7 +15311,7 @@
       </c>
       <c r="B132" s="8">
         <f t="shared" ref="B132:D147" si="38">+B131</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C132" s="12">
         <f t="shared" si="38"/>
@@ -15330,7 +15329,7 @@
       </c>
       <c r="B133" s="8">
         <f t="shared" ref="B133:C133" si="39">+B132</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C133" s="12">
         <f t="shared" si="39"/>
@@ -15348,7 +15347,7 @@
       </c>
       <c r="B134" s="8">
         <f t="shared" ref="B134:C134" si="40">+B133</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C134" s="12">
         <f t="shared" si="40"/>
@@ -15366,7 +15365,7 @@
       </c>
       <c r="B135" s="8">
         <f t="shared" ref="B135:C135" si="41">+B134</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C135" s="12">
         <f t="shared" si="41"/>
@@ -15384,7 +15383,7 @@
       </c>
       <c r="B136" s="8">
         <f t="shared" ref="B136:C136" si="42">+B135</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C136" s="12">
         <f t="shared" si="42"/>
@@ -15402,7 +15401,7 @@
       </c>
       <c r="B137" s="8">
         <f t="shared" ref="B137:C137" si="43">+B136</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C137" s="12">
         <f t="shared" si="43"/>
@@ -15420,7 +15419,7 @@
       </c>
       <c r="B138" s="8">
         <f t="shared" ref="B138:C138" si="44">+B137</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C138" s="12">
         <f t="shared" si="44"/>
@@ -15438,7 +15437,7 @@
       </c>
       <c r="B139" s="8">
         <f t="shared" ref="B139:C139" si="45">+B138</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C139" s="12">
         <f t="shared" si="45"/>
@@ -15456,7 +15455,7 @@
       </c>
       <c r="B140" s="8">
         <f t="shared" ref="B140:C140" si="46">+B139</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C140" s="12">
         <f t="shared" si="46"/>
@@ -15474,7 +15473,7 @@
       </c>
       <c r="B141" s="8">
         <f t="shared" ref="B141:C141" si="47">+B140</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C141" s="12">
         <f t="shared" si="47"/>
@@ -15492,7 +15491,7 @@
       </c>
       <c r="B142" s="8">
         <f t="shared" ref="B142:C142" si="48">+B141</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C142" s="12">
         <f t="shared" si="48"/>
@@ -15510,7 +15509,7 @@
       </c>
       <c r="B143" s="8">
         <f t="shared" ref="B143:C143" si="49">+B142</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C143" s="12">
         <f t="shared" si="49"/>
@@ -15528,7 +15527,7 @@
       </c>
       <c r="B144" s="8">
         <f t="shared" ref="B144:C144" si="50">+B143</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C144" s="12">
         <f t="shared" si="50"/>
@@ -15546,7 +15545,7 @@
       </c>
       <c r="B145" s="8">
         <f t="shared" ref="B145:C145" si="51">+B144</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C145" s="12">
         <f t="shared" si="51"/>
@@ -15564,7 +15563,7 @@
       </c>
       <c r="B146" s="8">
         <f t="shared" ref="B146:C146" si="52">+B145</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C146" s="12">
         <f t="shared" si="52"/>
@@ -15582,7 +15581,7 @@
       </c>
       <c r="B147" s="8">
         <f t="shared" ref="B147:C147" si="53">+B146</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C147" s="12">
         <f t="shared" si="53"/>
@@ -15600,7 +15599,7 @@
       </c>
       <c r="B148" s="8">
         <f t="shared" ref="B148:D163" si="54">+B147</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C148" s="12">
         <f t="shared" si="54"/>
@@ -15618,7 +15617,7 @@
       </c>
       <c r="B149" s="8">
         <f t="shared" ref="B149:C149" si="55">+B148</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C149" s="12">
         <f t="shared" si="55"/>
@@ -15636,7 +15635,7 @@
       </c>
       <c r="B150" s="8">
         <f t="shared" ref="B150:C150" si="56">+B149</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C150" s="12">
         <f t="shared" si="56"/>
@@ -15654,7 +15653,7 @@
       </c>
       <c r="B151" s="8">
         <f t="shared" ref="B151:C151" si="57">+B150</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C151" s="12">
         <f t="shared" si="57"/>
@@ -15672,7 +15671,7 @@
       </c>
       <c r="B152" s="8">
         <f t="shared" ref="B152:C152" si="58">+B151</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C152" s="12">
         <f t="shared" si="58"/>
@@ -15690,7 +15689,7 @@
       </c>
       <c r="B153" s="8">
         <f t="shared" ref="B153:C153" si="59">+B152</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C153" s="12">
         <f t="shared" si="59"/>
@@ -15708,7 +15707,7 @@
       </c>
       <c r="B154" s="8">
         <f t="shared" ref="B154:C154" si="60">+B153</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C154" s="12">
         <f t="shared" si="60"/>
@@ -15726,7 +15725,7 @@
       </c>
       <c r="B155" s="8">
         <f t="shared" ref="B155:C155" si="61">+B154</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C155" s="12">
         <f t="shared" si="61"/>
@@ -15744,7 +15743,7 @@
       </c>
       <c r="B156" s="8">
         <f t="shared" ref="B156:C156" si="62">+B155</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C156" s="12">
         <f t="shared" si="62"/>
@@ -15762,7 +15761,7 @@
       </c>
       <c r="B157" s="8">
         <f t="shared" ref="B157:C157" si="63">+B156</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C157" s="12">
         <f t="shared" si="63"/>
@@ -15780,7 +15779,7 @@
       </c>
       <c r="B158" s="8">
         <f t="shared" ref="B158:C158" si="64">+B157</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C158" s="12">
         <f t="shared" si="64"/>
@@ -15798,7 +15797,7 @@
       </c>
       <c r="B159" s="8">
         <f t="shared" ref="B159:C159" si="65">+B158</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C159" s="12">
         <f t="shared" si="65"/>
@@ -15816,7 +15815,7 @@
       </c>
       <c r="B160" s="8">
         <f t="shared" ref="B160:C160" si="66">+B159</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C160" s="12">
         <f t="shared" si="66"/>
@@ -15834,7 +15833,7 @@
       </c>
       <c r="B161" s="8">
         <f t="shared" ref="B161:C161" si="67">+B160</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C161" s="12">
         <f t="shared" si="67"/>
@@ -15852,7 +15851,7 @@
       </c>
       <c r="B162" s="8">
         <f t="shared" ref="B162:C162" si="68">+B161</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C162" s="12">
         <f t="shared" si="68"/>
@@ -15870,7 +15869,7 @@
       </c>
       <c r="B163" s="8">
         <f t="shared" ref="B163:C163" si="69">+B162</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C163" s="12">
         <f t="shared" si="69"/>
@@ -15888,7 +15887,7 @@
       </c>
       <c r="B164" s="8">
         <f t="shared" ref="B164:D179" si="70">+B163</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C164" s="12">
         <f t="shared" si="70"/>
@@ -15906,7 +15905,7 @@
       </c>
       <c r="B165" s="8">
         <f t="shared" ref="B165:C165" si="72">+B164</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C165" s="12">
         <f t="shared" si="72"/>
@@ -15924,7 +15923,7 @@
       </c>
       <c r="B166" s="8">
         <f t="shared" ref="B166:C166" si="73">+B165</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C166" s="12">
         <f t="shared" si="73"/>
@@ -15942,7 +15941,7 @@
       </c>
       <c r="B167" s="8">
         <f t="shared" ref="B167:C167" si="74">+B166</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C167" s="12">
         <f t="shared" si="74"/>
@@ -15960,7 +15959,7 @@
       </c>
       <c r="B168" s="8">
         <f t="shared" ref="B168:C168" si="75">+B167</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C168" s="12">
         <f t="shared" si="75"/>
@@ -15978,7 +15977,7 @@
       </c>
       <c r="B169" s="8">
         <f t="shared" ref="B169:C169" si="76">+B168</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C169" s="12">
         <f t="shared" si="76"/>
@@ -15996,7 +15995,7 @@
       </c>
       <c r="B170" s="8">
         <f t="shared" ref="B170:C170" si="77">+B169</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C170" s="12">
         <f t="shared" si="77"/>
@@ -16014,7 +16013,7 @@
       </c>
       <c r="B171" s="8">
         <f t="shared" ref="B171:C171" si="78">+B170</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C171" s="12">
         <f t="shared" si="78"/>
@@ -16032,7 +16031,7 @@
       </c>
       <c r="B172" s="8">
         <f t="shared" ref="B172:C172" si="79">+B171</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C172" s="12">
         <f t="shared" si="79"/>
@@ -16050,7 +16049,7 @@
       </c>
       <c r="B173" s="8">
         <f t="shared" ref="B173:C173" si="80">+B172</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C173" s="12">
         <f t="shared" si="80"/>
@@ -16068,7 +16067,7 @@
       </c>
       <c r="B174" s="8">
         <f t="shared" ref="B174:C174" si="81">+B173</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C174" s="12">
         <f t="shared" si="81"/>
@@ -16086,7 +16085,7 @@
       </c>
       <c r="B175" s="8">
         <f t="shared" ref="B175:C175" si="82">+B174</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C175" s="12">
         <f t="shared" si="82"/>
@@ -16104,7 +16103,7 @@
       </c>
       <c r="B176" s="8">
         <f t="shared" ref="B176:C176" si="83">+B175</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C176" s="12">
         <f t="shared" si="83"/>
@@ -16122,7 +16121,7 @@
       </c>
       <c r="B177" s="8">
         <f t="shared" ref="B177:C177" si="84">+B176</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C177" s="12">
         <f t="shared" si="84"/>
@@ -16140,7 +16139,7 @@
       </c>
       <c r="B178" s="8">
         <f t="shared" ref="B178:C178" si="85">+B177</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C178" s="12">
         <f t="shared" si="85"/>
@@ -16158,7 +16157,7 @@
       </c>
       <c r="B179" s="8">
         <f t="shared" ref="B179:C179" si="86">+B178</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C179" s="12">
         <f t="shared" si="86"/>
@@ -16176,7 +16175,7 @@
       </c>
       <c r="B180" s="8">
         <f t="shared" ref="B180:D195" si="87">+B179</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C180" s="12">
         <f t="shared" si="87"/>
@@ -16194,7 +16193,7 @@
       </c>
       <c r="B181" s="8">
         <f t="shared" ref="B181:C181" si="88">+B180</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C181" s="12">
         <f t="shared" si="88"/>
@@ -16212,7 +16211,7 @@
       </c>
       <c r="B182" s="8">
         <f t="shared" ref="B182:C182" si="89">+B181</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C182" s="12">
         <f t="shared" si="89"/>
@@ -16230,7 +16229,7 @@
       </c>
       <c r="B183" s="8">
         <f t="shared" ref="B183:C183" si="90">+B182</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C183" s="12">
         <f t="shared" si="90"/>
@@ -16248,7 +16247,7 @@
       </c>
       <c r="B184" s="8">
         <f t="shared" ref="B184:C184" si="91">+B183</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C184" s="12">
         <f t="shared" si="91"/>
@@ -16266,7 +16265,7 @@
       </c>
       <c r="B185" s="8">
         <f t="shared" ref="B185:C185" si="92">+B184</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C185" s="12">
         <f t="shared" si="92"/>
@@ -16284,7 +16283,7 @@
       </c>
       <c r="B186" s="8">
         <f t="shared" ref="B186:C186" si="93">+B185</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C186" s="12">
         <f t="shared" si="93"/>
@@ -16302,7 +16301,7 @@
       </c>
       <c r="B187" s="8">
         <f t="shared" ref="B187:C187" si="94">+B186</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C187" s="12">
         <f t="shared" si="94"/>
@@ -16320,7 +16319,7 @@
       </c>
       <c r="B188" s="8">
         <f t="shared" ref="B188:C188" si="95">+B187</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C188" s="12">
         <f t="shared" si="95"/>
@@ -16338,7 +16337,7 @@
       </c>
       <c r="B189" s="8">
         <f t="shared" ref="B189:C189" si="96">+B188</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C189" s="12">
         <f t="shared" si="96"/>
@@ -16356,7 +16355,7 @@
       </c>
       <c r="B190" s="8">
         <f t="shared" ref="B190:C190" si="97">+B189</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C190" s="12">
         <f t="shared" si="97"/>
@@ -16374,7 +16373,7 @@
       </c>
       <c r="B191" s="8">
         <f t="shared" ref="B191:C191" si="98">+B190</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C191" s="12">
         <f t="shared" si="98"/>
@@ -16392,7 +16391,7 @@
       </c>
       <c r="B192" s="8">
         <f t="shared" ref="B192:C192" si="99">+B191</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C192" s="12">
         <f t="shared" si="99"/>
@@ -16410,7 +16409,7 @@
       </c>
       <c r="B193" s="8">
         <f t="shared" ref="B193:C193" si="100">+B192</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C193" s="12">
         <f t="shared" si="100"/>
@@ -16428,7 +16427,7 @@
       </c>
       <c r="B194" s="8">
         <f t="shared" ref="B194:C194" si="101">+B193</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C194" s="12">
         <f t="shared" si="101"/>
@@ -16446,7 +16445,7 @@
       </c>
       <c r="B195" s="8">
         <f t="shared" ref="B195:C195" si="102">+B194</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C195" s="12">
         <f t="shared" si="102"/>
@@ -16464,7 +16463,7 @@
       </c>
       <c r="B196" s="8">
         <f t="shared" ref="B196:D200" si="103">+B195</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C196" s="12">
         <f t="shared" si="103"/>
@@ -16482,7 +16481,7 @@
       </c>
       <c r="B197" s="8">
         <f t="shared" ref="B197:C197" si="104">+B196</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C197" s="12">
         <f t="shared" si="104"/>
@@ -16500,7 +16499,7 @@
       </c>
       <c r="B198" s="8">
         <f t="shared" ref="B198:C198" si="105">+B197</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C198" s="12">
         <f t="shared" si="105"/>
@@ -16518,7 +16517,7 @@
       </c>
       <c r="B199" s="8">
         <f t="shared" ref="B199:C199" si="106">+B198</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C199" s="12">
         <f t="shared" si="106"/>
@@ -16536,7 +16535,7 @@
       </c>
       <c r="B200" s="8">
         <f t="shared" ref="B200:C200" si="107">+B199</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C200" s="12">
         <f t="shared" si="107"/>

--- a/input_examples/distanceDependency_square_amp.xlsx
+++ b/input_examples/distanceDependency_square_amp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\SelfImaging\input_examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6474C75-A6A1-4811-A5B8-77350028CB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2431E3D2-1EB0-4AA9-9E14-2EA37F18DC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grating" sheetId="1" r:id="rId1"/>
@@ -730,9 +730,7 @@
       <c r="E2" s="8">
         <v>1.5</v>
       </c>
-      <c r="F2" s="19">
-        <v>0</v>
-      </c>
+      <c r="F2" s="19"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="str">
@@ -7343,10 +7341,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C2" s="8">
         <v>0</v>
@@ -7359,11 +7357,11 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <f t="shared" ref="A3:D66" si="0">+A2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C3" s="8">
         <f>+C2</f>
@@ -7377,11 +7375,11 @@
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C4" s="8">
         <f t="shared" si="0"/>
@@ -7395,11 +7393,11 @@
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C5" s="8">
         <f t="shared" si="0"/>
@@ -7413,11 +7411,11 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C6" s="8">
         <f t="shared" si="0"/>
@@ -7431,11 +7429,11 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C7" s="8">
         <f t="shared" si="0"/>
@@ -7449,11 +7447,11 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C8" s="8">
         <f t="shared" si="0"/>
@@ -7467,11 +7465,11 @@
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C9" s="8">
         <f t="shared" si="0"/>
@@ -7485,11 +7483,11 @@
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C10" s="8">
         <f t="shared" si="0"/>
@@ -7503,11 +7501,11 @@
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C11" s="8">
         <f t="shared" si="0"/>
@@ -7521,11 +7519,11 @@
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C12" s="8">
         <f t="shared" si="0"/>
@@ -7539,11 +7537,11 @@
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B13" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C13" s="8">
         <f t="shared" si="0"/>
@@ -7557,11 +7555,11 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B14" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C14" s="8">
         <f t="shared" si="0"/>
@@ -7575,11 +7573,11 @@
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C15" s="8">
         <f t="shared" si="0"/>
@@ -7593,11 +7591,11 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C16" s="8">
         <f t="shared" si="0"/>
@@ -7611,11 +7609,11 @@
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C17" s="8">
         <f t="shared" si="0"/>
@@ -7629,11 +7627,11 @@
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B18" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C18" s="8">
         <f t="shared" si="0"/>
@@ -7647,11 +7645,11 @@
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B19" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C19" s="8">
         <f t="shared" si="0"/>
@@ -7665,11 +7663,11 @@
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B20" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C20" s="8">
         <f t="shared" si="0"/>
@@ -7683,11 +7681,11 @@
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B21" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C21" s="8">
         <f t="shared" si="0"/>
@@ -7701,11 +7699,11 @@
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B22" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C22" s="8">
         <f t="shared" si="0"/>
@@ -7719,11 +7717,11 @@
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B23" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C23" s="8">
         <f t="shared" si="0"/>
@@ -7737,11 +7735,11 @@
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B24" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C24" s="8">
         <f t="shared" si="0"/>
@@ -7755,11 +7753,11 @@
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B25" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C25" s="8">
         <f t="shared" si="0"/>
@@ -7773,11 +7771,11 @@
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C26" s="8">
         <f t="shared" si="0"/>
@@ -7791,11 +7789,11 @@
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C27" s="8">
         <f t="shared" si="0"/>
@@ -7809,11 +7807,11 @@
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B28" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C28" s="8">
         <f t="shared" si="0"/>
@@ -7827,11 +7825,11 @@
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C29" s="8">
         <f t="shared" si="0"/>
@@ -7845,11 +7843,11 @@
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C30" s="8">
         <f t="shared" si="0"/>
@@ -7863,11 +7861,11 @@
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B31" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C31" s="8">
         <f t="shared" si="0"/>
@@ -7881,11 +7879,11 @@
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C32" s="8">
         <f t="shared" si="0"/>
@@ -7899,11 +7897,11 @@
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C33" s="8">
         <f t="shared" si="0"/>
@@ -7917,11 +7915,11 @@
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C34" s="8">
         <f t="shared" si="0"/>
@@ -7935,11 +7933,11 @@
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B35" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C35" s="8">
         <f t="shared" si="0"/>
@@ -7953,11 +7951,11 @@
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C36" s="8">
         <f t="shared" si="0"/>
@@ -7971,11 +7969,11 @@
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C37" s="8">
         <f t="shared" si="0"/>
@@ -7989,11 +7987,11 @@
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C38" s="8">
         <f t="shared" si="0"/>
@@ -8007,11 +8005,11 @@
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C39" s="8">
         <f t="shared" si="0"/>
@@ -8025,11 +8023,11 @@
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C40" s="8">
         <f t="shared" si="0"/>
@@ -8043,11 +8041,11 @@
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C41" s="8">
         <f t="shared" si="0"/>
@@ -8061,11 +8059,11 @@
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C42" s="8">
         <f t="shared" si="0"/>
@@ -8079,11 +8077,11 @@
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C43" s="8">
         <f t="shared" si="0"/>
@@ -8097,11 +8095,11 @@
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C44" s="8">
         <f t="shared" si="0"/>
@@ -8115,11 +8113,11 @@
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C45" s="8">
         <f t="shared" si="0"/>
@@ -8133,11 +8131,11 @@
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C46" s="8">
         <f t="shared" si="0"/>
@@ -8151,11 +8149,11 @@
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C47" s="8">
         <f t="shared" si="0"/>
@@ -8169,11 +8167,11 @@
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C48" s="8">
         <f t="shared" si="0"/>
@@ -8187,11 +8185,11 @@
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B49" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C49" s="8">
         <f t="shared" si="0"/>
@@ -8205,11 +8203,11 @@
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C50" s="8">
         <f t="shared" si="0"/>
@@ -8223,11 +8221,11 @@
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B51" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C51" s="8">
         <f t="shared" si="0"/>
@@ -8241,11 +8239,11 @@
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B52" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C52" s="8">
         <f t="shared" si="0"/>
@@ -8259,11 +8257,11 @@
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B53" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C53" s="8">
         <f t="shared" si="0"/>
@@ -8277,11 +8275,11 @@
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B54" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C54" s="8">
         <f t="shared" si="0"/>
@@ -8295,11 +8293,11 @@
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B55" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C55" s="8">
         <f t="shared" si="0"/>
@@ -8313,11 +8311,11 @@
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B56" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C56" s="8">
         <f t="shared" si="0"/>
@@ -8331,11 +8329,11 @@
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B57" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C57" s="8">
         <f t="shared" si="0"/>
@@ -8349,11 +8347,11 @@
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B58" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C58" s="8">
         <f t="shared" si="0"/>
@@ -8367,11 +8365,11 @@
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C59" s="8">
         <f t="shared" si="0"/>
@@ -8385,11 +8383,11 @@
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B60" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C60" s="8">
         <f t="shared" si="0"/>
@@ -8403,11 +8401,11 @@
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C61" s="8">
         <f t="shared" si="0"/>
@@ -8421,11 +8419,11 @@
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C62" s="8">
         <f t="shared" si="0"/>
@@ -8439,11 +8437,11 @@
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B63" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C63" s="8">
         <f t="shared" si="0"/>
@@ -8457,11 +8455,11 @@
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B64" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C64" s="8">
         <f t="shared" si="0"/>
@@ -8475,11 +8473,11 @@
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B65" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C65" s="8">
         <f t="shared" si="0"/>
@@ -8493,11 +8491,11 @@
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B66" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C66" s="8">
         <f t="shared" si="0"/>
@@ -8511,11 +8509,11 @@
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <f t="shared" ref="A67:D100" si="2">+A66</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B67" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C67" s="8">
         <f t="shared" si="2"/>
@@ -8529,11 +8527,11 @@
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B68" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C68" s="8">
         <f t="shared" si="2"/>
@@ -8547,11 +8545,11 @@
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B69" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C69" s="8">
         <f t="shared" si="2"/>
@@ -8565,11 +8563,11 @@
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B70" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C70" s="8">
         <f t="shared" si="2"/>
@@ -8583,11 +8581,11 @@
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B71" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C71" s="8">
         <f t="shared" si="2"/>
@@ -8601,11 +8599,11 @@
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B72" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C72" s="8">
         <f t="shared" si="2"/>
@@ -8619,11 +8617,11 @@
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B73" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C73" s="8">
         <f t="shared" si="2"/>
@@ -8637,11 +8635,11 @@
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B74" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C74" s="8">
         <f t="shared" si="2"/>
@@ -8655,11 +8653,11 @@
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B75" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C75" s="8">
         <f t="shared" si="2"/>
@@ -8673,11 +8671,11 @@
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B76" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C76" s="8">
         <f t="shared" si="2"/>
@@ -8691,11 +8689,11 @@
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B77" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C77" s="8">
         <f t="shared" si="2"/>
@@ -8709,11 +8707,11 @@
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B78" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C78" s="8">
         <f t="shared" si="2"/>
@@ -8727,11 +8725,11 @@
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B79" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C79" s="8">
         <f t="shared" si="2"/>
@@ -8745,11 +8743,11 @@
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B80" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C80" s="8">
         <f t="shared" si="2"/>
@@ -8763,11 +8761,11 @@
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B81" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C81" s="8">
         <f t="shared" si="2"/>
@@ -8781,11 +8779,11 @@
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B82" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C82" s="8">
         <f t="shared" si="2"/>
@@ -8799,11 +8797,11 @@
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B83" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C83" s="8">
         <f t="shared" si="2"/>
@@ -8817,11 +8815,11 @@
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B84" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C84" s="8">
         <f t="shared" si="2"/>
@@ -8835,11 +8833,11 @@
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B85" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C85" s="8">
         <f t="shared" si="2"/>
@@ -8853,11 +8851,11 @@
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B86" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C86" s="8">
         <f t="shared" si="2"/>
@@ -8871,11 +8869,11 @@
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B87" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C87" s="8">
         <f t="shared" si="2"/>
@@ -8889,11 +8887,11 @@
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B88" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C88" s="8">
         <f t="shared" si="2"/>
@@ -8907,11 +8905,11 @@
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B89" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C89" s="8">
         <f t="shared" si="2"/>
@@ -8925,11 +8923,11 @@
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B90" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C90" s="8">
         <f t="shared" si="2"/>
@@ -8943,11 +8941,11 @@
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B91" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C91" s="8">
         <f t="shared" si="2"/>
@@ -8961,11 +8959,11 @@
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B92" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C92" s="8">
         <f t="shared" si="2"/>
@@ -8979,11 +8977,11 @@
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B93" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C93" s="8">
         <f t="shared" si="2"/>
@@ -8997,11 +8995,11 @@
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B94" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C94" s="8">
         <f t="shared" si="2"/>
@@ -9015,11 +9013,11 @@
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B95" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C95" s="8">
         <f t="shared" si="2"/>
@@ -9033,11 +9031,11 @@
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B96" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C96" s="8">
         <f t="shared" si="2"/>
@@ -9051,11 +9049,11 @@
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B97" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C97" s="8">
         <f t="shared" si="2"/>
@@ -9069,11 +9067,11 @@
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B98" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C98" s="8">
         <f t="shared" si="2"/>
@@ -9087,11 +9085,11 @@
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B99" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C99" s="8">
         <f t="shared" si="2"/>
@@ -9105,11 +9103,11 @@
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B100" s="8">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C100" s="8">
         <f t="shared" si="2"/>
@@ -9123,11 +9121,11 @@
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
         <f t="shared" ref="A101:D101" si="3">+A100</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B101" s="8">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C101" s="8">
         <f t="shared" si="3"/>
@@ -9141,11 +9139,11 @@
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
         <f t="shared" ref="A102:D102" si="4">+A101</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B102" s="8">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C102" s="8">
         <f t="shared" si="4"/>
@@ -9159,11 +9157,11 @@
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
         <f t="shared" ref="A103:D103" si="5">+A102</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B103" s="8">
         <f t="shared" si="5"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C103" s="8">
         <f t="shared" si="5"/>
@@ -9177,11 +9175,11 @@
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="8">
         <f t="shared" ref="A104:D104" si="6">+A103</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B104" s="8">
         <f t="shared" si="6"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C104" s="8">
         <f t="shared" si="6"/>
@@ -9195,11 +9193,11 @@
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
         <f t="shared" ref="A105:D105" si="7">+A104</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B105" s="8">
         <f t="shared" si="7"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C105" s="8">
         <f t="shared" si="7"/>
@@ -9213,11 +9211,11 @@
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="8">
         <f t="shared" ref="A106:D106" si="8">+A105</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B106" s="8">
         <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C106" s="8">
         <f t="shared" si="8"/>
@@ -9231,11 +9229,11 @@
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
         <f t="shared" ref="A107:D107" si="9">+A106</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B107" s="8">
         <f t="shared" si="9"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C107" s="8">
         <f t="shared" si="9"/>
@@ -9249,11 +9247,11 @@
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="8">
         <f t="shared" ref="A108:D108" si="10">+A107</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B108" s="8">
         <f t="shared" si="10"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C108" s="8">
         <f t="shared" si="10"/>
@@ -9267,11 +9265,11 @@
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
         <f t="shared" ref="A109:D109" si="11">+A108</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B109" s="8">
         <f t="shared" si="11"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C109" s="8">
         <f t="shared" si="11"/>
@@ -9285,11 +9283,11 @@
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="8">
         <f t="shared" ref="A110:D110" si="12">+A109</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B110" s="8">
         <f t="shared" si="12"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C110" s="8">
         <f t="shared" si="12"/>
@@ -9303,11 +9301,11 @@
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
         <f t="shared" ref="A111:D111" si="13">+A110</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B111" s="8">
         <f t="shared" si="13"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C111" s="8">
         <f t="shared" si="13"/>
@@ -9321,11 +9319,11 @@
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="8">
         <f t="shared" ref="A112:D112" si="14">+A111</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B112" s="8">
         <f t="shared" si="14"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C112" s="8">
         <f t="shared" si="14"/>
@@ -9339,11 +9337,11 @@
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
         <f t="shared" ref="A113:D113" si="15">+A112</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B113" s="8">
         <f t="shared" si="15"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C113" s="8">
         <f t="shared" si="15"/>
@@ -9357,11 +9355,11 @@
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="8">
         <f t="shared" ref="A114:D114" si="16">+A113</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B114" s="8">
         <f t="shared" si="16"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C114" s="8">
         <f t="shared" si="16"/>
@@ -9375,11 +9373,11 @@
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
         <f t="shared" ref="A115:D115" si="17">+A114</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B115" s="8">
         <f t="shared" si="17"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C115" s="8">
         <f t="shared" si="17"/>
@@ -9393,11 +9391,11 @@
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="8">
         <f t="shared" ref="A116:D116" si="18">+A115</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B116" s="8">
         <f t="shared" si="18"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C116" s="8">
         <f t="shared" si="18"/>
@@ -9411,11 +9409,11 @@
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="8">
         <f t="shared" ref="A117:D117" si="19">+A116</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B117" s="8">
         <f t="shared" si="19"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C117" s="8">
         <f t="shared" si="19"/>
@@ -9429,11 +9427,11 @@
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
         <f t="shared" ref="A118:D118" si="20">+A117</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B118" s="8">
         <f t="shared" si="20"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C118" s="8">
         <f t="shared" si="20"/>
@@ -9447,11 +9445,11 @@
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="8">
         <f t="shared" ref="A119:D119" si="21">+A118</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B119" s="8">
         <f t="shared" si="21"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C119" s="8">
         <f t="shared" si="21"/>
@@ -9465,11 +9463,11 @@
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
         <f t="shared" ref="A120:D120" si="22">+A119</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B120" s="8">
         <f t="shared" si="22"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C120" s="8">
         <f t="shared" si="22"/>
@@ -9483,11 +9481,11 @@
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="8">
         <f t="shared" ref="A121:D121" si="23">+A120</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B121" s="8">
         <f t="shared" si="23"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C121" s="8">
         <f t="shared" si="23"/>
@@ -9501,11 +9499,11 @@
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
         <f t="shared" ref="A122:D122" si="24">+A121</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B122" s="8">
         <f t="shared" si="24"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C122" s="8">
         <f t="shared" si="24"/>
@@ -9519,11 +9517,11 @@
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="8">
         <f t="shared" ref="A123:D123" si="25">+A122</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B123" s="8">
         <f t="shared" si="25"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C123" s="8">
         <f t="shared" si="25"/>
@@ -9537,11 +9535,11 @@
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
         <f t="shared" ref="A124:D124" si="26">+A123</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B124" s="8">
         <f t="shared" si="26"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C124" s="8">
         <f t="shared" si="26"/>
@@ -9555,11 +9553,11 @@
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="8">
         <f t="shared" ref="A125:D125" si="27">+A124</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B125" s="8">
         <f t="shared" si="27"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C125" s="8">
         <f t="shared" si="27"/>
@@ -9573,11 +9571,11 @@
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="8">
         <f t="shared" ref="A126:D126" si="28">+A125</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B126" s="8">
         <f t="shared" si="28"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C126" s="8">
         <f t="shared" si="28"/>
@@ -9591,11 +9589,11 @@
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
         <f t="shared" ref="A127:D127" si="29">+A126</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B127" s="8">
         <f t="shared" si="29"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C127" s="8">
         <f t="shared" si="29"/>
@@ -9609,11 +9607,11 @@
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
         <f t="shared" ref="A128:D128" si="30">+A127</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B128" s="8">
         <f t="shared" si="30"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C128" s="8">
         <f t="shared" si="30"/>
@@ -9627,11 +9625,11 @@
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
         <f t="shared" ref="A129:D129" si="31">+A128</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B129" s="8">
         <f t="shared" si="31"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C129" s="8">
         <f t="shared" si="31"/>
@@ -9645,11 +9643,11 @@
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="8">
         <f t="shared" ref="A130:D130" si="32">+A129</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B130" s="8">
         <f t="shared" si="32"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C130" s="8">
         <f t="shared" si="32"/>
@@ -9663,11 +9661,11 @@
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
         <f t="shared" ref="A131:D131" si="33">+A130</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B131" s="8">
         <f t="shared" si="33"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C131" s="8">
         <f t="shared" si="33"/>
@@ -9681,11 +9679,11 @@
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
         <f t="shared" ref="A132:D132" si="34">+A131</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B132" s="8">
         <f t="shared" si="34"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C132" s="8">
         <f t="shared" si="34"/>
@@ -9699,11 +9697,11 @@
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
         <f t="shared" ref="A133:D133" si="35">+A132</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B133" s="8">
         <f t="shared" si="35"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C133" s="8">
         <f t="shared" si="35"/>
@@ -9717,11 +9715,11 @@
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
         <f t="shared" ref="A134:D134" si="36">+A133</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B134" s="8">
         <f t="shared" si="36"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C134" s="8">
         <f t="shared" si="36"/>
@@ -9735,11 +9733,11 @@
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
         <f t="shared" ref="A135:D135" si="37">+A134</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B135" s="8">
         <f t="shared" si="37"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C135" s="8">
         <f t="shared" si="37"/>
@@ -9753,11 +9751,11 @@
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
         <f t="shared" ref="A136:D136" si="38">+A135</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B136" s="8">
         <f t="shared" si="38"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C136" s="8">
         <f t="shared" si="38"/>
@@ -9771,11 +9769,11 @@
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
         <f t="shared" ref="A137:D137" si="39">+A136</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B137" s="8">
         <f t="shared" si="39"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C137" s="8">
         <f t="shared" si="39"/>
@@ -9789,11 +9787,11 @@
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
         <f t="shared" ref="A138:D138" si="40">+A137</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B138" s="8">
         <f t="shared" si="40"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C138" s="8">
         <f t="shared" si="40"/>
@@ -9807,11 +9805,11 @@
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
         <f t="shared" ref="A139:D139" si="41">+A138</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B139" s="8">
         <f t="shared" si="41"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C139" s="8">
         <f t="shared" si="41"/>
@@ -9825,11 +9823,11 @@
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
         <f t="shared" ref="A140:D140" si="42">+A139</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B140" s="8">
         <f t="shared" si="42"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C140" s="8">
         <f t="shared" si="42"/>
@@ -9843,11 +9841,11 @@
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
         <f t="shared" ref="A141:D141" si="43">+A140</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B141" s="8">
         <f t="shared" si="43"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C141" s="8">
         <f t="shared" si="43"/>
@@ -9861,11 +9859,11 @@
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
         <f t="shared" ref="A142:D142" si="44">+A141</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B142" s="8">
         <f t="shared" si="44"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C142" s="8">
         <f t="shared" si="44"/>
@@ -9879,11 +9877,11 @@
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
         <f t="shared" ref="A143:D143" si="45">+A142</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B143" s="8">
         <f t="shared" si="45"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C143" s="8">
         <f t="shared" si="45"/>
@@ -9897,11 +9895,11 @@
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
         <f t="shared" ref="A144:D144" si="46">+A143</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B144" s="8">
         <f t="shared" si="46"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C144" s="8">
         <f t="shared" si="46"/>
@@ -9915,11 +9913,11 @@
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
         <f t="shared" ref="A145:D145" si="47">+A144</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B145" s="8">
         <f t="shared" si="47"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C145" s="8">
         <f t="shared" si="47"/>
@@ -9933,11 +9931,11 @@
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
         <f t="shared" ref="A146:D146" si="48">+A145</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B146" s="8">
         <f t="shared" si="48"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C146" s="8">
         <f t="shared" si="48"/>
@@ -9951,11 +9949,11 @@
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
         <f t="shared" ref="A147:D147" si="49">+A146</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B147" s="8">
         <f t="shared" si="49"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C147" s="8">
         <f t="shared" si="49"/>
@@ -9969,11 +9967,11 @@
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
         <f t="shared" ref="A148:D148" si="50">+A147</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B148" s="8">
         <f t="shared" si="50"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C148" s="8">
         <f t="shared" si="50"/>
@@ -9987,11 +9985,11 @@
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
         <f t="shared" ref="A149:D149" si="51">+A148</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B149" s="8">
         <f t="shared" si="51"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C149" s="8">
         <f t="shared" si="51"/>
@@ -10005,11 +10003,11 @@
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
         <f t="shared" ref="A150:D150" si="52">+A149</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B150" s="8">
         <f t="shared" si="52"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C150" s="8">
         <f t="shared" si="52"/>
@@ -10023,11 +10021,11 @@
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
         <f t="shared" ref="A151:D151" si="53">+A150</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B151" s="8">
         <f t="shared" si="53"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C151" s="8">
         <f t="shared" si="53"/>
@@ -10041,11 +10039,11 @@
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
         <f t="shared" ref="A152:D152" si="54">+A151</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B152" s="8">
         <f t="shared" si="54"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C152" s="8">
         <f t="shared" si="54"/>
@@ -10059,11 +10057,11 @@
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
         <f t="shared" ref="A153:D153" si="55">+A152</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B153" s="8">
         <f t="shared" si="55"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C153" s="8">
         <f t="shared" si="55"/>
@@ -10077,11 +10075,11 @@
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
         <f t="shared" ref="A154:D154" si="56">+A153</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B154" s="8">
         <f t="shared" si="56"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C154" s="8">
         <f t="shared" si="56"/>
@@ -10095,11 +10093,11 @@
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
         <f t="shared" ref="A155:D155" si="57">+A154</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B155" s="8">
         <f t="shared" si="57"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C155" s="8">
         <f t="shared" si="57"/>
@@ -10113,11 +10111,11 @@
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
         <f t="shared" ref="A156:D156" si="58">+A155</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B156" s="8">
         <f t="shared" si="58"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C156" s="8">
         <f t="shared" si="58"/>
@@ -10131,11 +10129,11 @@
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
         <f t="shared" ref="A157:D157" si="59">+A156</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B157" s="8">
         <f t="shared" si="59"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C157" s="8">
         <f t="shared" si="59"/>
@@ -10149,11 +10147,11 @@
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
         <f t="shared" ref="A158:D158" si="60">+A157</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B158" s="8">
         <f t="shared" si="60"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C158" s="8">
         <f t="shared" si="60"/>
@@ -10167,11 +10165,11 @@
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
         <f t="shared" ref="A159:D159" si="61">+A158</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B159" s="8">
         <f t="shared" si="61"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C159" s="8">
         <f t="shared" si="61"/>
@@ -10185,11 +10183,11 @@
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
         <f t="shared" ref="A160:D160" si="62">+A159</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B160" s="8">
         <f t="shared" si="62"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C160" s="8">
         <f t="shared" si="62"/>
@@ -10203,11 +10201,11 @@
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
         <f t="shared" ref="A161:D161" si="63">+A160</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B161" s="8">
         <f t="shared" si="63"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C161" s="8">
         <f t="shared" si="63"/>
@@ -10221,11 +10219,11 @@
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
         <f t="shared" ref="A162:D162" si="64">+A161</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B162" s="8">
         <f t="shared" si="64"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C162" s="8">
         <f t="shared" si="64"/>
@@ -10239,11 +10237,11 @@
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
         <f t="shared" ref="A163:D163" si="65">+A162</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B163" s="8">
         <f t="shared" si="65"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C163" s="8">
         <f t="shared" si="65"/>
@@ -10257,11 +10255,11 @@
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
         <f t="shared" ref="A164:D164" si="66">+A163</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B164" s="8">
         <f t="shared" si="66"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C164" s="8">
         <f t="shared" si="66"/>
@@ -10275,11 +10273,11 @@
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
         <f t="shared" ref="A165:D165" si="67">+A164</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B165" s="8">
         <f t="shared" si="67"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C165" s="8">
         <f t="shared" si="67"/>
@@ -10293,11 +10291,11 @@
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
         <f t="shared" ref="A166:D166" si="68">+A165</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B166" s="8">
         <f t="shared" si="68"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C166" s="8">
         <f t="shared" si="68"/>
@@ -10311,11 +10309,11 @@
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
         <f t="shared" ref="A167:D167" si="69">+A166</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B167" s="8">
         <f t="shared" si="69"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C167" s="8">
         <f t="shared" si="69"/>
@@ -10329,11 +10327,11 @@
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
         <f t="shared" ref="A168:D168" si="70">+A167</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B168" s="8">
         <f t="shared" si="70"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C168" s="8">
         <f t="shared" si="70"/>
@@ -10347,11 +10345,11 @@
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
         <f t="shared" ref="A169:D169" si="71">+A168</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B169" s="8">
         <f t="shared" si="71"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C169" s="8">
         <f t="shared" si="71"/>
@@ -10365,11 +10363,11 @@
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="8">
         <f t="shared" ref="A170:D170" si="72">+A169</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B170" s="8">
         <f t="shared" si="72"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C170" s="8">
         <f t="shared" si="72"/>
@@ -10383,11 +10381,11 @@
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="8">
         <f t="shared" ref="A171:D171" si="73">+A170</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B171" s="8">
         <f t="shared" si="73"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C171" s="8">
         <f t="shared" si="73"/>
@@ -10401,11 +10399,11 @@
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="8">
         <f t="shared" ref="A172:D172" si="74">+A171</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B172" s="8">
         <f t="shared" si="74"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C172" s="8">
         <f t="shared" si="74"/>
@@ -10419,11 +10417,11 @@
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="8">
         <f t="shared" ref="A173:D173" si="75">+A172</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B173" s="8">
         <f t="shared" si="75"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C173" s="8">
         <f t="shared" si="75"/>
@@ -10437,11 +10435,11 @@
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="8">
         <f t="shared" ref="A174:D174" si="76">+A173</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B174" s="8">
         <f t="shared" si="76"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C174" s="8">
         <f t="shared" si="76"/>
@@ -10455,11 +10453,11 @@
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="8">
         <f t="shared" ref="A175:D175" si="77">+A174</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B175" s="8">
         <f t="shared" si="77"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C175" s="8">
         <f t="shared" si="77"/>
@@ -10473,11 +10471,11 @@
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="8">
         <f t="shared" ref="A176:D176" si="78">+A175</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B176" s="8">
         <f t="shared" si="78"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C176" s="8">
         <f t="shared" si="78"/>
@@ -10491,11 +10489,11 @@
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="8">
         <f t="shared" ref="A177:D177" si="79">+A176</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B177" s="8">
         <f t="shared" si="79"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C177" s="8">
         <f t="shared" si="79"/>
@@ -10509,11 +10507,11 @@
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="8">
         <f t="shared" ref="A178:D178" si="80">+A177</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B178" s="8">
         <f t="shared" si="80"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C178" s="8">
         <f t="shared" si="80"/>
@@ -10527,11 +10525,11 @@
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="8">
         <f t="shared" ref="A179:D179" si="81">+A178</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B179" s="8">
         <f t="shared" si="81"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C179" s="8">
         <f t="shared" si="81"/>
@@ -10545,11 +10543,11 @@
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="8">
         <f t="shared" ref="A180:D180" si="82">+A179</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B180" s="8">
         <f t="shared" si="82"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C180" s="8">
         <f t="shared" si="82"/>
@@ -10563,11 +10561,11 @@
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="8">
         <f t="shared" ref="A181:D181" si="83">+A180</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B181" s="8">
         <f t="shared" si="83"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C181" s="8">
         <f t="shared" si="83"/>
@@ -10581,11 +10579,11 @@
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="8">
         <f t="shared" ref="A182:D182" si="84">+A181</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B182" s="8">
         <f t="shared" si="84"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C182" s="8">
         <f t="shared" si="84"/>
@@ -10599,11 +10597,11 @@
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="8">
         <f t="shared" ref="A183:D183" si="85">+A182</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B183" s="8">
         <f t="shared" si="85"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C183" s="8">
         <f t="shared" si="85"/>
@@ -10617,11 +10615,11 @@
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="8">
         <f t="shared" ref="A184:D184" si="86">+A183</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B184" s="8">
         <f t="shared" si="86"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C184" s="8">
         <f t="shared" si="86"/>
@@ -10635,11 +10633,11 @@
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="8">
         <f t="shared" ref="A185:D185" si="87">+A184</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B185" s="8">
         <f t="shared" si="87"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C185" s="8">
         <f t="shared" si="87"/>
@@ -10653,11 +10651,11 @@
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="8">
         <f t="shared" ref="A186:D186" si="88">+A185</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B186" s="8">
         <f t="shared" si="88"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C186" s="8">
         <f t="shared" si="88"/>
@@ -10671,11 +10669,11 @@
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="8">
         <f t="shared" ref="A187:D187" si="89">+A186</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B187" s="8">
         <f t="shared" si="89"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C187" s="8">
         <f t="shared" si="89"/>
@@ -10689,11 +10687,11 @@
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="8">
         <f t="shared" ref="A188:D188" si="90">+A187</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B188" s="8">
         <f t="shared" si="90"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C188" s="8">
         <f t="shared" si="90"/>
@@ -10707,11 +10705,11 @@
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="8">
         <f t="shared" ref="A189:D189" si="91">+A188</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B189" s="8">
         <f t="shared" si="91"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C189" s="8">
         <f t="shared" si="91"/>
@@ -10725,11 +10723,11 @@
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="8">
         <f t="shared" ref="A190:D190" si="92">+A189</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B190" s="8">
         <f t="shared" si="92"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C190" s="8">
         <f t="shared" si="92"/>
@@ -10743,11 +10741,11 @@
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="8">
         <f t="shared" ref="A191:D191" si="93">+A190</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B191" s="8">
         <f t="shared" si="93"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C191" s="8">
         <f t="shared" si="93"/>
@@ -10761,11 +10759,11 @@
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="8">
         <f t="shared" ref="A192:D192" si="94">+A191</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B192" s="8">
         <f t="shared" si="94"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C192" s="8">
         <f t="shared" si="94"/>
@@ -10779,11 +10777,11 @@
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="8">
         <f t="shared" ref="A193:D193" si="95">+A192</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B193" s="8">
         <f t="shared" si="95"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C193" s="8">
         <f t="shared" si="95"/>
@@ -10797,11 +10795,11 @@
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="8">
         <f t="shared" ref="A194:D194" si="96">+A193</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B194" s="8">
         <f t="shared" si="96"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C194" s="8">
         <f t="shared" si="96"/>
@@ -10815,11 +10813,11 @@
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="8">
         <f t="shared" ref="A195:D195" si="97">+A194</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B195" s="8">
         <f t="shared" si="97"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C195" s="8">
         <f t="shared" si="97"/>
@@ -10833,11 +10831,11 @@
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="8">
         <f t="shared" ref="A196:D196" si="98">+A195</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B196" s="8">
         <f t="shared" si="98"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C196" s="8">
         <f t="shared" si="98"/>
@@ -10851,11 +10849,11 @@
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="8">
         <f t="shared" ref="A197:D197" si="99">+A196</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B197" s="8">
         <f t="shared" si="99"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C197" s="8">
         <f t="shared" si="99"/>
@@ -10869,11 +10867,11 @@
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="8">
         <f t="shared" ref="A198:D198" si="100">+A197</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B198" s="8">
         <f t="shared" si="100"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C198" s="8">
         <f t="shared" si="100"/>
@@ -10887,11 +10885,11 @@
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="8">
         <f t="shared" ref="A199:D199" si="101">+A198</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B199" s="8">
         <f t="shared" si="101"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C199" s="8">
         <f t="shared" si="101"/>
@@ -10905,11 +10903,11 @@
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="8">
         <f t="shared" ref="A200:D200" si="102">+A199</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B200" s="8">
         <f t="shared" si="102"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C200" s="8">
         <f t="shared" si="102"/>
@@ -10952,1990 +10950,3581 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="8">
         <v>0</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8">
+        <f>-1/200</f>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <f>+A2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="8">
         <f>+B2</f>
         <v>0</v>
       </c>
+      <c r="C3" s="8">
+        <f>+C2</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="8">
+        <f>+D2</f>
+        <v>-5.0000000000000001E-3</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
-        <f t="shared" ref="A4:B67" si="0">+A3</f>
-        <v>0</v>
+        <f t="shared" ref="A4:D67" si="0">+A3</f>
+        <v>1</v>
       </c>
       <c r="B4" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C4" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C5" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D5" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C6" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D6" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D7" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C8" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D8" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C9" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D9" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C10" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D10" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C11" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C12" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D12" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B13" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C13" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B14" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C14" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D14" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="C15" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D16" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B18" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D18" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B19" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B20" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D20" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B21" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B22" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D22" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B23" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D23" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B24" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B25" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B26" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C27" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B28" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B31" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C32" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B33" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C33" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B35" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C36" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B37" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C37" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B39" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C43" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C44" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C45" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B46" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C46" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D46" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B47" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C47" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D47" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B48" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C48" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D48" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B49" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C49" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D49" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B50" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C50" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D50" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B51" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C51" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D51" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B52" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C52" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D52" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B53" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C53" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D53" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B54" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C54" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D54" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B55" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C55" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D55" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B56" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C56" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D56" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B57" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C57" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D57" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B58" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C58" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D58" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B59" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C59" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D59" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B60" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C60" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D60" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C61" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D61" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C62" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D62" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B63" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C63" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D63" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B64" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C64" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D64" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B65" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C65" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D65" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B66" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C66" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D66" s="8">
+        <f t="shared" si="0"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B67" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C67" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D67" s="8">
+        <f t="shared" ref="D67:D68" si="1">+D66</f>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
-        <f t="shared" ref="A68:B100" si="1">+A67</f>
-        <v>0</v>
+        <f t="shared" ref="A68:D100" si="2">+A67</f>
+        <v>1</v>
       </c>
       <c r="B68" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C68" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D68" s="8">
+        <f t="shared" si="1"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B69" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C69" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D69" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B70" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C70" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D70" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B71" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C71" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D71" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B72" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C72" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D72" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B73" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C73" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D73" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B74" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C74" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D74" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B75" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C75" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D75" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B76" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C76" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D76" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B77" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C77" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D77" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B78" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C78" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D78" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B79" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C79" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D79" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B80" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C80" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D80" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B81" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C81" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D81" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B82" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C82" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D82" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B83" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C83" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D83" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B84" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C84" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D84" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B85" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C85" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D85" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B86" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C86" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D86" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B87" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C87" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D87" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B88" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C88" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D88" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B89" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C89" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D89" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B90" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D90" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B91" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C91" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D91" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B92" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C92" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D92" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B93" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C93" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D93" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B94" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D94" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B95" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C95" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D95" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B96" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C96" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D96" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B97" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D97" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B98" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C98" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D98" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B99" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C99" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D99" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="B100" s="8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C100" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D100" s="8">
+        <f t="shared" si="2"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="8">
-        <f t="shared" ref="A101:B101" si="2">+A100</f>
-        <v>0</v>
+        <f t="shared" ref="A101:D116" si="3">+A100</f>
+        <v>1</v>
       </c>
       <c r="B101" s="8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="C101" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D101" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="8">
-        <f t="shared" ref="A102:B102" si="3">+A101</f>
-        <v>0</v>
+        <f t="shared" ref="A102:B102" si="4">+A101</f>
+        <v>1</v>
       </c>
       <c r="B102" s="8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="C102" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D102" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="8">
-        <f t="shared" ref="A103:B103" si="4">+A102</f>
-        <v>0</v>
+        <f t="shared" ref="A103:B103" si="5">+A102</f>
+        <v>1</v>
       </c>
       <c r="B103" s="8">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C103" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D103" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="8">
-        <f t="shared" ref="A104:B104" si="5">+A103</f>
-        <v>0</v>
+        <f t="shared" ref="A104:B104" si="6">+A103</f>
+        <v>1</v>
       </c>
       <c r="B104" s="8">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="C104" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D104" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="8">
-        <f t="shared" ref="A105:B105" si="6">+A104</f>
-        <v>0</v>
+        <f t="shared" ref="A105:B105" si="7">+A104</f>
+        <v>1</v>
       </c>
       <c r="B105" s="8">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="C105" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D105" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="8">
-        <f t="shared" ref="A106:B106" si="7">+A105</f>
-        <v>0</v>
+        <f t="shared" ref="A106:B106" si="8">+A105</f>
+        <v>1</v>
       </c>
       <c r="B106" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="C106" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D106" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="8">
-        <f t="shared" ref="A107:B107" si="8">+A106</f>
-        <v>0</v>
+        <f t="shared" ref="A107:B107" si="9">+A106</f>
+        <v>1</v>
       </c>
       <c r="B107" s="8">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="C107" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D107" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="8">
-        <f t="shared" ref="A108:B108" si="9">+A107</f>
-        <v>0</v>
+        <f t="shared" ref="A108:B108" si="10">+A107</f>
+        <v>1</v>
       </c>
       <c r="B108" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="C108" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D108" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="8">
-        <f t="shared" ref="A109:B109" si="10">+A108</f>
-        <v>0</v>
+        <f t="shared" ref="A109:B109" si="11">+A108</f>
+        <v>1</v>
       </c>
       <c r="B109" s="8">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="C109" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D109" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="8">
-        <f t="shared" ref="A110:B110" si="11">+A109</f>
-        <v>0</v>
+        <f t="shared" ref="A110:B110" si="12">+A109</f>
+        <v>1</v>
       </c>
       <c r="B110" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="C110" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D110" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="8">
-        <f t="shared" ref="A111:B111" si="12">+A110</f>
-        <v>0</v>
+        <f t="shared" ref="A111:B111" si="13">+A110</f>
+        <v>1</v>
       </c>
       <c r="B111" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="C111" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D111" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="8">
-        <f t="shared" ref="A112:B112" si="13">+A111</f>
-        <v>0</v>
+        <f t="shared" ref="A112:B112" si="14">+A111</f>
+        <v>1</v>
       </c>
       <c r="B112" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="C112" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D112" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="8">
-        <f t="shared" ref="A113:B113" si="14">+A112</f>
-        <v>0</v>
+        <f t="shared" ref="A113:B113" si="15">+A112</f>
+        <v>1</v>
       </c>
       <c r="B113" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="C113" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D113" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="8">
-        <f t="shared" ref="A114:B114" si="15">+A113</f>
-        <v>0</v>
+        <f t="shared" ref="A114:B114" si="16">+A113</f>
+        <v>1</v>
       </c>
       <c r="B114" s="8">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="C114" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D114" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="8">
-        <f t="shared" ref="A115:B115" si="16">+A114</f>
-        <v>0</v>
+        <f t="shared" ref="A115:B115" si="17">+A114</f>
+        <v>1</v>
       </c>
       <c r="B115" s="8">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="C115" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D115" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="8">
-        <f t="shared" ref="A116:B116" si="17">+A115</f>
-        <v>0</v>
+        <f t="shared" ref="A116:B116" si="18">+A115</f>
+        <v>1</v>
       </c>
       <c r="B116" s="8">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="C116" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="D116" s="8">
+        <f t="shared" si="3"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="8">
-        <f t="shared" ref="A117:B117" si="18">+A116</f>
-        <v>0</v>
+        <f t="shared" ref="A117:D132" si="19">+A116</f>
+        <v>1</v>
       </c>
       <c r="B117" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="C117" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D117" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="8">
-        <f t="shared" ref="A118:B118" si="19">+A117</f>
-        <v>0</v>
+        <f t="shared" ref="A118:B118" si="20">+A117</f>
+        <v>1</v>
       </c>
       <c r="B118" s="8">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="C118" s="8">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D118" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="8">
-        <f t="shared" ref="A119:B119" si="20">+A118</f>
-        <v>0</v>
+        <f t="shared" ref="A119:B119" si="21">+A118</f>
+        <v>1</v>
       </c>
       <c r="B119" s="8">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="C119" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D119" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="8">
-        <f t="shared" ref="A120:B120" si="21">+A119</f>
-        <v>0</v>
+        <f t="shared" ref="A120:B120" si="22">+A119</f>
+        <v>1</v>
       </c>
       <c r="B120" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="C120" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D120" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="8">
-        <f t="shared" ref="A121:B121" si="22">+A120</f>
-        <v>0</v>
+        <f t="shared" ref="A121:B121" si="23">+A120</f>
+        <v>1</v>
       </c>
       <c r="B121" s="8">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="C121" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D121" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="8">
-        <f t="shared" ref="A122:B122" si="23">+A121</f>
-        <v>0</v>
+        <f t="shared" ref="A122:B122" si="24">+A121</f>
+        <v>1</v>
       </c>
       <c r="B122" s="8">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="C122" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D122" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="8">
-        <f t="shared" ref="A123:B123" si="24">+A122</f>
-        <v>0</v>
+        <f t="shared" ref="A123:B123" si="25">+A122</f>
+        <v>1</v>
       </c>
       <c r="B123" s="8">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="C123" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D123" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="8">
-        <f t="shared" ref="A124:B124" si="25">+A123</f>
-        <v>0</v>
+        <f t="shared" ref="A124:B124" si="26">+A123</f>
+        <v>1</v>
       </c>
       <c r="B124" s="8">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="C124" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D124" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="8">
-        <f t="shared" ref="A125:B125" si="26">+A124</f>
-        <v>0</v>
+        <f t="shared" ref="A125:B125" si="27">+A124</f>
+        <v>1</v>
       </c>
       <c r="B125" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="C125" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D125" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="8">
-        <f t="shared" ref="A126:B126" si="27">+A125</f>
-        <v>0</v>
+        <f t="shared" ref="A126:B126" si="28">+A125</f>
+        <v>1</v>
       </c>
       <c r="B126" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="C126" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D126" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="8">
-        <f t="shared" ref="A127:B127" si="28">+A126</f>
-        <v>0</v>
+        <f t="shared" ref="A127:B127" si="29">+A126</f>
+        <v>1</v>
       </c>
       <c r="B127" s="8">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="C127" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D127" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="8">
-        <f t="shared" ref="A128:B128" si="29">+A127</f>
-        <v>0</v>
+        <f t="shared" ref="A128:B128" si="30">+A127</f>
+        <v>1</v>
       </c>
       <c r="B128" s="8">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="C128" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D128" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="8">
-        <f t="shared" ref="A129:B129" si="30">+A128</f>
-        <v>0</v>
+        <f t="shared" ref="A129:B129" si="31">+A128</f>
+        <v>1</v>
       </c>
       <c r="B129" s="8">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="C129" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D129" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="8">
-        <f t="shared" ref="A130:B130" si="31">+A129</f>
-        <v>0</v>
+        <f t="shared" ref="A130:B130" si="32">+A129</f>
+        <v>1</v>
       </c>
       <c r="B130" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="C130" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D130" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="8">
-        <f t="shared" ref="A131:B131" si="32">+A130</f>
-        <v>0</v>
+        <f t="shared" ref="A131:B131" si="33">+A130</f>
+        <v>1</v>
       </c>
       <c r="B131" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="C131" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D131" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="8">
-        <f t="shared" ref="A132:B132" si="33">+A131</f>
-        <v>0</v>
+        <f t="shared" ref="A132:B132" si="34">+A131</f>
+        <v>1</v>
       </c>
       <c r="B132" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="C132" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="D132" s="8">
+        <f t="shared" si="19"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="8">
-        <f t="shared" ref="A133:B133" si="34">+A132</f>
-        <v>0</v>
+        <f t="shared" ref="A133:D148" si="35">+A132</f>
+        <v>1</v>
       </c>
       <c r="B133" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="C133" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D133" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="8">
-        <f t="shared" ref="A134:B134" si="35">+A133</f>
-        <v>0</v>
+        <f t="shared" ref="A134:B134" si="36">+A133</f>
+        <v>1</v>
       </c>
       <c r="B134" s="8">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="C134" s="8">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D134" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="8">
-        <f t="shared" ref="A135:B135" si="36">+A134</f>
-        <v>0</v>
+        <f t="shared" ref="A135:B135" si="37">+A134</f>
+        <v>1</v>
       </c>
       <c r="B135" s="8">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="C135" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D135" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="8">
-        <f t="shared" ref="A136:B136" si="37">+A135</f>
-        <v>0</v>
+        <f t="shared" ref="A136:B136" si="38">+A135</f>
+        <v>1</v>
       </c>
       <c r="B136" s="8">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="C136" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D136" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="8">
-        <f t="shared" ref="A137:B137" si="38">+A136</f>
-        <v>0</v>
+        <f t="shared" ref="A137:B137" si="39">+A136</f>
+        <v>1</v>
       </c>
       <c r="B137" s="8">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="C137" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D137" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="8">
-        <f t="shared" ref="A138:B138" si="39">+A137</f>
-        <v>0</v>
+        <f t="shared" ref="A138:B138" si="40">+A137</f>
+        <v>1</v>
       </c>
       <c r="B138" s="8">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="C138" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D138" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="8">
-        <f t="shared" ref="A139:B139" si="40">+A138</f>
-        <v>0</v>
+        <f t="shared" ref="A139:B139" si="41">+A138</f>
+        <v>1</v>
       </c>
       <c r="B139" s="8">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="C139" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D139" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="8">
-        <f t="shared" ref="A140:B140" si="41">+A139</f>
-        <v>0</v>
+        <f t="shared" ref="A140:B140" si="42">+A139</f>
+        <v>1</v>
       </c>
       <c r="B140" s="8">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="C140" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D140" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="8">
-        <f t="shared" ref="A141:B141" si="42">+A140</f>
-        <v>0</v>
+        <f t="shared" ref="A141:B141" si="43">+A140</f>
+        <v>1</v>
       </c>
       <c r="B141" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="C141" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D141" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="8">
-        <f t="shared" ref="A142:B142" si="43">+A141</f>
-        <v>0</v>
+        <f t="shared" ref="A142:B142" si="44">+A141</f>
+        <v>1</v>
       </c>
       <c r="B142" s="8">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="C142" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D142" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="8">
-        <f t="shared" ref="A143:B143" si="44">+A142</f>
-        <v>0</v>
+        <f t="shared" ref="A143:B143" si="45">+A142</f>
+        <v>1</v>
       </c>
       <c r="B143" s="8">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="C143" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D143" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="8">
-        <f t="shared" ref="A144:B144" si="45">+A143</f>
-        <v>0</v>
+        <f t="shared" ref="A144:B144" si="46">+A143</f>
+        <v>1</v>
       </c>
       <c r="B144" s="8">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="C144" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D144" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="8">
-        <f t="shared" ref="A145:B145" si="46">+A144</f>
-        <v>0</v>
+        <f t="shared" ref="A145:B145" si="47">+A144</f>
+        <v>1</v>
       </c>
       <c r="B145" s="8">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="C145" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D145" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="8">
-        <f t="shared" ref="A146:B146" si="47">+A145</f>
-        <v>0</v>
+        <f t="shared" ref="A146:B146" si="48">+A145</f>
+        <v>1</v>
       </c>
       <c r="B146" s="8">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="C146" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D146" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="8">
-        <f t="shared" ref="A147:B147" si="48">+A146</f>
-        <v>0</v>
+        <f t="shared" ref="A147:B147" si="49">+A146</f>
+        <v>1</v>
       </c>
       <c r="B147" s="8">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="C147" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D147" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="8">
-        <f t="shared" ref="A148:B148" si="49">+A147</f>
-        <v>0</v>
+        <f t="shared" ref="A148:B148" si="50">+A147</f>
+        <v>1</v>
       </c>
       <c r="B148" s="8">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="C148" s="8">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="D148" s="8">
+        <f t="shared" si="35"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="8">
-        <f t="shared" ref="A149:B149" si="50">+A148</f>
-        <v>0</v>
+        <f t="shared" ref="A149:D164" si="51">+A148</f>
+        <v>1</v>
       </c>
       <c r="B149" s="8">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="C149" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D149" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
-        <f t="shared" ref="A150:B150" si="51">+A149</f>
-        <v>0</v>
+        <f t="shared" ref="A150:B150" si="52">+A149</f>
+        <v>1</v>
       </c>
       <c r="B150" s="8">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="C150" s="8">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D150" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="8">
-        <f t="shared" ref="A151:B151" si="52">+A150</f>
-        <v>0</v>
+        <f t="shared" ref="A151:B151" si="53">+A150</f>
+        <v>1</v>
       </c>
       <c r="B151" s="8">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="C151" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D151" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="8">
-        <f t="shared" ref="A152:B152" si="53">+A151</f>
-        <v>0</v>
+        <f t="shared" ref="A152:B152" si="54">+A151</f>
+        <v>1</v>
       </c>
       <c r="B152" s="8">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="C152" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D152" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="8">
-        <f t="shared" ref="A153:B153" si="54">+A152</f>
-        <v>0</v>
+        <f t="shared" ref="A153:B153" si="55">+A152</f>
+        <v>1</v>
       </c>
       <c r="B153" s="8">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="C153" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D153" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="8">
-        <f t="shared" ref="A154:B154" si="55">+A153</f>
-        <v>0</v>
+        <f t="shared" ref="A154:B154" si="56">+A153</f>
+        <v>1</v>
       </c>
       <c r="B154" s="8">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="C154" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D154" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="8">
-        <f t="shared" ref="A155:B155" si="56">+A154</f>
-        <v>0</v>
+        <f t="shared" ref="A155:B155" si="57">+A154</f>
+        <v>1</v>
       </c>
       <c r="B155" s="8">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="C155" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D155" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="8">
-        <f t="shared" ref="A156:B156" si="57">+A155</f>
-        <v>0</v>
+        <f t="shared" ref="A156:B156" si="58">+A155</f>
+        <v>1</v>
       </c>
       <c r="B156" s="8">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="C156" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D156" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="8">
-        <f t="shared" ref="A157:B157" si="58">+A156</f>
-        <v>0</v>
+        <f t="shared" ref="A157:B157" si="59">+A156</f>
+        <v>1</v>
       </c>
       <c r="B157" s="8">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="C157" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D157" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="8">
-        <f t="shared" ref="A158:B158" si="59">+A157</f>
-        <v>0</v>
+        <f t="shared" ref="A158:B158" si="60">+A157</f>
+        <v>1</v>
       </c>
       <c r="B158" s="8">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="C158" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D158" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="8">
-        <f t="shared" ref="A159:B159" si="60">+A158</f>
-        <v>0</v>
+        <f t="shared" ref="A159:B159" si="61">+A158</f>
+        <v>1</v>
       </c>
       <c r="B159" s="8">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="C159" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D159" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="8">
-        <f t="shared" ref="A160:B160" si="61">+A159</f>
-        <v>0</v>
+        <f t="shared" ref="A160:B160" si="62">+A159</f>
+        <v>1</v>
       </c>
       <c r="B160" s="8">
-        <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="C160" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D160" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="8">
-        <f t="shared" ref="A161:B161" si="62">+A160</f>
-        <v>0</v>
+        <f t="shared" ref="A161:B161" si="63">+A160</f>
+        <v>1</v>
       </c>
       <c r="B161" s="8">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="C161" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D161" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="8">
-        <f t="shared" ref="A162:B162" si="63">+A161</f>
-        <v>0</v>
+        <f t="shared" ref="A162:B162" si="64">+A161</f>
+        <v>1</v>
       </c>
       <c r="B162" s="8">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="C162" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D162" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="8">
-        <f t="shared" ref="A163:B163" si="64">+A162</f>
-        <v>0</v>
+        <f t="shared" ref="A163:B163" si="65">+A162</f>
+        <v>1</v>
       </c>
       <c r="B163" s="8">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
+      <c r="C163" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D163" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="8">
-        <f t="shared" ref="A164:B164" si="65">+A163</f>
-        <v>0</v>
+        <f t="shared" ref="A164:B164" si="66">+A163</f>
+        <v>1</v>
       </c>
       <c r="B164" s="8">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="C164" s="8">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="D164" s="8">
+        <f t="shared" si="51"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
-        <f t="shared" ref="A165:B165" si="66">+A164</f>
-        <v>0</v>
+        <f t="shared" ref="A165:D180" si="67">+A164</f>
+        <v>1</v>
       </c>
       <c r="B165" s="8">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="C165" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D165" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
-        <f t="shared" ref="A166:B166" si="67">+A165</f>
-        <v>0</v>
+        <f t="shared" ref="A166:B166" si="68">+A165</f>
+        <v>1</v>
       </c>
       <c r="B166" s="8">
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="C166" s="8">
         <f t="shared" si="67"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D166" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
-        <f t="shared" ref="A167:B167" si="68">+A166</f>
-        <v>0</v>
+        <f t="shared" ref="A167:B167" si="69">+A166</f>
+        <v>1</v>
       </c>
       <c r="B167" s="8">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+      <c r="C167" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D167" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="8">
-        <f t="shared" ref="A168:B168" si="69">+A167</f>
-        <v>0</v>
+        <f t="shared" ref="A168:B168" si="70">+A167</f>
+        <v>1</v>
       </c>
       <c r="B168" s="8">
-        <f t="shared" si="69"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="70"/>
+        <v>0</v>
+      </c>
+      <c r="C168" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D168" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="8">
-        <f t="shared" ref="A169:B169" si="70">+A168</f>
-        <v>0</v>
+        <f t="shared" ref="A169:B169" si="71">+A168</f>
+        <v>1</v>
       </c>
       <c r="B169" s="8">
-        <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="71"/>
+        <v>0</v>
+      </c>
+      <c r="C169" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D169" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="8">
-        <f t="shared" ref="A170:B170" si="71">+A169</f>
-        <v>0</v>
+        <f t="shared" ref="A170:B170" si="72">+A169</f>
+        <v>1</v>
       </c>
       <c r="B170" s="8">
-        <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="C170" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D170" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="8">
-        <f t="shared" ref="A171:B171" si="72">+A170</f>
-        <v>0</v>
+        <f t="shared" ref="A171:B171" si="73">+A170</f>
+        <v>1</v>
       </c>
       <c r="B171" s="8">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="C171" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D171" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="8">
-        <f t="shared" ref="A172:B172" si="73">+A171</f>
-        <v>0</v>
+        <f t="shared" ref="A172:B172" si="74">+A171</f>
+        <v>1</v>
       </c>
       <c r="B172" s="8">
-        <f t="shared" si="73"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="C172" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D172" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="8">
-        <f t="shared" ref="A173:B173" si="74">+A172</f>
-        <v>0</v>
+        <f t="shared" ref="A173:B173" si="75">+A172</f>
+        <v>1</v>
       </c>
       <c r="B173" s="8">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="C173" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D173" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="8">
-        <f t="shared" ref="A174:B174" si="75">+A173</f>
-        <v>0</v>
+        <f t="shared" ref="A174:B174" si="76">+A173</f>
+        <v>1</v>
       </c>
       <c r="B174" s="8">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="76"/>
+        <v>0</v>
+      </c>
+      <c r="C174" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D174" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="8">
-        <f t="shared" ref="A175:B175" si="76">+A174</f>
-        <v>0</v>
+        <f t="shared" ref="A175:B175" si="77">+A174</f>
+        <v>1</v>
       </c>
       <c r="B175" s="8">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="77"/>
+        <v>0</v>
+      </c>
+      <c r="C175" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D175" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="8">
-        <f t="shared" ref="A176:B176" si="77">+A175</f>
-        <v>0</v>
+        <f t="shared" ref="A176:B176" si="78">+A175</f>
+        <v>1</v>
       </c>
       <c r="B176" s="8">
-        <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="78"/>
+        <v>0</v>
+      </c>
+      <c r="C176" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D176" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="8">
-        <f t="shared" ref="A177:B177" si="78">+A176</f>
-        <v>0</v>
+        <f t="shared" ref="A177:B177" si="79">+A176</f>
+        <v>1</v>
       </c>
       <c r="B177" s="8">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="79"/>
+        <v>0</v>
+      </c>
+      <c r="C177" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D177" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="8">
-        <f t="shared" ref="A178:B178" si="79">+A177</f>
-        <v>0</v>
+        <f t="shared" ref="A178:B178" si="80">+A177</f>
+        <v>1</v>
       </c>
       <c r="B178" s="8">
-        <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="C178" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D178" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="8">
-        <f t="shared" ref="A179:B179" si="80">+A178</f>
-        <v>0</v>
+        <f t="shared" ref="A179:B179" si="81">+A178</f>
+        <v>1</v>
       </c>
       <c r="B179" s="8">
-        <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="81"/>
+        <v>0</v>
+      </c>
+      <c r="C179" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D179" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="8">
-        <f t="shared" ref="A180:B180" si="81">+A179</f>
-        <v>0</v>
+        <f t="shared" ref="A180:B180" si="82">+A179</f>
+        <v>1</v>
       </c>
       <c r="B180" s="8">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="C180" s="8">
+        <f t="shared" si="67"/>
+        <v>0</v>
+      </c>
+      <c r="D180" s="8">
+        <f t="shared" si="67"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="8">
-        <f t="shared" ref="A181:B181" si="82">+A180</f>
-        <v>0</v>
+        <f t="shared" ref="A181:D196" si="83">+A180</f>
+        <v>1</v>
       </c>
       <c r="B181" s="8">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="C181" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D181" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="8">
-        <f t="shared" ref="A182:B182" si="83">+A181</f>
-        <v>0</v>
+        <f t="shared" ref="A182:B182" si="84">+A181</f>
+        <v>1</v>
       </c>
       <c r="B182" s="8">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="C182" s="8">
         <f t="shared" si="83"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D182" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="8">
-        <f t="shared" ref="A183:B183" si="84">+A182</f>
-        <v>0</v>
+        <f t="shared" ref="A183:B183" si="85">+A182</f>
+        <v>1</v>
       </c>
       <c r="B183" s="8">
-        <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="C183" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D183" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="8">
-        <f t="shared" ref="A184:B184" si="85">+A183</f>
-        <v>0</v>
+        <f t="shared" ref="A184:B184" si="86">+A183</f>
+        <v>1</v>
       </c>
       <c r="B184" s="8">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="C184" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D184" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="8">
-        <f t="shared" ref="A185:B185" si="86">+A184</f>
-        <v>0</v>
+        <f t="shared" ref="A185:B185" si="87">+A184</f>
+        <v>1</v>
       </c>
       <c r="B185" s="8">
-        <f t="shared" si="86"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="C185" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D185" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="8">
-        <f t="shared" ref="A186:B186" si="87">+A185</f>
-        <v>0</v>
+        <f t="shared" ref="A186:B186" si="88">+A185</f>
+        <v>1</v>
       </c>
       <c r="B186" s="8">
-        <f t="shared" si="87"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="C186" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D186" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="8">
-        <f t="shared" ref="A187:B187" si="88">+A186</f>
-        <v>0</v>
+        <f t="shared" ref="A187:B187" si="89">+A186</f>
+        <v>1</v>
       </c>
       <c r="B187" s="8">
-        <f t="shared" si="88"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="89"/>
+        <v>0</v>
+      </c>
+      <c r="C187" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D187" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="8">
-        <f t="shared" ref="A188:B188" si="89">+A187</f>
-        <v>0</v>
+        <f t="shared" ref="A188:B188" si="90">+A187</f>
+        <v>1</v>
       </c>
       <c r="B188" s="8">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="90"/>
+        <v>0</v>
+      </c>
+      <c r="C188" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D188" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="8">
-        <f t="shared" ref="A189:B189" si="90">+A188</f>
-        <v>0</v>
+        <f t="shared" ref="A189:B189" si="91">+A188</f>
+        <v>1</v>
       </c>
       <c r="B189" s="8">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="C189" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D189" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="8">
-        <f t="shared" ref="A190:B190" si="91">+A189</f>
-        <v>0</v>
+        <f t="shared" ref="A190:B190" si="92">+A189</f>
+        <v>1</v>
       </c>
       <c r="B190" s="8">
-        <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="92"/>
+        <v>0</v>
+      </c>
+      <c r="C190" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D190" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="8">
-        <f t="shared" ref="A191:B191" si="92">+A190</f>
-        <v>0</v>
+        <f t="shared" ref="A191:B191" si="93">+A190</f>
+        <v>1</v>
       </c>
       <c r="B191" s="8">
-        <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="C191" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D191" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="8">
-        <f t="shared" ref="A192:B192" si="93">+A191</f>
-        <v>0</v>
+        <f t="shared" ref="A192:B192" si="94">+A191</f>
+        <v>1</v>
       </c>
       <c r="B192" s="8">
-        <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="C192" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D192" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="8">
-        <f t="shared" ref="A193:B193" si="94">+A192</f>
-        <v>0</v>
+        <f t="shared" ref="A193:B193" si="95">+A192</f>
+        <v>1</v>
       </c>
       <c r="B193" s="8">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="95"/>
+        <v>0</v>
+      </c>
+      <c r="C193" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D193" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="8">
-        <f t="shared" ref="A194:B194" si="95">+A193</f>
-        <v>0</v>
+        <f t="shared" ref="A194:B194" si="96">+A193</f>
+        <v>1</v>
       </c>
       <c r="B194" s="8">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="96"/>
+        <v>0</v>
+      </c>
+      <c r="C194" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D194" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="8">
-        <f t="shared" ref="A195:B195" si="96">+A194</f>
-        <v>0</v>
+        <f t="shared" ref="A195:B195" si="97">+A194</f>
+        <v>1</v>
       </c>
       <c r="B195" s="8">
-        <f t="shared" si="96"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="97"/>
+        <v>0</v>
+      </c>
+      <c r="C195" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D195" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="8">
-        <f t="shared" ref="A196:B196" si="97">+A195</f>
-        <v>0</v>
+        <f t="shared" ref="A196:B196" si="98">+A195</f>
+        <v>1</v>
       </c>
       <c r="B196" s="8">
-        <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="98"/>
+        <v>0</v>
+      </c>
+      <c r="C196" s="8">
+        <f t="shared" si="83"/>
+        <v>0</v>
+      </c>
+      <c r="D196" s="8">
+        <f t="shared" si="83"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="8">
-        <f t="shared" ref="A197:B197" si="98">+A196</f>
-        <v>0</v>
+        <f t="shared" ref="A197:D200" si="99">+A196</f>
+        <v>1</v>
       </c>
       <c r="B197" s="8">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="99"/>
+        <v>0</v>
+      </c>
+      <c r="C197" s="8">
+        <f t="shared" si="99"/>
+        <v>0</v>
+      </c>
+      <c r="D197" s="8">
+        <f t="shared" si="99"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="8">
-        <f t="shared" ref="A198:B198" si="99">+A197</f>
-        <v>0</v>
+        <f t="shared" ref="A198:B198" si="100">+A197</f>
+        <v>1</v>
       </c>
       <c r="B198" s="8">
+        <f t="shared" si="100"/>
+        <v>0</v>
+      </c>
+      <c r="C198" s="8">
         <f t="shared" si="99"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D198" s="8">
+        <f t="shared" si="99"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="8">
-        <f t="shared" ref="A199:B199" si="100">+A198</f>
-        <v>0</v>
+        <f t="shared" ref="A199:B199" si="101">+A198</f>
+        <v>1</v>
       </c>
       <c r="B199" s="8">
-        <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+        <f t="shared" si="101"/>
+        <v>0</v>
+      </c>
+      <c r="C199" s="8">
+        <f t="shared" si="99"/>
+        <v>0</v>
+      </c>
+      <c r="D199" s="8">
+        <f t="shared" si="99"/>
+        <v>-5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="8">
-        <f t="shared" ref="A200:B200" si="101">+A199</f>
-        <v>0</v>
+        <f t="shared" ref="A200:B200" si="102">+A199</f>
+        <v>1</v>
       </c>
       <c r="B200" s="8">
-        <f t="shared" si="101"/>
-        <v>0</v>
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="C200" s="8">
+        <f t="shared" si="99"/>
+        <v>0</v>
+      </c>
+      <c r="D200" s="8">
+        <f t="shared" si="99"/>
+        <v>-5.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>

--- a/input_examples/distanceDependency_square_amp.xlsx
+++ b/input_examples/distanceDependency_square_amp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\SelfImaging\input_examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2431E3D2-1EB0-4AA9-9E14-2EA37F18DC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445090C1-532E-4EC1-943D-F1A4D2A298B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grating" sheetId="1" r:id="rId1"/>
@@ -5103,9 +5103,9 @@
   <dimension ref="A1:C200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -5135,6 +5135,7 @@
         <v>633</v>
       </c>
       <c r="B3" s="10">
+        <f>+B2</f>
         <v>0</v>
       </c>
       <c r="C3" s="8">
@@ -5146,6 +5147,7 @@
         <v>633</v>
       </c>
       <c r="B4" s="10">
+        <f t="shared" ref="B4:B67" si="0">+B3</f>
         <v>0</v>
       </c>
       <c r="C4" s="8">
@@ -5157,6 +5159,7 @@
         <v>633</v>
       </c>
       <c r="B5" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C5" s="8">
@@ -5168,6 +5171,7 @@
         <v>633</v>
       </c>
       <c r="B6" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C6" s="8">
@@ -5179,6 +5183,7 @@
         <v>633</v>
       </c>
       <c r="B7" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C7" s="8">
@@ -5190,6 +5195,7 @@
         <v>633</v>
       </c>
       <c r="B8" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C8" s="8">
@@ -5201,6 +5207,7 @@
         <v>633</v>
       </c>
       <c r="B9" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C9" s="8">
@@ -5212,6 +5219,7 @@
         <v>633</v>
       </c>
       <c r="B10" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C10" s="8">
@@ -5223,6 +5231,7 @@
         <v>633</v>
       </c>
       <c r="B11" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C11" s="8">
@@ -5234,6 +5243,7 @@
         <v>633</v>
       </c>
       <c r="B12" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C12" s="8">
@@ -5245,6 +5255,7 @@
         <v>633</v>
       </c>
       <c r="B13" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C13" s="8">
@@ -5256,6 +5267,7 @@
         <v>633</v>
       </c>
       <c r="B14" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C14" s="8">
@@ -5267,6 +5279,7 @@
         <v>633</v>
       </c>
       <c r="B15" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C15" s="8">
@@ -5278,6 +5291,7 @@
         <v>633</v>
       </c>
       <c r="B16" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C16" s="8">
@@ -5289,6 +5303,7 @@
         <v>633</v>
       </c>
       <c r="B17" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C17" s="8">
@@ -5300,6 +5315,7 @@
         <v>633</v>
       </c>
       <c r="B18" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C18" s="8">
@@ -5311,6 +5327,7 @@
         <v>633</v>
       </c>
       <c r="B19" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C19" s="8">
@@ -5322,6 +5339,7 @@
         <v>633</v>
       </c>
       <c r="B20" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C20" s="8">
@@ -5333,6 +5351,7 @@
         <v>633</v>
       </c>
       <c r="B21" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C21" s="8">
@@ -5344,6 +5363,7 @@
         <v>633</v>
       </c>
       <c r="B22" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C22" s="8">
@@ -5355,6 +5375,7 @@
         <v>633</v>
       </c>
       <c r="B23" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C23" s="8">
@@ -5366,6 +5387,7 @@
         <v>633</v>
       </c>
       <c r="B24" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C24" s="8">
@@ -5377,6 +5399,7 @@
         <v>633</v>
       </c>
       <c r="B25" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C25" s="8">
@@ -5388,6 +5411,7 @@
         <v>633</v>
       </c>
       <c r="B26" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C26" s="8">
@@ -5399,6 +5423,7 @@
         <v>633</v>
       </c>
       <c r="B27" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C27" s="8">
@@ -5410,6 +5435,7 @@
         <v>633</v>
       </c>
       <c r="B28" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C28" s="8">
@@ -5421,6 +5447,7 @@
         <v>633</v>
       </c>
       <c r="B29" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C29" s="8">
@@ -5432,6 +5459,7 @@
         <v>633</v>
       </c>
       <c r="B30" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C30" s="8">
@@ -5443,6 +5471,7 @@
         <v>633</v>
       </c>
       <c r="B31" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C31" s="8">
@@ -5454,6 +5483,7 @@
         <v>633</v>
       </c>
       <c r="B32" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C32" s="8">
@@ -5465,6 +5495,7 @@
         <v>633</v>
       </c>
       <c r="B33" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C33" s="8">
@@ -5476,6 +5507,7 @@
         <v>633</v>
       </c>
       <c r="B34" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C34" s="8">
@@ -5487,6 +5519,7 @@
         <v>633</v>
       </c>
       <c r="B35" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C35" s="8">
@@ -5498,6 +5531,7 @@
         <v>633</v>
       </c>
       <c r="B36" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C36" s="8">
@@ -5509,6 +5543,7 @@
         <v>633</v>
       </c>
       <c r="B37" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C37" s="8">
@@ -5520,6 +5555,7 @@
         <v>633</v>
       </c>
       <c r="B38" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C38" s="8">
@@ -5531,6 +5567,7 @@
         <v>633</v>
       </c>
       <c r="B39" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C39" s="8">
@@ -5542,6 +5579,7 @@
         <v>633</v>
       </c>
       <c r="B40" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C40" s="8">
@@ -5553,6 +5591,7 @@
         <v>633</v>
       </c>
       <c r="B41" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C41" s="8">
@@ -5564,6 +5603,7 @@
         <v>633</v>
       </c>
       <c r="B42" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C42" s="8">
@@ -5575,6 +5615,7 @@
         <v>633</v>
       </c>
       <c r="B43" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C43" s="8">
@@ -5586,6 +5627,7 @@
         <v>633</v>
       </c>
       <c r="B44" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C44" s="8">
@@ -5597,6 +5639,7 @@
         <v>633</v>
       </c>
       <c r="B45" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C45" s="8">
@@ -5608,6 +5651,7 @@
         <v>633</v>
       </c>
       <c r="B46" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" s="8">
@@ -5619,6 +5663,7 @@
         <v>633</v>
       </c>
       <c r="B47" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C47" s="8">
@@ -5630,6 +5675,7 @@
         <v>633</v>
       </c>
       <c r="B48" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" s="8">
@@ -5641,6 +5687,7 @@
         <v>633</v>
       </c>
       <c r="B49" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C49" s="8">
@@ -5652,6 +5699,7 @@
         <v>633</v>
       </c>
       <c r="B50" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="8">
@@ -5663,6 +5711,7 @@
         <v>633</v>
       </c>
       <c r="B51" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="8">
@@ -5674,6 +5723,7 @@
         <v>633</v>
       </c>
       <c r="B52" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="8">
@@ -5685,6 +5735,7 @@
         <v>633</v>
       </c>
       <c r="B53" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="8">
@@ -5696,6 +5747,7 @@
         <v>633</v>
       </c>
       <c r="B54" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="8">
@@ -5707,6 +5759,7 @@
         <v>633</v>
       </c>
       <c r="B55" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="8">
@@ -5718,6 +5771,7 @@
         <v>633</v>
       </c>
       <c r="B56" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="8">
@@ -5729,6 +5783,7 @@
         <v>633</v>
       </c>
       <c r="B57" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="8">
@@ -5740,6 +5795,7 @@
         <v>633</v>
       </c>
       <c r="B58" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="8">
@@ -5751,6 +5807,7 @@
         <v>633</v>
       </c>
       <c r="B59" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="8">
@@ -5762,6 +5819,7 @@
         <v>633</v>
       </c>
       <c r="B60" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="8">
@@ -5773,6 +5831,7 @@
         <v>633</v>
       </c>
       <c r="B61" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="8">
@@ -5784,6 +5843,7 @@
         <v>633</v>
       </c>
       <c r="B62" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="8">
@@ -5795,6 +5855,7 @@
         <v>633</v>
       </c>
       <c r="B63" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="8">
@@ -5806,6 +5867,7 @@
         <v>633</v>
       </c>
       <c r="B64" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="8">
@@ -5817,6 +5879,7 @@
         <v>633</v>
       </c>
       <c r="B65" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="8">
@@ -5828,6 +5891,7 @@
         <v>633</v>
       </c>
       <c r="B66" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="8">
@@ -5839,6 +5903,7 @@
         <v>633</v>
       </c>
       <c r="B67" s="10">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C67" s="8">
@@ -5850,6 +5915,7 @@
         <v>633</v>
       </c>
       <c r="B68" s="10">
+        <f t="shared" ref="B68:B131" si="1">+B67</f>
         <v>0</v>
       </c>
       <c r="C68" s="8">
@@ -5861,6 +5927,7 @@
         <v>633</v>
       </c>
       <c r="B69" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="8">
@@ -5872,6 +5939,7 @@
         <v>633</v>
       </c>
       <c r="B70" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="8">
@@ -5883,6 +5951,7 @@
         <v>633</v>
       </c>
       <c r="B71" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="8">
@@ -5894,6 +5963,7 @@
         <v>633</v>
       </c>
       <c r="B72" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="8">
@@ -5905,6 +5975,7 @@
         <v>633</v>
       </c>
       <c r="B73" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="8">
@@ -5916,6 +5987,7 @@
         <v>633</v>
       </c>
       <c r="B74" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="8">
@@ -5927,6 +5999,7 @@
         <v>633</v>
       </c>
       <c r="B75" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="8">
@@ -5938,6 +6011,7 @@
         <v>633</v>
       </c>
       <c r="B76" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="8">
@@ -5949,6 +6023,7 @@
         <v>633</v>
       </c>
       <c r="B77" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="8">
@@ -5960,6 +6035,7 @@
         <v>633</v>
       </c>
       <c r="B78" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="8">
@@ -5971,6 +6047,7 @@
         <v>633</v>
       </c>
       <c r="B79" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="8">
@@ -5982,6 +6059,7 @@
         <v>633</v>
       </c>
       <c r="B80" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="8">
@@ -5993,6 +6071,7 @@
         <v>633</v>
       </c>
       <c r="B81" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="8">
@@ -6004,6 +6083,7 @@
         <v>633</v>
       </c>
       <c r="B82" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="8">
@@ -6015,6 +6095,7 @@
         <v>633</v>
       </c>
       <c r="B83" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="8">
@@ -6026,6 +6107,7 @@
         <v>633</v>
       </c>
       <c r="B84" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="8">
@@ -6037,6 +6119,7 @@
         <v>633</v>
       </c>
       <c r="B85" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="8">
@@ -6048,6 +6131,7 @@
         <v>633</v>
       </c>
       <c r="B86" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="8">
@@ -6059,6 +6143,7 @@
         <v>633</v>
       </c>
       <c r="B87" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="8">
@@ -6070,6 +6155,7 @@
         <v>633</v>
       </c>
       <c r="B88" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="8">
@@ -6081,6 +6167,7 @@
         <v>633</v>
       </c>
       <c r="B89" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="8">
@@ -6092,6 +6179,7 @@
         <v>633</v>
       </c>
       <c r="B90" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="8">
@@ -6103,6 +6191,7 @@
         <v>633</v>
       </c>
       <c r="B91" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="8">
@@ -6114,6 +6203,7 @@
         <v>633</v>
       </c>
       <c r="B92" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="8">
@@ -6125,6 +6215,7 @@
         <v>633</v>
       </c>
       <c r="B93" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="8">
@@ -6136,6 +6227,7 @@
         <v>633</v>
       </c>
       <c r="B94" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="8">
@@ -6147,6 +6239,7 @@
         <v>633</v>
       </c>
       <c r="B95" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="8">
@@ -6158,6 +6251,7 @@
         <v>633</v>
       </c>
       <c r="B96" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="8">
@@ -6169,6 +6263,7 @@
         <v>633</v>
       </c>
       <c r="B97" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="8">
@@ -6180,6 +6275,7 @@
         <v>633</v>
       </c>
       <c r="B98" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="8">
@@ -6191,6 +6287,7 @@
         <v>633</v>
       </c>
       <c r="B99" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="8">
@@ -6202,6 +6299,7 @@
         <v>633</v>
       </c>
       <c r="B100" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="8">
@@ -6213,6 +6311,7 @@
         <v>633</v>
       </c>
       <c r="B101" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="8">
@@ -6224,6 +6323,7 @@
         <v>633</v>
       </c>
       <c r="B102" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C102" s="8">
@@ -6235,6 +6335,7 @@
         <v>633</v>
       </c>
       <c r="B103" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C103" s="8">
@@ -6246,6 +6347,7 @@
         <v>633</v>
       </c>
       <c r="B104" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C104" s="8">
@@ -6257,6 +6359,7 @@
         <v>633</v>
       </c>
       <c r="B105" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C105" s="8">
@@ -6268,6 +6371,7 @@
         <v>633</v>
       </c>
       <c r="B106" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C106" s="8">
@@ -6279,6 +6383,7 @@
         <v>633</v>
       </c>
       <c r="B107" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C107" s="8">
@@ -6290,6 +6395,7 @@
         <v>633</v>
       </c>
       <c r="B108" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C108" s="8">
@@ -6301,6 +6407,7 @@
         <v>633</v>
       </c>
       <c r="B109" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C109" s="8">
@@ -6312,6 +6419,7 @@
         <v>633</v>
       </c>
       <c r="B110" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C110" s="8">
@@ -6323,6 +6431,7 @@
         <v>633</v>
       </c>
       <c r="B111" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C111" s="8">
@@ -6334,6 +6443,7 @@
         <v>633</v>
       </c>
       <c r="B112" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C112" s="8">
@@ -6345,6 +6455,7 @@
         <v>633</v>
       </c>
       <c r="B113" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C113" s="8">
@@ -6356,6 +6467,7 @@
         <v>633</v>
       </c>
       <c r="B114" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C114" s="8">
@@ -6367,6 +6479,7 @@
         <v>633</v>
       </c>
       <c r="B115" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C115" s="8">
@@ -6378,6 +6491,7 @@
         <v>633</v>
       </c>
       <c r="B116" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C116" s="8">
@@ -6389,6 +6503,7 @@
         <v>633</v>
       </c>
       <c r="B117" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C117" s="8">
@@ -6400,6 +6515,7 @@
         <v>633</v>
       </c>
       <c r="B118" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C118" s="8">
@@ -6411,6 +6527,7 @@
         <v>633</v>
       </c>
       <c r="B119" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C119" s="8">
@@ -6422,6 +6539,7 @@
         <v>633</v>
       </c>
       <c r="B120" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C120" s="8">
@@ -6433,6 +6551,7 @@
         <v>633</v>
       </c>
       <c r="B121" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C121" s="8">
@@ -6444,6 +6563,7 @@
         <v>633</v>
       </c>
       <c r="B122" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C122" s="8">
@@ -6455,6 +6575,7 @@
         <v>633</v>
       </c>
       <c r="B123" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C123" s="8">
@@ -6466,6 +6587,7 @@
         <v>633</v>
       </c>
       <c r="B124" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C124" s="8">
@@ -6477,6 +6599,7 @@
         <v>633</v>
       </c>
       <c r="B125" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C125" s="8">
@@ -6488,6 +6611,7 @@
         <v>633</v>
       </c>
       <c r="B126" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C126" s="8">
@@ -6499,6 +6623,7 @@
         <v>633</v>
       </c>
       <c r="B127" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C127" s="8">
@@ -6510,6 +6635,7 @@
         <v>633</v>
       </c>
       <c r="B128" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C128" s="8">
@@ -6521,6 +6647,7 @@
         <v>633</v>
       </c>
       <c r="B129" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C129" s="8">
@@ -6532,6 +6659,7 @@
         <v>633</v>
       </c>
       <c r="B130" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C130" s="8">
@@ -6543,6 +6671,7 @@
         <v>633</v>
       </c>
       <c r="B131" s="10">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C131" s="8">
@@ -6554,6 +6683,7 @@
         <v>633</v>
       </c>
       <c r="B132" s="10">
+        <f t="shared" ref="B132:B195" si="2">+B131</f>
         <v>0</v>
       </c>
       <c r="C132" s="8">
@@ -6565,6 +6695,7 @@
         <v>633</v>
       </c>
       <c r="B133" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C133" s="8">
@@ -6576,6 +6707,7 @@
         <v>633</v>
       </c>
       <c r="B134" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C134" s="8">
@@ -6587,6 +6719,7 @@
         <v>633</v>
       </c>
       <c r="B135" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C135" s="8">
@@ -6598,6 +6731,7 @@
         <v>633</v>
       </c>
       <c r="B136" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C136" s="8">
@@ -6609,6 +6743,7 @@
         <v>633</v>
       </c>
       <c r="B137" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C137" s="8">
@@ -6620,6 +6755,7 @@
         <v>633</v>
       </c>
       <c r="B138" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C138" s="8">
@@ -6631,6 +6767,7 @@
         <v>633</v>
       </c>
       <c r="B139" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C139" s="8">
@@ -6642,6 +6779,7 @@
         <v>633</v>
       </c>
       <c r="B140" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C140" s="8">
@@ -6653,6 +6791,7 @@
         <v>633</v>
       </c>
       <c r="B141" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C141" s="8">
@@ -6664,6 +6803,7 @@
         <v>633</v>
       </c>
       <c r="B142" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C142" s="8">
@@ -6675,6 +6815,7 @@
         <v>633</v>
       </c>
       <c r="B143" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C143" s="8">
@@ -6686,6 +6827,7 @@
         <v>633</v>
       </c>
       <c r="B144" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C144" s="8">
@@ -6697,6 +6839,7 @@
         <v>633</v>
       </c>
       <c r="B145" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C145" s="8">
@@ -6708,6 +6851,7 @@
         <v>633</v>
       </c>
       <c r="B146" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C146" s="8">
@@ -6719,6 +6863,7 @@
         <v>633</v>
       </c>
       <c r="B147" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C147" s="8">
@@ -6730,6 +6875,7 @@
         <v>633</v>
       </c>
       <c r="B148" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C148" s="8">
@@ -6741,6 +6887,7 @@
         <v>633</v>
       </c>
       <c r="B149" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C149" s="8">
@@ -6752,6 +6899,7 @@
         <v>633</v>
       </c>
       <c r="B150" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C150" s="8">
@@ -6763,6 +6911,7 @@
         <v>633</v>
       </c>
       <c r="B151" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C151" s="8">
@@ -6774,6 +6923,7 @@
         <v>633</v>
       </c>
       <c r="B152" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C152" s="8">
@@ -6785,6 +6935,7 @@
         <v>633</v>
       </c>
       <c r="B153" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C153" s="8">
@@ -6796,6 +6947,7 @@
         <v>633</v>
       </c>
       <c r="B154" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C154" s="8">
@@ -6807,6 +6959,7 @@
         <v>633</v>
       </c>
       <c r="B155" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C155" s="8">
@@ -6818,6 +6971,7 @@
         <v>633</v>
       </c>
       <c r="B156" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C156" s="8">
@@ -6829,6 +6983,7 @@
         <v>633</v>
       </c>
       <c r="B157" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C157" s="8">
@@ -6840,6 +6995,7 @@
         <v>633</v>
       </c>
       <c r="B158" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C158" s="8">
@@ -6851,6 +7007,7 @@
         <v>633</v>
       </c>
       <c r="B159" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C159" s="8">
@@ -6862,6 +7019,7 @@
         <v>633</v>
       </c>
       <c r="B160" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C160" s="8">
@@ -6873,6 +7031,7 @@
         <v>633</v>
       </c>
       <c r="B161" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C161" s="8">
@@ -6884,6 +7043,7 @@
         <v>633</v>
       </c>
       <c r="B162" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C162" s="8">
@@ -6895,6 +7055,7 @@
         <v>633</v>
       </c>
       <c r="B163" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C163" s="8">
@@ -6906,6 +7067,7 @@
         <v>633</v>
       </c>
       <c r="B164" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C164" s="8">
@@ -6917,6 +7079,7 @@
         <v>633</v>
       </c>
       <c r="B165" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C165" s="8">
@@ -6928,6 +7091,7 @@
         <v>633</v>
       </c>
       <c r="B166" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C166" s="8">
@@ -6939,6 +7103,7 @@
         <v>633</v>
       </c>
       <c r="B167" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C167" s="8">
@@ -6950,6 +7115,7 @@
         <v>633</v>
       </c>
       <c r="B168" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C168" s="8">
@@ -6961,6 +7127,7 @@
         <v>633</v>
       </c>
       <c r="B169" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C169" s="8">
@@ -6972,6 +7139,7 @@
         <v>633</v>
       </c>
       <c r="B170" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C170" s="8">
@@ -6983,6 +7151,7 @@
         <v>633</v>
       </c>
       <c r="B171" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C171" s="8">
@@ -6994,6 +7163,7 @@
         <v>633</v>
       </c>
       <c r="B172" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C172" s="8">
@@ -7005,6 +7175,7 @@
         <v>633</v>
       </c>
       <c r="B173" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C173" s="8">
@@ -7016,6 +7187,7 @@
         <v>633</v>
       </c>
       <c r="B174" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C174" s="8">
@@ -7027,6 +7199,7 @@
         <v>633</v>
       </c>
       <c r="B175" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C175" s="8">
@@ -7038,6 +7211,7 @@
         <v>633</v>
       </c>
       <c r="B176" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C176" s="8">
@@ -7049,6 +7223,7 @@
         <v>633</v>
       </c>
       <c r="B177" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C177" s="8">
@@ -7060,6 +7235,7 @@
         <v>633</v>
       </c>
       <c r="B178" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C178" s="8">
@@ -7071,6 +7247,7 @@
         <v>633</v>
       </c>
       <c r="B179" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C179" s="8">
@@ -7082,6 +7259,7 @@
         <v>633</v>
       </c>
       <c r="B180" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C180" s="8">
@@ -7093,6 +7271,7 @@
         <v>633</v>
       </c>
       <c r="B181" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C181" s="8">
@@ -7104,6 +7283,7 @@
         <v>633</v>
       </c>
       <c r="B182" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C182" s="8">
@@ -7115,6 +7295,7 @@
         <v>633</v>
       </c>
       <c r="B183" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C183" s="8">
@@ -7126,6 +7307,7 @@
         <v>633</v>
       </c>
       <c r="B184" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C184" s="8">
@@ -7137,6 +7319,7 @@
         <v>633</v>
       </c>
       <c r="B185" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C185" s="8">
@@ -7148,6 +7331,7 @@
         <v>633</v>
       </c>
       <c r="B186" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C186" s="8">
@@ -7159,6 +7343,7 @@
         <v>633</v>
       </c>
       <c r="B187" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C187" s="8">
@@ -7170,6 +7355,7 @@
         <v>633</v>
       </c>
       <c r="B188" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C188" s="8">
@@ -7181,6 +7367,7 @@
         <v>633</v>
       </c>
       <c r="B189" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C189" s="8">
@@ -7192,6 +7379,7 @@
         <v>633</v>
       </c>
       <c r="B190" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C190" s="8">
@@ -7203,6 +7391,7 @@
         <v>633</v>
       </c>
       <c r="B191" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C191" s="8">
@@ -7214,6 +7403,7 @@
         <v>633</v>
       </c>
       <c r="B192" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C192" s="8">
@@ -7225,6 +7415,7 @@
         <v>633</v>
       </c>
       <c r="B193" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C193" s="8">
@@ -7236,6 +7427,7 @@
         <v>633</v>
       </c>
       <c r="B194" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C194" s="8">
@@ -7247,6 +7439,7 @@
         <v>633</v>
       </c>
       <c r="B195" s="10">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C195" s="8">
@@ -7258,6 +7451,7 @@
         <v>633</v>
       </c>
       <c r="B196" s="10">
+        <f t="shared" ref="B196:B200" si="3">+B195</f>
         <v>0</v>
       </c>
       <c r="C196" s="8">
@@ -7269,6 +7463,7 @@
         <v>633</v>
       </c>
       <c r="B197" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="C197" s="8">
@@ -7280,6 +7475,7 @@
         <v>633</v>
       </c>
       <c r="B198" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="C198" s="8">
@@ -7291,6 +7487,7 @@
         <v>633</v>
       </c>
       <c r="B199" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="C199" s="8">
@@ -7302,6 +7499,7 @@
         <v>633</v>
       </c>
       <c r="B200" s="10">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="C200" s="8">
